--- a/REVISION_COTIZACIONES_2026.xlsx
+++ b/REVISION_COTIZACIONES_2026.xlsx
@@ -2095,38 +2095,46 @@
       <c r="J39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>COTIZACION1294 KFCK91PASEO SHOPP MACHALA.xlsx</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>K91PASEO</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="n">
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>K91</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>K091 - MACHALA RIO CENTRO</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>87.5</v>
       </c>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'K91PASEO' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="F40" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>173.44</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2525,38 +2533,46 @@
       <c r="J50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1359 CN37 EL DORADO.xlsx</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>CN37</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="n">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>BS37</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>BS37 - DORADO</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'CN37' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="F51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3951,7 +3967,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CN35</t>
+          <t>BS35</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4119,7 +4135,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>CN34</t>
+          <t>BS34</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5517,7 +5533,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>CN26</t>
+          <t>BS26</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -6755,7 +6771,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -6765,7 +6781,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -6785,7 +6801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -6879,10 +6895,10 @@
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -6895,13 +6911,13 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">

--- a/REVISION_COTIZACIONES_2026.xlsx
+++ b/REVISION_COTIZACIONES_2026.xlsx
@@ -35,7 +35,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B942"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +102,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -6321,88 +6327,96 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="B145" s="5" t="inlineStr">
         <is>
           <t>COTIZACION1217 M33 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>M33</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>M033 - CITY MALL</t>
         </is>
       </c>
-      <c r="E145" s="3" t="n">
+      <c r="E145" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="F145" s="3" t="n">
+      <c r="F145" s="5" t="n">
         <v>63.8</v>
       </c>
-      <c r="G145" s="3" t="inlineStr">
+      <c r="G145" s="5" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H145" s="3" t="n">
+      <c r="H145" s="5" t="n">
         <v>56.11</v>
       </c>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J145" s="3" t="inlineStr"/>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>Cotización emitida como MANTENIMIENTO ($28.0=28.0), debe ser RECARGA ($63.8)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>COTIZACION1218 CJNC11 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>J11</t>
         </is>
       </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>J011 - CITY MALL</t>
         </is>
       </c>
-      <c r="E146" s="3" t="n">
+      <c r="E146" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="F146" s="3" t="n">
+      <c r="F146" s="5" t="n">
         <v>63.8</v>
       </c>
-      <c r="G146" s="3" t="inlineStr">
+      <c r="G146" s="5" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H146" s="3" t="n">
+      <c r="H146" s="5" t="n">
         <v>56.11</v>
       </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J146" s="3" t="inlineStr"/>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>Cotización emitida como MANTENIMIENTO ($28.0=28.0), debe ser RECARGA ($63.8)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -6473,88 +6487,96 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>COTIZACION1221 M61 PORTETE.xlsx</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C149" s="5" t="inlineStr">
         <is>
           <t>M61</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>M061 - PORTETE</t>
         </is>
       </c>
-      <c r="E149" s="3" t="n">
+      <c r="E149" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="F149" s="3" t="n">
+      <c r="F149" s="5" t="n">
         <v>152</v>
       </c>
-      <c r="G149" s="3" t="inlineStr">
+      <c r="G149" s="5" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H149" s="3" t="n">
+      <c r="H149" s="5" t="n">
         <v>57.89</v>
       </c>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J149" s="3" t="inlineStr"/>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>Cotización emitida como MANTENIMIENTO ($64.0=64.0), debe ser RECARGA ($152.0)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>COTIZACION1222 KFCK109 CITY MALL PA.xlsx</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>K109</t>
         </is>
       </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>K109 - CITY MALL PA</t>
         </is>
       </c>
-      <c r="E150" s="3" t="n">
+      <c r="E150" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="F150" s="3" t="n">
+      <c r="F150" s="5" t="n">
         <v>72.8</v>
       </c>
-      <c r="G150" s="3" t="inlineStr">
+      <c r="G150" s="5" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H150" s="3" t="n">
+      <c r="H150" s="5" t="n">
         <v>56.04</v>
       </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J150" s="3" t="inlineStr"/>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>Cotización emitida como MANTENIMIENTO ($32.0=32.0), debe ser RECARGA ($72.8)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -6641,46 +6663,50 @@
       <c r="J152" s="3" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B153" s="5" t="inlineStr">
         <is>
           <t>COTIZACION1216 KFCK117 SEDALANA.xlsx</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C153" s="5" t="inlineStr">
         <is>
           <t>K117</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>K117 - 29 Y SEDALANA</t>
         </is>
       </c>
-      <c r="E153" s="3" t="n">
+      <c r="E153" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="F153" s="3" t="n">
+      <c r="F153" s="5" t="n">
         <v>241.2</v>
       </c>
-      <c r="G153" s="3" t="inlineStr">
+      <c r="G153" s="5" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H153" s="3" t="n">
+      <c r="H153" s="5" t="n">
         <v>56.88</v>
       </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J153" s="3" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>Cotización emitida como MANTENIMIENTO ($104.0=104.0), debe ser RECARGA ($241.2)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -6735,7 +6761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -6743,7 +6769,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>RESUMEN DE REVISION COTIZACIONES 2026</t>
         </is>
@@ -6777,279 +6803,324 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INCONSISTENCIAS (diferencia &gt; 1%)</t>
+          <t>INCONSISTENCIAS DE PRECIO (diferencia &gt; 1%)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SIN SUBTOTAL en cotizacion</t>
+          <t>COT_DEBE_RECARGA (emitida como MANT, debe ser RECARGA)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIN MATCH en base de datos</t>
+          <t>SIN SUBTOTAL en cotizacion</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIN VALOR en base de datos</t>
+          <t>SIN MATCH en base de datos (otras marcas)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>SIN VALOR en base de datos</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>ERRORES (descarga/parseo)</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DETALLE POR MES</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MES</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>OTROS</t>
-        </is>
-      </c>
+          <t>DETALLE POR MES</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENERO</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>24</v>
-      </c>
-      <c r="C13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
+          <t>MES</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FEBRERO</t>
+          <t>ENERO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MARZO</t>
+          <t>FEBRERO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
         <v>7</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAYO</t>
+          <t>ABRIL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JUNIO</t>
+          <t>MAYO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JULIO</t>
+          <t>JUNIO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AGOSTO</t>
+          <t>JULIO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C20" t="n">
         <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEPTIEMBRE</t>
+          <t>AGOSTO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>11</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
         <v>3</v>
       </c>
     </row>

--- a/REVISION_COTIZACIONES_2026.xlsx
+++ b/REVISION_COTIZACIONES_2026.xlsx
@@ -94,15 +94,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -469,22 +489,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:L154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MES</t>
@@ -532,7 +554,17 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>NOTAS</t>
+          <t>COT_DETALLE</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>DB_DETALLE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ANALISIS</t>
         </is>
       </c>
     </row>
@@ -576,7 +608,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -618,7 +652,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -660,49 +696,65 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1282 KFCK79 BABAHOYO.xlsx</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>K79</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>K079 - BABAHOYO</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>126.7</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>295.94</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>1×??@$48 + 1×10lbPQS@$34</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>-2 ext en COT vs DB (2 vs 4) | ⚠ suma líneas COT=$81.80 ≠ subtotal=$126.70 | Extra en COT: +1×??(@$48) | Falta en COT: -1×50lbCO2, -1×10lbCO2, -1×10lbPQS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -744,7 +796,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -786,7 +840,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -828,91 +884,121 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1262 KFCK25 MOBIL DURAN.xlsx</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>K25</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>K025 - MOBIL DURAN</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>9.52</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbCO2@$4 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (5 vs 4) | Extra en COT: +1×10lbPQS(@$4)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1273 KFCK154 PASCUALES.xlsx</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>K154</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>K154 - PASCUALES</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>3.85</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 1×20lbPQS@$8 + 3×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (9 vs 8) | Extra en COT: +1×5lbCO2(@$2), +1×2.5glnK(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -954,7 +1040,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -996,7 +1084,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1038,7 +1128,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1080,7 +1172,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1122,49 +1216,65 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1267 KFCK76 PARQUE CENTENARIO.xlsx</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>K76</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>K076 - PARQUE CENTENARIO</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="n">
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>-1 ext en COT vs DB (6 vs 7) | Falta en COT: -1×10lbPQS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1206,7 +1316,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1248,7 +1360,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1290,7 +1404,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1332,7 +1448,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1374,7 +1492,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1416,49 +1536,65 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1271 KFCK105 RIOCENTRO NORTE.xlsx</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>K105</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>K105 - HIPER MARKET</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n">
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
         <v>4.55</v>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$4 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Precio unitario distinto ($11.50 vs $11.00/ext)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1500,7 +1636,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1542,7 +1680,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1584,91 +1724,121 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1291 KFCK45 BOYACA.xlsx</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>K45</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>K045 - BOYACA</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n">
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
         <v>6.06</v>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 3×20lbPQS@$8 + 6×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (11 vs 10) | Extra en COT: +1×10lbPQS(@$4)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1295 KFCK148 TERMINAL MACHALA.xlsx</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>K148</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>K148 - TERMINAL TERRESTRE MACHALA</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>93.5</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="n">
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
         <v>146.05</v>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbPQS@$2 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$38.00 ≠ subtotal=$93.50 | Extra en COT: +1×2.5glnK(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1710,7 +1880,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1752,109 +1924,117 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1301 ESPE06 MALL DEL SOL.xlsx</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>ESPE6</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="n">
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ESPE6' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1302 ESPE10 SAN MARINO.xlsx</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>ESPE10</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="n">
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ESPE10' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1303 ESPE26 RIOC PUNTILLA.xlsx</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>ESPE26</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="n">
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ESPE26' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1896,7 +2076,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1938,7 +2120,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1980,209 +2164,269 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1307 ILCI02 RIOC. CEIBOS.xlsx</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>ILCI2</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="n">
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ILCI2' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1308 JV75 PASEO SHOPPING MACHALA.xlsx</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>V75</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>V075 - PASEO SHOPPING MACHALA</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="n">
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 1×10lbCO2@$4</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$8.00 ≠ subtotal=$16.00 | Extra en COT: +2×10lbPQS(@$4) | Falta en COT: -2×10lbCO2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1293 KFCK90 MACHALA CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>K90</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>K090 - MACHALA CENTRO</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>111.5</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="n">
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>99.11</v>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 4×5lbCO2@$2 + 1×10lbPQS@$4 + 3×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$56.00 ≠ subtotal=$111.50</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1294 KFCK91PASEO SHOPP MACHALA.xlsx</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>K91</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>K091 - MACHALA RIO CENTRO</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>87.5</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F40" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="n">
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
         <v>173.44</v>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×2.5glnK@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$32.00 ≠ subtotal=$87.50 | Extra en COT: +1×2.5glnK(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1292 KFCK65 MILAGRO.xlsx</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>K65</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>K065 - MILAGRO</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F41" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="n">
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
         <v>69.44</v>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbCO2@$4</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$36.00 ≠ subtotal=$61.00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2224,83 +2468,101 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1309 JV79 MILAGRO.xlsx</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>V79</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>V079 - MILAGRO</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="F43" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="n">
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$8.00 ≠ subtotal=$16.00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1296 AMCA37 EL DORADO.xlsx</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>AMCA37</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="n">
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'AMCA37' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2342,41 +2604,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1352 GUSG49 DURAN.xlsx</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>GUSG49</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="n">
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'GUSG49' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2418,7 +2684,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2460,83 +2728,101 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1357 ILCI05 SAN MARINO.xlsx</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>ILCI5</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="n">
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ILCI5' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1358 KFCK75 MOBIL KENNEDY.xlsx</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>K75</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>K075 - MOBIL KENNEDY</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="n">
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 2×10lbPQS@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (5 vs 4) | Extra en COT: +1×20lbPQS(@$8)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2578,7 +2864,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2620,7 +2908,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2662,7 +2952,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2704,175 +2996,233 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1350 KFCK94 PASEO SHOPPING DURAN.xlsx</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>K94</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>K094 - OUTLET DURAN</t>
         </is>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="F55" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="n">
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
         <v>6.25</v>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>-1 ext en COT vs DB (4 vs 5) | Falta en COT: -1×5lbCO2</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1353 M11 MALL DEL SUR.xlsx</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>M011 - MALL SUR</t>
         </is>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F56" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="n">
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
         <v>26.32</v>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×10lbPQS@$4 + 1×5lbCO2@$2 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>+2 ext en COT vs DB (5 vs 3) | Extra en COT: +1×5lbCO2(@$2), +1×2.5glnK(@$8)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1351 KFCK145 AKI SAN EDUARDO.xlsx</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>K145</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>K145 - SUPER AKI SAN EDUARDO</t>
         </is>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="n">
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
         <v>19.05</v>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 2×10lbPQS@$4 + 1×2.5glnK@$8 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (8 vs 7) | Extra en COT: +1×2.5glnK(@$8), +1×20lbPQS(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1354 M37 CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>M37</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>M037 - 9 DE OCTUBRE</t>
         </is>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="n">
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
         <v>20.83</v>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 6×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Extra en COT: +1×75lbCO2(@$30) | Falta en COT: -1×50lbCO2</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2914,41 +3264,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1404 ILCI12 TERMINAL.xlsx</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>ILCI12</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="4" t="n">
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="n"/>
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ILCI12' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2990,41 +3344,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1403 GUSG45 TUNGURAHUA.xlsx</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>GUSG45</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="4" t="n">
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="F62" s="4" t="n"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="n"/>
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'GUSG45' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3066,49 +3424,65 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1401 KFCK82 PLAYAS.xlsx</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>K82</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>K082 - SHOPPING PLAYAS</t>
         </is>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="F64" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="n">
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="n">
         <v>137.5</v>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbPQS@$4 + 2×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$32.00 ≠ subtotal=$76.00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3150,91 +3524,121 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1400 KFCK124 GRAN AKI LOJA.xlsx</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>K124</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>K124 - GRAN AKI</t>
         </is>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="F66" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="n">
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n">
         <v>28.57</v>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>3×10lbCO2@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 1×10lbCO2@$4 + 1×10lbCO2@$4 + 1×20lbPQS@$8 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>-1 ext en COT vs DB (4 vs 5) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1407 KFCK88 HIPER VIA A DAULE.xlsx</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>K88</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>K088 - HIPERMARKET VIA DAULE</t>
         </is>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="F67" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="n">
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="n">
         <v>19.52</v>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$34</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>-6 ext en COT vs DB (1 vs 7) | Falta en COT: -1×50lbCO2, -3×5lbCO2, -1×10lbPQS, -1×20lbPQS</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3276,41 +3680,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1455 AMCA24 MALL DEL SUR.xlsx</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>AMCA24</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="4" t="n">
+      <c r="D69" s="6" t="inlineStr"/>
+      <c r="E69" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F69" s="4" t="n"/>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="F69" s="6" t="n"/>
+      <c r="G69" s="6" t="inlineStr"/>
+      <c r="H69" s="6" t="n"/>
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'AMCA24' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3352,7 +3760,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3394,7 +3804,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3436,7 +3848,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3478,7 +3892,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3520,445 +3936,565 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1453 GUSG50 MALL DEL SUR.xlsx</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>GUSG50</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr"/>
-      <c r="E75" s="4" t="n">
+      <c r="D75" s="6" t="inlineStr"/>
+      <c r="E75" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="inlineStr"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'GUSG50' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1454 AMCA06 TERMINAL.xlsx</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>AMCA6</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr"/>
-      <c r="E76" s="4" t="n">
+      <c r="D76" s="6" t="inlineStr"/>
+      <c r="E76" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="inlineStr"/>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'AMCA6' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr"/>
+      <c r="L76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1460 R004 SAN MARINO.xlsx</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>R004 - SAN MARINO</t>
         </is>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="n">
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="n">
         <v>13.89</v>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J77" s="3" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>2×50lbCO2@$20 + 3×5lbCO2@$2 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Extra en COT: +1×50lbCO2(@$20), +1×2.5glnK(@$8) | Falta en COT: -1×75lbCO2, -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1463 R010 ORELLANA.xlsx</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>R010 - FRANCISCO DE ORELLANA</t>
         </is>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="4" t="n">
         <v>418.7</v>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="n">
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="n">
         <v>310.49</v>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr"/>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 2×10lbCO2@$9 + 4×5lbCO2@$4 + 1×20lbPQS@$20 + 10×10lbPQS@$10 + 2×2.5glnK@$99</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>+2 ext en COT vs DB (20 vs 18) | Extra en COT: +1×10lbCO2(@$9), +1×10lbPQS(@$10), +2×2.5glnK(@$99) | Falta en COT: -2×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1462 R008 MALL DEL SOL.xlsx</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>R008 - MALL DEL SOL</t>
         </is>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="4" t="n">
         <v>232.5</v>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="n">
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
         <v>252.27</v>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>2×50lbCO2@$45 + 1×5lbCO2@$4 + 4×10lbPQS@$10 + 1×2.5glnK@$99</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×50lbCO2@$20 + 1×50lbCO2@$20 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Extra en COT: +1×2.5glnK(@$99) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1461 R003 CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>R003 - 9 DE OCTUBRE</t>
         </is>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="4" t="n">
         <v>192</v>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="n">
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J80" s="3" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 2×5lbCO2@$4 + 4×10lbPQS@$10 + 1×2.5glnK@$99</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Extra en COT: +1×2.5glnK(@$99) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1452 KFCK96 PORTETE.xlsx</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>K96</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>K096 - PORTETE</t>
         </is>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="F81" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="n">
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
         <v>11.63</v>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J81" s="3" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>2×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×20lbPQS@$8 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Extra en COT: +1×5lbCO2(@$2), +1×10lbPQS(@$4) | Falta en COT: -2×20lbPQS</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1464 R010 ORELLANA.xlsx</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>R010 - FRANCISCO DE ORELLANA</t>
         </is>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="F82" s="3" t="n">
+      <c r="F82" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="n">
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
         <v>11.76</v>
       </c>
-      <c r="I82" s="3" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>(sin líneas)</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>-18 ext en COT vs DB (0 vs 18) | ⚠ suma líneas COT=$0.00 ≠ subtotal=$90.00 | Falta en COT: -1×75lbCO2, -1×10lbCO2, -4×5lbCO2, -1×20lbPQS, -9×10lbPQS, -2×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1501 ILCI04 MALL DEL SUR.xlsx</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>ILCI4</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr"/>
-      <c r="E83" s="4" t="n">
+      <c r="D83" s="6" t="inlineStr"/>
+      <c r="E83" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="4" t="inlineStr"/>
-      <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="F83" s="6" t="n"/>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="n"/>
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ILCI4' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1511 F003 DOLCE INCONTRO  AEROPUERTO.xlsx</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>F003 - DOLCE INCONTRO AERGYE</t>
         </is>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="F84" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="n">
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n">
         <v>10.53</v>
       </c>
-      <c r="I84" s="3" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr"/>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 3×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (6 vs 5) | Extra en COT: +1×10lbPQS(@$4), +1×2.5glnK(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1507 CJNC08 TERMINAL.xlsx</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>J8</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>J008 - TERMINAL</t>
         </is>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="F85" s="3" t="n">
+      <c r="F85" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="n">
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="n">
         <v>26.32</v>
       </c>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="I85" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr"/>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Extra en COT: +1×50lbCO2(@$20) | Falta en COT: -1×75lbCO2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4000,7 +4536,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4042,49 +4580,65 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1512 KFCK83 MUCHO LOTE.xlsx</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>K83</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>K083 - MUCHO LOTE</t>
         </is>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="F88" s="3" t="n">
+      <c r="F88" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="n">
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n">
         <v>17.39</v>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr"/>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 2×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×20lbPQS@$8 + 1×75lbCO2@$30</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (6 vs 5) | Extra en COT: +1×20lbPQS(@$8)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4126,7 +4680,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4168,75 +4724,81 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1504 GUSG52 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>GUSG52</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr"/>
-      <c r="E91" s="4" t="n">
+      <c r="D91" s="6" t="inlineStr"/>
+      <c r="E91" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="inlineStr"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="inlineStr">
+      <c r="F91" s="6" t="n"/>
+      <c r="G91" s="6" t="inlineStr"/>
+      <c r="H91" s="6" t="n"/>
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'GUSG52' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1503 GUSG48 TERMINAL.xlsx</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>GUSG48</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="n">
+      <c r="D92" s="6" t="inlineStr"/>
+      <c r="E92" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="inlineStr"/>
-      <c r="H92" s="4" t="n"/>
-      <c r="I92" s="4" t="inlineStr">
+      <c r="F92" s="6" t="n"/>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="n"/>
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'GUSG48' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4278,49 +4840,65 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1500 KFCK79 MALECON BABAHOYO.xlsx</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>K79</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>K079 - BABAHOYO</t>
         </is>
       </c>
-      <c r="E94" s="3" t="n">
+      <c r="E94" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="F94" s="3" t="n">
+      <c r="F94" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="n">
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="n">
         <v>137.5</v>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr"/>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (5 vs 4) | ⚠ suma líneas COT=$36.00 ≠ subtotal=$76.00 | Extra en COT: +1×10lbCO2(@$4)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4362,7 +4940,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4404,41 +4984,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
+      <c r="K96" s="3" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1562 DOLCEI02 RIOC CEIBOS.xlsx</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>DOLCEI2</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="n">
+      <c r="D97" s="6" t="inlineStr"/>
+      <c r="E97" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="inlineStr"/>
-      <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="inlineStr">
+      <c r="F97" s="6" t="n"/>
+      <c r="G97" s="6" t="inlineStr"/>
+      <c r="H97" s="6" t="n"/>
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'DOLCEI2' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr"/>
+      <c r="L97" s="7" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4480,49 +5064,65 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1569 KFCK93 QUEVEDO CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>K93</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>K093 - QUEVEDO</t>
         </is>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="E99" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="F99" s="3" t="n">
+      <c r="F99" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="n">
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="n">
         <v>79.55</v>
       </c>
-      <c r="I99" s="3" t="inlineStr">
+      <c r="I99" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J99" s="3" t="inlineStr"/>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbPQS@$4 + 2×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×20lbPQS@$8 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$44.00 ≠ subtotal=$79.00</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4564,117 +5164,137 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1563 DOLCEI03 RIOC ENTRE RIOS.xlsx</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>DOLCEI3</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr"/>
-      <c r="E101" s="4" t="n">
+      <c r="D101" s="6" t="inlineStr"/>
+      <c r="E101" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="4" t="inlineStr"/>
-      <c r="H101" s="4" t="n"/>
-      <c r="I101" s="4" t="inlineStr">
+      <c r="F101" s="6" t="n"/>
+      <c r="G101" s="6" t="inlineStr"/>
+      <c r="H101" s="6" t="n"/>
+      <c r="I101" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'DOLCEI3' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1564 CJNC20 LIBERTAD.xlsx</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>J20</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>J020 - CAJUN PENINSULA</t>
         </is>
       </c>
-      <c r="E102" s="3" t="n">
+      <c r="E102" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="F102" s="3" t="n">
+      <c r="F102" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="n">
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="n">
         <v>178.95</v>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J102" s="3" t="inlineStr"/>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$38.00 ≠ subtotal=$106.00</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1552 GUSG47 ALBORADA.xlsx</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>GUSG47</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr"/>
-      <c r="E103" s="4" t="n">
+      <c r="D103" s="6" t="inlineStr"/>
+      <c r="E103" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="F103" s="4" t="n"/>
-      <c r="G103" s="4" t="inlineStr"/>
-      <c r="H103" s="4" t="n"/>
-      <c r="I103" s="4" t="inlineStr">
+      <c r="F103" s="6" t="n"/>
+      <c r="G103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="n"/>
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'GUSG47' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$30 + 1×10lbCO2@$4 + 1×20lbPQS@$8 + 4×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr"/>
+      <c r="L103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4716,49 +5336,65 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1565 KFCK78 DAULE.xlsx</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>K78</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>K078 - SHOPPING DAULE</t>
         </is>
       </c>
-      <c r="E105" s="3" t="n">
+      <c r="E105" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="F105" s="3" t="n">
+      <c r="F105" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="n">
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="n">
         <v>83.33</v>
       </c>
-      <c r="I105" s="3" t="inlineStr">
+      <c r="I105" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J105" s="3" t="inlineStr"/>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$30.00 ≠ subtotal=$55.00</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4800,7 +5436,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4842,7 +5480,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr"/>
+      <c r="K107" s="3" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4884,7 +5524,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="3" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4926,7 +5568,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="3" t="inlineStr"/>
+      <c r="L109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4968,7 +5612,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5010,7 +5656,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="3" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -5052,7 +5700,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5094,437 +5744,545 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+      <c r="K113" s="3" t="inlineStr"/>
+      <c r="L113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1556 AMCA07 SAN MARINO.xlsx</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>AMCA7</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr"/>
-      <c r="E114" s="4" t="n">
+      <c r="D114" s="6" t="inlineStr"/>
+      <c r="E114" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F114" s="4" t="n"/>
-      <c r="G114" s="4" t="inlineStr"/>
-      <c r="H114" s="4" t="n"/>
-      <c r="I114" s="4" t="inlineStr">
+      <c r="F114" s="6" t="n"/>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="6" t="n"/>
+      <c r="I114" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'AMCA7' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×20lbPQS@$8 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K114" s="7" t="inlineStr"/>
+      <c r="L114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1557 AMCA20 VILLAGE PLAZA.xlsx</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>AMCA20</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr"/>
-      <c r="E115" s="4" t="n">
+      <c r="D115" s="6" t="inlineStr"/>
+      <c r="E115" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="F115" s="4" t="n"/>
-      <c r="G115" s="4" t="inlineStr"/>
-      <c r="H115" s="4" t="n"/>
-      <c r="I115" s="4" t="inlineStr">
+      <c r="F115" s="6" t="n"/>
+      <c r="G115" s="6" t="inlineStr"/>
+      <c r="H115" s="6" t="n"/>
+      <c r="I115" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'AMCA20' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K115" s="7" t="inlineStr"/>
+      <c r="L115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1573 KFCK149 VENTANAS.xlsx</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>K149</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>K149 - PETROCOMERIAL VENTANAS</t>
         </is>
       </c>
-      <c r="E116" s="3" t="n">
+      <c r="E116" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="F116" s="3" t="n">
+      <c r="F116" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="n">
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="I116" s="3" t="inlineStr">
+      <c r="I116" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J116" s="3" t="inlineStr"/>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$50.00 ≠ subtotal=$85.00 | Extra en COT: +1×2.5glnK(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1574 KFCK162 SHELL PASCUALES.xlsx</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>K162</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>K162 - DAULE ESTACION</t>
         </is>
       </c>
-      <c r="E117" s="3" t="n">
+      <c r="E117" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F117" s="3" t="n">
+      <c r="F117" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="n">
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I117" s="3" t="inlineStr">
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J117" s="3" t="inlineStr"/>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 1×10lbPQS@$4 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>Extra en COT: +1×10lbPQS(@$4), +1×2.5glnK(@$8) | Falta en COT: -1×20lbPQS, -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1575 KFCK171 SHELL ABUDHABI.xlsx</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>K171</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>K171 - SHELL ABU DABI</t>
         </is>
       </c>
-      <c r="E118" s="3" t="n">
+      <c r="E118" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="F118" s="3" t="n">
+      <c r="F118" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="n">
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I118" s="3" t="inlineStr">
+      <c r="I118" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J118" s="3" t="inlineStr"/>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×20lbPQS@$8 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>Extra en COT: +1×10lbCO2(@$4), +1×20lbPQS(@$8), +1×2.5glnK(@$8) | Falta en COT: -2×10lbPQS, -1×2.5GLSTIPO K</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1570 KFCK106 SHOPPING QUEVEDO.xlsx</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>K106</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>K106 - SHOPPING QUEVEDO</t>
         </is>
       </c>
-      <c r="E119" s="3" t="n">
+      <c r="E119" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="F119" s="3" t="n">
+      <c r="F119" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="n">
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="n">
         <v>83.33</v>
       </c>
-      <c r="I119" s="3" t="inlineStr">
+      <c r="I119" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J119" s="3" t="inlineStr"/>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$42.00 ≠ subtotal=$77.00</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1571 GUSG51 SHOPPING QUEVEDO.xlsx</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>GUSG51</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr"/>
-      <c r="E120" s="4" t="n">
+      <c r="D120" s="6" t="inlineStr"/>
+      <c r="E120" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="4" t="inlineStr"/>
-      <c r="H120" s="4" t="n"/>
-      <c r="I120" s="4" t="inlineStr">
+      <c r="F120" s="6" t="n"/>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="n"/>
+      <c r="I120" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'GUSG51' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K120" s="7" t="inlineStr"/>
+      <c r="L120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1572 M32 SHOPPING QUEVEDO.xlsx</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>M32</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>M032 - SHOPPING QUEVEDO</t>
         </is>
       </c>
-      <c r="E121" s="3" t="n">
+      <c r="E121" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="F121" s="3" t="n">
+      <c r="F121" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="n">
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="n">
         <v>92.11</v>
       </c>
-      <c r="I121" s="3" t="inlineStr">
+      <c r="I121" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J121" s="3" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$38.00 ≠ subtotal=$73.00</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1606 M39 BABAHOYO.xlsx</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>M39</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>M039 - PASEO SHOPPING BABAHOYO</t>
         </is>
       </c>
-      <c r="E122" s="3" t="n">
+      <c r="E122" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="F122" s="3" t="n">
+      <c r="F122" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="n">
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="I122" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr"/>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$28.00 ≠ subtotal=$52.00</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1614 ESPE22 AEROPUERTO ARRIBO NAC.xlsx</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>ESPE22</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr"/>
-      <c r="E123" s="4" t="n">
+      <c r="D123" s="6" t="inlineStr"/>
+      <c r="E123" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F123" s="4" t="n"/>
-      <c r="G123" s="4" t="inlineStr"/>
-      <c r="H123" s="4" t="n"/>
-      <c r="I123" s="4" t="inlineStr">
+      <c r="F123" s="6" t="n"/>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="6" t="n"/>
+      <c r="I123" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ESPE22' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 2×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K123" s="7" t="inlineStr"/>
+      <c r="L123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1603 KFCK53 SHOPPING BABAHOYO.xlsx</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>K53</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>K053 - PASEO SHOPPING BABAHOYO</t>
         </is>
       </c>
-      <c r="E124" s="3" t="n">
+      <c r="E124" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="F124" s="3" t="n">
+      <c r="F124" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="n">
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="I124" s="3" t="inlineStr">
+      <c r="I124" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J124" s="3" t="inlineStr"/>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>⚠ suma líneas COT=$28.00 ≠ subtotal=$52.00</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5566,7 +6324,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr"/>
+      <c r="K125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5608,7 +6368,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5650,7 +6412,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="3" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5692,7 +6456,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="3" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5734,7 +6500,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr"/>
+      <c r="K129" s="3" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5776,41 +6544,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1609 AMCA19 MALL DEL SOL.xlsx</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>AMCA19</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr"/>
-      <c r="E131" s="4" t="n">
+      <c r="D131" s="6" t="inlineStr"/>
+      <c r="E131" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F131" s="4" t="n"/>
-      <c r="G131" s="4" t="inlineStr"/>
-      <c r="H131" s="4" t="n"/>
-      <c r="I131" s="4" t="inlineStr">
+      <c r="F131" s="6" t="n"/>
+      <c r="G131" s="6" t="inlineStr"/>
+      <c r="H131" s="6" t="n"/>
+      <c r="I131" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'AMCA19' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr"/>
+      <c r="L131" s="7" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5852,7 +6624,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="3" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -5894,7 +6668,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -5936,7 +6712,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5978,7 +6756,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6020,7 +6800,9 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="3" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -6062,41 +6844,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="3" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1610 ESPE07 URDESA.xlsx</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>ESPE7</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr"/>
-      <c r="E138" s="4" t="n">
+      <c r="D138" s="6" t="inlineStr"/>
+      <c r="E138" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F138" s="4" t="n"/>
-      <c r="G138" s="4" t="inlineStr"/>
-      <c r="H138" s="4" t="n"/>
-      <c r="I138" s="4" t="inlineStr">
+      <c r="F138" s="6" t="n"/>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="6" t="n"/>
+      <c r="I138" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ESPE7' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>2×5lbCO2@$2 + 4×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K138" s="7" t="inlineStr"/>
+      <c r="L138" s="7" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -6138,41 +6924,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="3" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="A140" s="6" t="inlineStr">
         <is>
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1651 AMCA33 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C140" s="6" t="inlineStr">
         <is>
           <t>AMCA33</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr"/>
-      <c r="E140" s="4" t="n">
+      <c r="D140" s="6" t="inlineStr"/>
+      <c r="E140" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F140" s="4" t="n"/>
-      <c r="G140" s="4" t="inlineStr"/>
-      <c r="H140" s="4" t="n"/>
-      <c r="I140" s="4" t="inlineStr">
+      <c r="F140" s="6" t="n"/>
+      <c r="G140" s="6" t="inlineStr"/>
+      <c r="H140" s="6" t="n"/>
+      <c r="I140" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'AMCA33' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K140" s="7" t="inlineStr"/>
+      <c r="L140" s="7" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -6214,41 +7004,45 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr"/>
+      <c r="J141" s="3" t="inlineStr"/>
+      <c r="K141" s="3" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="A142" s="6" t="inlineStr">
         <is>
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B142" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1653 ESPE31 POLICENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>ESPE31</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr"/>
-      <c r="E142" s="4" t="n">
+      <c r="D142" s="6" t="inlineStr"/>
+      <c r="E142" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F142" s="4" t="n"/>
-      <c r="G142" s="4" t="inlineStr"/>
-      <c r="H142" s="4" t="n"/>
-      <c r="I142" s="4" t="inlineStr">
+      <c r="F142" s="6" t="n"/>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="6" t="n"/>
+      <c r="I142" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ESPE31' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K142" s="7" t="inlineStr"/>
+      <c r="L142" s="7" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -6290,465 +7084,565 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr"/>
+      <c r="J143" s="3" t="inlineStr"/>
+      <c r="K143" s="3" t="inlineStr"/>
+      <c r="L143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1213 KFC OFICINAS CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C144" s="6" t="inlineStr">
         <is>
           <t>KFC</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr"/>
-      <c r="E144" s="4" t="n">
+      <c r="D144" s="6" t="inlineStr"/>
+      <c r="E144" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="F144" s="4" t="n"/>
-      <c r="G144" s="4" t="inlineStr"/>
-      <c r="H144" s="4" t="n"/>
-      <c r="I144" s="4" t="inlineStr">
+      <c r="F144" s="6" t="n"/>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="6" t="n"/>
+      <c r="I144" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'KFC' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 4×5lbCO2@$2 + 12×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr"/>
+      <c r="L144" s="7" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1217 M33 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
+      <c r="C145" s="8" t="inlineStr">
         <is>
           <t>M33</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D145" s="8" t="inlineStr">
         <is>
           <t>M033 - CITY MALL</t>
         </is>
       </c>
-      <c r="E145" s="5" t="n">
+      <c r="E145" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F145" s="5" t="n">
+      <c r="F145" s="8" t="n">
         <v>63.8</v>
       </c>
-      <c r="G145" s="5" t="inlineStr">
+      <c r="G145" s="8" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H145" s="5" t="n">
+      <c r="H145" s="8" t="n">
         <v>56.11</v>
       </c>
-      <c r="I145" s="5" t="inlineStr">
+      <c r="I145" s="8" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J145" s="5" t="inlineStr">
-        <is>
-          <t>Cotización emitida como MANTENIMIENTO ($28.0=28.0), debe ser RECARGA ($63.8)</t>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
+        <is>
+          <t>Cotización usa precio MANTENIMIENTO ($28.0). Debe ser RECARGA ($63.8). | Precio unitario distinto ($7.00 vs $15.95/ext)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1218 CJNC11 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C146" s="8" t="inlineStr">
         <is>
           <t>J11</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D146" s="8" t="inlineStr">
         <is>
           <t>J011 - CITY MALL</t>
         </is>
       </c>
-      <c r="E146" s="5" t="n">
+      <c r="E146" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F146" s="5" t="n">
+      <c r="F146" s="8" t="n">
         <v>63.8</v>
       </c>
-      <c r="G146" s="5" t="inlineStr">
+      <c r="G146" s="8" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H146" s="5" t="n">
+      <c r="H146" s="8" t="n">
         <v>56.11</v>
       </c>
-      <c r="I146" s="5" t="inlineStr">
+      <c r="I146" s="8" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J146" s="5" t="inlineStr">
-        <is>
-          <t>Cotización emitida como MANTENIMIENTO ($28.0=28.0), debe ser RECARGA ($63.8)</t>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K146" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L146" s="9" t="inlineStr">
+        <is>
+          <t>Cotización usa precio MANTENIMIENTO ($28.0). Debe ser RECARGA ($63.8). | Precio unitario distinto ($7.00 vs $15.95/ext)</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="inlineStr">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1219 ESPE09 RIOCENTRO CEIBOS.xlsx</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>ESPE9</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr"/>
-      <c r="E147" s="4" t="n">
+      <c r="D147" s="6" t="inlineStr"/>
+      <c r="E147" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F147" s="4" t="n"/>
-      <c r="G147" s="4" t="inlineStr"/>
-      <c r="H147" s="4" t="n"/>
-      <c r="I147" s="4" t="inlineStr">
+      <c r="F147" s="6" t="n"/>
+      <c r="G147" s="6" t="inlineStr"/>
+      <c r="H147" s="6" t="n"/>
+      <c r="I147" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ESPE9' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K147" s="7" t="inlineStr"/>
+      <c r="L147" s="7" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1220 ESPE30 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t>ESPE30</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr"/>
-      <c r="E148" s="4" t="n">
+      <c r="D148" s="6" t="inlineStr"/>
+      <c r="E148" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F148" s="4" t="n"/>
-      <c r="G148" s="4" t="inlineStr"/>
-      <c r="H148" s="4" t="n"/>
-      <c r="I148" s="4" t="inlineStr">
+      <c r="F148" s="6" t="n"/>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="6" t="n"/>
+      <c r="I148" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>Codigo 'ESPE30' no encontrado en DB.</t>
-        </is>
-      </c>
+      <c r="J148" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K148" s="7" t="inlineStr"/>
+      <c r="L148" s="7" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1221 M61 PORTETE.xlsx</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C149" s="8" t="inlineStr">
         <is>
           <t>M61</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D149" s="8" t="inlineStr">
         <is>
           <t>M061 - PORTETE</t>
         </is>
       </c>
-      <c r="E149" s="5" t="n">
+      <c r="E149" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="F149" s="5" t="n">
+      <c r="F149" s="8" t="n">
         <v>152</v>
       </c>
-      <c r="G149" s="5" t="inlineStr">
+      <c r="G149" s="8" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H149" s="5" t="n">
+      <c r="H149" s="8" t="n">
         <v>57.89</v>
       </c>
-      <c r="I149" s="5" t="inlineStr">
+      <c r="I149" s="8" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J149" s="5" t="inlineStr">
-        <is>
-          <t>Cotización emitida como MANTENIMIENTO ($64.0=64.0), debe ser RECARGA ($152.0)</t>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 6×10lbPQS@$4 + 2×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K149" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20</t>
+        </is>
+      </c>
+      <c r="L149" s="9" t="inlineStr">
+        <is>
+          <t>Cotización usa precio MANTENIMIENTO ($64.0). Debe ser RECARGA ($152.0). | Precio unitario distinto ($6.40 vs $15.20/ext)</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1222 KFCK109 CITY MALL PA.xlsx</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C150" s="8" t="inlineStr">
         <is>
           <t>K109</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="D150" s="8" t="inlineStr">
         <is>
           <t>K109 - CITY MALL PA</t>
         </is>
       </c>
-      <c r="E150" s="5" t="n">
+      <c r="E150" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F150" s="5" t="n">
+      <c r="F150" s="8" t="n">
         <v>72.8</v>
       </c>
-      <c r="G150" s="5" t="inlineStr">
+      <c r="G150" s="8" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H150" s="5" t="n">
+      <c r="H150" s="8" t="n">
         <v>56.04</v>
       </c>
-      <c r="I150" s="5" t="inlineStr">
+      <c r="I150" s="8" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J150" s="5" t="inlineStr">
-        <is>
-          <t>Cotización emitida como MANTENIMIENTO ($32.0=32.0), debe ser RECARGA ($72.8)</t>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>1×50lb?@$20 + 1×10lbCO2@$4 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K150" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L150" s="9" t="inlineStr">
+        <is>
+          <t>Cotización usa precio MANTENIMIENTO ($32.0). Debe ser RECARGA ($72.8). | Extra en COT: +1×50lb?(@$20) | Falta en COT: -1×50lbCO2</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr">
+      <c r="B151" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1214 KFCK88 HIPER VIA A DAULE.xlsx</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
+      <c r="C151" s="4" t="inlineStr">
         <is>
           <t>K88</t>
         </is>
       </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="D151" s="4" t="inlineStr">
         <is>
           <t>K088 - HIPERMARKET VIA DAULE</t>
         </is>
       </c>
-      <c r="E151" s="3" t="n">
+      <c r="E151" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F151" s="3" t="n">
+      <c r="F151" s="4" t="n">
         <v>97.7</v>
       </c>
-      <c r="G151" s="3" t="inlineStr">
+      <c r="G151" s="4" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H151" s="3" t="n">
+      <c r="H151" s="4" t="n">
         <v>52.92</v>
       </c>
-      <c r="I151" s="3" t="inlineStr">
+      <c r="I151" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J151" s="3" t="inlineStr"/>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 3×10lbPQS@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>+1 ext en COT vs DB (8 vs 7) | Extra en COT: +1×10lbPQS(@$4)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1215 KFCK110 CITY MALL PB.xlsx</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>K110</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr">
         <is>
           <t>K110 - CITY MALL PB</t>
         </is>
       </c>
-      <c r="E152" s="3" t="n">
+      <c r="E152" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="F152" s="3" t="n">
+      <c r="F152" s="4" t="n">
         <v>124.7</v>
       </c>
-      <c r="G152" s="3" t="inlineStr">
+      <c r="G152" s="4" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H152" s="3" t="n">
+      <c r="H152" s="4" t="n">
         <v>59.9</v>
       </c>
-      <c r="I152" s="3" t="inlineStr">
+      <c r="I152" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J152" s="3" t="inlineStr"/>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×20lbPQS@$8 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbCO2@$9 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>-1 ext en COT vs DB (6 vs 7) | Falta en COT: -1×10lbCO2</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1216 KFCK117 SEDALANA.xlsx</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
+      <c r="C153" s="8" t="inlineStr">
         <is>
           <t>K117</t>
         </is>
       </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="D153" s="8" t="inlineStr">
         <is>
           <t>K117 - 29 Y SEDALANA</t>
         </is>
       </c>
-      <c r="E153" s="5" t="n">
+      <c r="E153" s="8" t="n">
         <v>104</v>
       </c>
-      <c r="F153" s="5" t="n">
+      <c r="F153" s="8" t="n">
         <v>241.2</v>
       </c>
-      <c r="G153" s="5" t="inlineStr">
+      <c r="G153" s="8" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H153" s="5" t="n">
+      <c r="H153" s="8" t="n">
         <v>56.88</v>
       </c>
-      <c r="I153" s="5" t="inlineStr">
+      <c r="I153" s="8" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J153" s="5" t="inlineStr">
-        <is>
-          <t>Cotización emitida como MANTENIMIENTO ($104.0=104.0), debe ser RECARGA ($241.2)</t>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>3×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 5×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L153" s="9" t="inlineStr">
+        <is>
+          <t>Cotización usa precio MANTENIMIENTO ($104.0). Debe ser RECARGA ($241.2). | Precio unitario distinto ($7.43 vs $17.23/ext)</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>COTIZACION1212 B001 ARRECIFE AEROPUERTO.xlsx</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D154" s="4" t="inlineStr">
         <is>
           <t>B001 - STATION SPORTS BAR</t>
         </is>
       </c>
-      <c r="E154" s="3" t="n">
+      <c r="E154" s="4" t="n">
         <v>78.8</v>
       </c>
-      <c r="F154" s="3" t="n">
+      <c r="F154" s="4" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="G154" s="3" t="inlineStr">
+      <c r="G154" s="4" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H154" s="3" t="n">
+      <c r="H154" s="4" t="n">
         <v>14.72</v>
       </c>
-      <c r="I154" s="3" t="inlineStr">
+      <c r="I154" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J154" s="3" t="inlineStr"/>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>1×20lbCO2@$20 + 3×10lbPQS@$10 + 2×5lbPQS@$5 + 1×50lbCO2@$20</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×20lbCO2@$18 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>+2 ext en COT vs DB (7 vs 5) | Extra en COT: +2×5lbPQS(@$5)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6761,17 +7655,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>RESUMEN DE REVISION COTIZACIONES 2026</t>
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>RESUMEN REVISION COTIZACIONES 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -6783,7 +7677,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TOTAL archivos revisados</t>
+          <t>Total archivos revisados</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -6793,7 +7687,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OK (diferencia &lt;= 1%)</t>
+          <t>✅ OK (≤1% diferencia)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6803,7 +7697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INCONSISTENCIAS DE PRECIO (diferencia &gt; 1%)</t>
+          <t>🔴 INCONSISTENCIA de precio (&gt;1%)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6813,7 +7707,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COT_DEBE_RECARGA (emitida como MANT, debe ser RECARGA)</t>
+          <t>🟠 COT_DEBE_RECARGA (emitida como MANT/OCT)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6823,189 +7717,252 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIN SUBTOTAL en cotizacion</t>
+          <t>🟡 SIN MATCH en DB (otras marcas)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIN MATCH en base de datos (otras marcas)</t>
+          <t>⚫ ERRORES (descarga/parseo)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SIN VALOR en base de datos</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ERRORES (descarga/parseo)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
+          <t>DETALLE POR MES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SIN_MATCH</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DETALLE POR MES</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MES</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>COT_DEBE_RECARGA</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OTROS</t>
-        </is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENERO</t>
+          <t>ABRIL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FEBRERO</t>
+          <t>MAYO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MARZO</t>
+          <t>JUNIO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>JULIO</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
         <v>8</v>
       </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MAYO</t>
+          <t>AGOSTO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7013,115 +7970,58 @@
       <c r="F18" t="n">
         <v>3</v>
       </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JUNIO</t>
+          <t>SEPTIEMBRE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JULIO</t>
+          <t>OCTUBRE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>17</v>
-      </c>
-      <c r="C21" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>11</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3</v>
+      <c r="G20" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/REVISION_COTIZACIONES_2026.xlsx
+++ b/REVISION_COTIZACIONES_2026.xlsx
@@ -725,7 +725,7 @@
         <v>126.7</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>295.94</v>
+        <v>75.97</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
@@ -747,12 +747,12 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×MOVILIZACIÓN@$40</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>-2 ext en COT vs DB (2 vs 4) | ⚠ suma líneas COT=$81.80 ≠ subtotal=$126.70 | Extra en COT: +1×??(@$48) | Falta en COT: -1×50lbCO2, -1×10lbCO2, -1×10lbPQS</t>
+          <t>-3 ext en COT vs DB (2 vs 5) | ⚠ suma líneas COT=$81.80 ≠ subtotal=$126.70 | Extra en COT: +1×??(@$48) | Falta en COT: -1×50lbCO2, -1×10lbCO2, -1×10lbPQS, -1×MOVILIZACIÓN</t>
         </is>
       </c>
     </row>
@@ -1785,60 +1785,48 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1295 KFCK148 TERMINAL MACHALA.xlsx</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>K148</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>K148 - TERMINAL TERRESTRE MACHALA</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="2" t="n">
         <v>93.5</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>146.05</v>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbPQS@$2 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$38.00 ≠ subtotal=$93.50 | Extra en COT: +1×2.5glnK(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
-        </is>
-      </c>
+      <c r="F28" s="2" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2205,228 +2193,180 @@
       <c r="L37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1308 JV75 PASEO SHOPPING MACHALA.xlsx</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>V75</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>V075 - PASEO SHOPPING MACHALA</t>
         </is>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F38" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>1×10lbCO2@$4 + 1×10lbCO2@$4</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$8.00 ≠ subtotal=$16.00 | Extra en COT: +2×10lbPQS(@$4) | Falta en COT: -2×10lbCO2</t>
-        </is>
-      </c>
+      <c r="F38" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1293 KFCK90 MACHALA CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>K90</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>K090 - MACHALA CENTRO</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="2" t="n">
         <v>111.5</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>99.11</v>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 4×5lbCO2@$2 + 1×10lbPQS@$4 + 3×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$56.00 ≠ subtotal=$111.50</t>
-        </is>
-      </c>
+      <c r="F39" s="2" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1294 KFCK91PASEO SHOPP MACHALA.xlsx</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>K91</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>K091 - MACHALA RIO CENTRO</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="2" t="n">
         <v>87.5</v>
       </c>
-      <c r="F40" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>173.44</v>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×2.5glnK@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$32.00 ≠ subtotal=$87.50 | Extra en COT: +1×2.5glnK(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1292 KFCK65 MILAGRO.xlsx</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>K65</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>K065 - MILAGRO</t>
         </is>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 3×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbCO2@$4</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$36.00 ≠ subtotal=$61.00</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2473,60 +2413,48 @@
       <c r="L42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1309 JV79 MILAGRO.xlsx</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>V79</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>V079 - MILAGRO</t>
         </is>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$8.00 ≠ subtotal=$16.00</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -3429,60 +3357,48 @@
       <c r="L63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1401 KFCK82 PLAYAS.xlsx</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>K82</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>K082 - SHOPPING PLAYAS</t>
         </is>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="F64" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×10lbPQS@$4 + 2×5lbPQS@$2</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×5lbPQS@$2</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$32.00 ≠ subtotal=$76.00</t>
-        </is>
-      </c>
+      <c r="F64" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3609,15 +3525,15 @@
         <v>33.8</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>42</v>
+        <v>97.7</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO</t>
+          <t>RECARGA</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>19.52</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
@@ -3631,7 +3547,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×20lbPQS@$8</t>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
@@ -4069,172 +3985,136 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1463 R010 ORELLANA.xlsx</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>R010 - FRANCISCO DE ORELLANA</t>
         </is>
       </c>
-      <c r="E78" s="4" t="n">
+      <c r="E78" s="2" t="n">
         <v>418.7</v>
       </c>
-      <c r="F78" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>310.49</v>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$68 + 2×10lbCO2@$9 + 4×5lbCO2@$4 + 1×20lbPQS@$20 + 10×10lbPQS@$10 + 2×2.5glnK@$99</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L78" s="5" t="inlineStr">
-        <is>
-          <t>+2 ext en COT vs DB (20 vs 18) | Extra en COT: +1×10lbCO2(@$9), +1×10lbPQS(@$10), +2×2.5glnK(@$99) | Falta en COT: -2×2.5GLSTIPO K</t>
-        </is>
-      </c>
+      <c r="F78" s="2" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1462 R008 MALL DEL SOL.xlsx</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>R008 - MALL DEL SOL</t>
         </is>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="2" t="n">
         <v>232.5</v>
       </c>
-      <c r="F79" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>252.27</v>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>2×50lbCO2@$45 + 1×5lbCO2@$4 + 4×10lbPQS@$10 + 1×2.5glnK@$99</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×50lbCO2@$20 + 1×50lbCO2@$20 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L79" s="5" t="inlineStr">
-        <is>
-          <t>Extra en COT: +1×2.5glnK(@$99) | Falta en COT: -1×2.5GLSTIPO K</t>
-        </is>
-      </c>
+      <c r="F79" s="2" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1461 R003 CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>R003 - 9 DE OCTUBRE</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="F80" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 2×5lbCO2@$4 + 4×10lbPQS@$10 + 1×2.5glnK@$99</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L80" s="5" t="inlineStr">
-        <is>
-          <t>Extra en COT: +1×2.5glnK(@$99) | Falta en COT: -1×2.5GLSTIPO K</t>
-        </is>
-      </c>
+      <c r="F80" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -4317,15 +4197,15 @@
         <v>90</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>102</v>
+        <v>418.7</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO</t>
+          <t>RECARGA</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>11.76</v>
+        <v>78.5</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
@@ -4339,12 +4219,12 @@
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>1×75lbCO2@$30 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×2.5GLSTIPO K@$8</t>
+          <t>1×75lbCO2@$68 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×2.5GLSTIPO K@$99 + 1×2.5GLSTIPO K@$99 + 1×MOVILIZACIÓN@$19</t>
         </is>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>-18 ext en COT vs DB (0 vs 18) | ⚠ suma líneas COT=$0.00 ≠ subtotal=$90.00 | Falta en COT: -1×75lbCO2, -1×10lbCO2, -4×5lbCO2, -1×20lbPQS, -9×10lbPQS, -2×2.5GLSTIPO K</t>
+          <t>-19 ext en COT vs DB (0 vs 19) | ⚠ suma líneas COT=$0.00 ≠ subtotal=$90.00 | Falta en COT: -1×75lbCO2, -1×10lbCO2, -4×5lbCO2, -1×20lbPQS, -9×10lbPQS, -2×2.5GLSTIPO K, -1×MOVILIZACIÓN</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4749,7 @@
         <v>76</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
@@ -4877,7 +4757,7 @@
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>137.5</v>
+        <v>5.56</v>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
@@ -4891,12 +4771,12 @@
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×MOVILIZACIÓN@$40</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>+1 ext en COT vs DB (5 vs 4) | ⚠ suma líneas COT=$36.00 ≠ subtotal=$76.00 | Extra en COT: +1×10lbCO2(@$4)</t>
+          <t>⚠ suma líneas COT=$36.00 ≠ subtotal=$76.00 | Extra en COT: +1×10lbCO2(@$4) | Falta en COT: -1×MOVILIZACIÓN</t>
         </is>
       </c>
     </row>
@@ -5069,60 +4949,48 @@
       <c r="L98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1569 KFCK93 QUEVEDO CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>K93</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>K093 - QUEVEDO</t>
         </is>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="F99" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×10lbPQS@$4 + 2×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×20lbPQS@$8 + 1×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="L99" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$44.00 ≠ subtotal=$79.00</t>
-        </is>
-      </c>
+      <c r="F99" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5205,60 +5073,48 @@
       <c r="L101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1564 CJNC20 LIBERTAD.xlsx</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>J20</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>J020 - CAJUN PENINSULA</t>
         </is>
       </c>
-      <c r="E102" s="4" t="n">
+      <c r="E102" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="F102" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="n">
-        <v>178.95</v>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$38.00 ≠ subtotal=$106.00</t>
-        </is>
-      </c>
+      <c r="F102" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -5341,60 +5197,48 @@
       <c r="L104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1565 KFCK78 DAULE.xlsx</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>K78</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>K078 - SHOPPING DAULE</t>
         </is>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="F105" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J105" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L105" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$30.00 ≠ subtotal=$55.00</t>
-        </is>
-      </c>
+      <c r="F105" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5821,60 +5665,48 @@
       <c r="L115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1573 KFCK149 VENTANAS.xlsx</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>K149</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>K149 - PETROCOMERIAL VENTANAS</t>
         </is>
       </c>
-      <c r="E116" s="4" t="n">
+      <c r="E116" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="F116" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J116" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K116" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L116" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$50.00 ≠ subtotal=$85.00 | Extra en COT: +1×2.5glnK(@$8) | Falta en COT: -1×2.5GLSTIPO K</t>
-        </is>
-      </c>
+      <c r="F116" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="3" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -5989,60 +5821,48 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1570 KFCK106 SHOPPING QUEVEDO.xlsx</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>K106</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>K106 - SHOPPING QUEVEDO</t>
         </is>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="F119" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J119" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2</t>
-        </is>
-      </c>
-      <c r="L119" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$42.00 ≠ subtotal=$77.00</t>
-        </is>
-      </c>
+      <c r="F119" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -6081,116 +5901,92 @@
       <c r="L120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1572 M32 SHOPPING QUEVEDO.xlsx</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>M32</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>M032 - SHOPPING QUEVEDO</t>
         </is>
       </c>
-      <c r="E121" s="4" t="n">
+      <c r="E121" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="F121" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="n">
-        <v>92.11</v>
-      </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J121" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$38.00 ≠ subtotal=$73.00</t>
-        </is>
-      </c>
+      <c r="F121" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1606 M39 BABAHOYO.xlsx</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>M39</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>M039 - PASEO SHOPPING BABAHOYO</t>
         </is>
       </c>
-      <c r="E122" s="4" t="n">
+      <c r="E122" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="F122" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="I122" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J122" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K122" s="5" t="inlineStr">
-        <is>
-          <t>1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L122" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$28.00 ≠ subtotal=$52.00</t>
-        </is>
-      </c>
+      <c r="F122" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -6229,60 +6025,48 @@
       <c r="L123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1603 KFCK53 SHOPPING BABAHOYO.xlsx</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>K53</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>K053 - PASEO SHOPPING BABAHOYO</t>
         </is>
       </c>
-      <c r="E124" s="4" t="n">
+      <c r="E124" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="F124" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="I124" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J124" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L124" s="5" t="inlineStr">
-        <is>
-          <t>⚠ suma líneas COT=$28.00 ≠ subtotal=$52.00</t>
-        </is>
-      </c>
+      <c r="F124" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7691,7 +7475,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
@@ -7701,7 +7485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -7809,10 +7593,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -7859,10 +7643,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -7884,10 +7668,10 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -7934,10 +7718,10 @@
         <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7959,10 +7743,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/REVISION_COTIZACIONES_2026.xlsx
+++ b/REVISION_COTIZACIONES_2026.xlsx
@@ -35,7 +35,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B942"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,10 +94,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -445,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -530,6 +574,7139 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1281 M58 PEÑAS.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>M58</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>M058 - LAS PENAS</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1269 KFCK87 TERMINAL GYE.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>K87</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>K087 - TERMINAL TERRESTRE GYQ</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1280 KFCK85 SHELL CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>K85</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>K085 - MOBIL CEIBOS</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1282 KFCK79 BABAHOYO.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>K79</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>K079 - BABAHOYO</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>75.97</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>1×??@$48 + 1×10lbPQS@$34  [+MOVIL:$40.00 — MOVILIZACION (GYE - BABAHOYO)]</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4  [+MOVIL:$40.00 — GYE-BABAHOYO 75KM]</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$81.80 vs DB=$32.00 (neto +$49.80) | Cantidad: 2 ext en COT vs 4 en DB | COT tiene +1×?? que no está en DB (precio $48/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($20/ext) | DB tiene +1×10lbCO2 que no aparece en COT ($4/ext) | DB tiene +1×10lbPQS que no aparece en COT ($4/ext)</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×?? a BD? ($48/ext) | ¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1262 KFCK02 9 DE OCT Y CHIMBORAZO.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>K002 - 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1275 M35 GARZOTA.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>M35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>M035 - GARZOTA</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1270 KFCK95 PASEO SHOPPING VIA A DAULE.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>K95</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>K095 - PASEO SHOP KM 9 VIA DAULE</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1262 KFCK25 MOBIL DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>K25</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>K025 - MOBIL DURAN</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbCO2@$4 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$42.00 (neto +$4.00) | Cantidad: 5 ext en COT vs 4 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext)</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1273 KFCK154 PASCUALES.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>K154</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>K154 - PASCUALES</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 1×20lbPQS@$8 + 3×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$54.00 vs DB=$52.00 (neto +$2.00) | Cantidad: 9 ext en COT vs 8 en DB | COT tiene +1×5lbCO2 que no está en DB (precio $2/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×5lbCO2 a BD? ($2/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1266 KFCK74 PARQUE CALIFORNIA.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>K74</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>K074 - CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1268 KFCK77 RIOCENTRO CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>K77</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>K077 - RIO CENTRO LOS CEIBOS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1272 KFCK153 LIGA CANTONAL DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>K153</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>K153 - LIGA CANTONAL DURAN</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1277 T032 TERMINAL GYE.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>T032 - TERMINAL</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1263 KFCK34 KM4,5 VIA A DAULE.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>K34</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>K034 - VIA DAULE</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1267 KFCK76 PARQUE CENTENARIO.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>K76</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>K076 - PARQUE CENTENARIO</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$36.00 vs DB=$40.00 (neto $-4.00) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbPQS que no aparece en COT ($4/ext)</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1279 KFCK63 RIOCENTRO SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>K063 - RIO CENTRO SUR</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1274 M31 RIOCENTRO NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>M031 - RIO CENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1276 CJNC01 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>J001 - MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1263 KFCK29 MALECON Y OLMEDO.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>K29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>K029 - MALECON 2000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1278 I003 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>I003 - MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1260 JV55 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>V55</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>V055 - MALL DEL SOL ZONA GASTRO</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1271 KFCK105 RIOCENTRO NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>K105</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>K105 - HIPER MARKET</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$4 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$44.00 (neto +$2.00) | 1×5lbCO2: precio COT=$4 vs DB=$2/ext</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>¿Actualizar precio 5lbCO2 en BD: $2→$4/ext?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1264 KFCK37 AKI DOMINGO COMIN.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>K37</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>K037 - DOMINGO COMIN</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1265 KFCK55 MOBIL CORDOVA.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>K55</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>K055 - MOBIL CORDOVA</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1290 KFCK07 ALBORADA.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>K007 - ALBORADA</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1291 KFCK45 BOYACA.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>K45</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>K045 - BOYACA</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 3×20lbPQS@$8 + 6×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$70.00 vs DB=$66.00 (neto +$4.00) | Cantidad: 11 ext en COT vs 10 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext)</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1295 KFCK148 TERMINAL MACHALA.xlsx</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>K148</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>K148 - TERMINAL TERRESTRE MACHALA</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1299 BS31 RIOC CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>BS31</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>CN31 - RIOCENTRO CEIBOS</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1300 BS38 RIOC CEIBOS2.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>BS38</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>BS38 - CEIBOS BASKIN</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1301 ESPE06 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ESPE6</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1302 ESPE10 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>ESPE10</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1303 ESPE26 RIOC PUNTILLA.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>ESPE26</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1304 V015 RIOC CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>V15</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>V015 - CEIBOS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1305 V021 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>V21</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>V021 - MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1306 CJNC02 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>J002 - SAN MARINO</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1307 ILCI02 RIOC. CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>ILCI2</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1308 JV75 PASEO SHOPPING MACHALA.xlsx</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>V75</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>V075 - PASEO SHOPPING MACHALA</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1293 KFCK90 MACHALA CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>K90</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>K090 - MACHALA CENTRO</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1294 KFCK91PASEO SHOPP MACHALA.xlsx</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>K91</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>K091 - MACHALA RIO CENTRO</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1292 KFCK65 MILAGRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>K65</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>K065 - MILAGRO</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1298 BS09 RIOC SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>BS9</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>BS09 - RIO CENTRO SUR</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1309 JV79 MILAGRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>V79</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>V079 - MILAGRO</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1296 AMCA37 EL DORADO.xlsx</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>AMCA37</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1297 BS04 CN04 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>BS04 - MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1352 GUSG49 DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>GUSG49</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1355 M47 DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>M47</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>M047 - PASEO SHOPPING DURAN</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1356 M57 ALBORADA.xlsx</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>M57</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>M057 - ALBORADA</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1357 ILCI05 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>ILCI5</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1358 KFCK75 MOBIL KENNEDY.xlsx</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>K75</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>K075 - MOBIL KENNEDY</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 2×10lbPQS@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$40.00 vs DB=$32.00 (neto +$8.00) | Cantidad: 5 ext en COT vs 4 en DB | COT tiene +1×20lbPQS que no está en DB (precio $8/ext)</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×20lbPQS a BD? ($8/ext)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1359 CN37 EL DORADO.xlsx</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>BS37</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>BS37 - DORADO</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1361 KFCK176 SUPERCINES ORELLANA.xlsx</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>K176</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>K176 - SUPERCINES</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1362 KFCK169 PLAZA PACIFICO.xlsx</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>K169</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>K169 - PLAZA PACIFICO DAULE</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1363 JV66 PLAZA PACIFICO.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>V66</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>V066 PLAZA PACIFICO DAULE</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1350 KFCK94 PASEO SHOPPING DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>K94</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>K094 - OUTLET DURAN</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$30.00 vs DB=$32.00 (neto $-2.00) | Cantidad: 4 ext en COT vs 5 en DB | DB tiene +1×5lbCO2 que no aparece en COT ($2/ext)</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×5lbCO2 de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1353 M11 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>M011 - MALL SUR</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×10lbPQS@$4 + 1×5lbCO2@$2 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$48.00 vs DB=$38.00 (neto +$10.00) | Cantidad: 5 ext en COT vs 3 en DB | COT tiene +1×5lbCO2 que no está en DB (precio $2/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext)</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×5lbCO2 a BD? ($2/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1351 KFCK145 AKI SAN EDUARDO.xlsx</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>K145</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>K145 - SUPER AKI SAN EDUARDO</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 2×10lbPQS@$4 + 1×2.5glnK@$8 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$50.00 vs DB=$42.00 (neto +$8.00) | Cantidad: 8 ext en COT vs 7 en DB | COT tiene +1×20lbPQS que no está en DB (precio $8/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×20lbPQS a BD? ($8/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1354 M37 CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>M37</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>M037 - 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 6×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$58.00 vs DB=$48.00 (neto +$10.00) | COT tiene +1×75lbCO2 que no está en DB (precio $30/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($20/ext)</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×75lbCO2 a BD? ($30/ext) | ¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1360 M46 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>M46</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>M046 - SAN MARINO</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1404 ILCI12 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>ILCI12</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="n"/>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1405 JV57 CORAL SAMBORONDON.xlsx</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>V57</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>V057 - CORAL SAMBORONDON</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1403 GUSG45 TUNGURAHUA.xlsx</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>GUSG45</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="n"/>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1402 KFCK161 MALL DEL RIO GYE.xlsx</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>K161</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>K161 - MALL DEL RIO GYE</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1401 KFCK82 PLAYAS.xlsx</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>K82</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>K082 - SHOPPING PLAYAS</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1406 JV87 DAULE.xlsx</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>V87</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>V087 - PASEO SHOPPING DAULE</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1400 KFCK124 GRAN AKI LOJA.xlsx</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>K124</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>K124 - GRAN AKI</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>3×10lbCO2@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 1×10lbCO2@$4 + 1×10lbCO2@$4 + 1×20lbPQS@$8 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$20.00 vs DB=$28.00 (neto $-8.00) | Cantidad: 4 ext en COT vs 5 en DB | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1407 KFCK88 HIPER VIA A DAULE.xlsx</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>K88</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>K088 - HIPERMARKET VIA DAULE</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$34</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$33.80 vs DB=$97.70 (neto $-63.90) | Cantidad: 1 ext en COT vs 7 en DB | DB tiene +1×50lbCO2 que no aparece en COT ($45/ext) | DB tiene +1×20lbPQS que no aparece en COT ($20/ext) | DB tiene +3×5lbCO2 que no aparece en COT ($4/ext) | DB tiene +1×10lbPQS que no aparece en COT ($10/ext)</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 3×5lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1456 BS16 RIOC PUNTILLA.xlsx</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>BS16</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>BS16 - PUNTILLA</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1455 AMCA24 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>AMCA24</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr"/>
+      <c r="E69" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F69" s="6" t="n"/>
+      <c r="G69" s="6" t="inlineStr"/>
+      <c r="H69" s="6" t="n"/>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1450 KFCK03 PLAZA QUIL.xlsx</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>K003 - PLAZA QUIL</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1459 M56 AEROPUERTO.xlsx</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>M56</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>M056 - AEROPUERTO GYE</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1458 JV48 MALL DEL RIO GYE.xlsx</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>V48</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>V048 - MALL DEL RIO GYE</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1457 BS20 RIOCENTRO NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>BS20</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>BS20 - RIO CENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1451 KFCK59 MALL DEL SUR PB.xlsx</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>K59</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>K059 - MALL DEL SUR P/B</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1453 GUSG50 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>GUSG50</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr"/>
+      <c r="E75" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1454 AMCA06 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>AMCA6</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr"/>
+      <c r="E76" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr"/>
+      <c r="L76" s="7" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1460 R004 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>R004 - SAN MARINO</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>2×50lbCO2@$20 + 3×5lbCO2@$2 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$62.00 vs DB=$72.00 (neto $-10.00) | COT tiene +1×50lbCO2 que no está en DB (precio $20/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×75lbCO2 que no aparece en COT ($30/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×50lbCO2 a BD? ($20/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1463 R010 ORELLANA.xlsx</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>R010 - FRANCISCO DE ORELLANA</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1462 R008 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>R008 - MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1461 R003 CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>R003 - 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1452 KFCK96 PORTETE.xlsx</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>K96</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>K096 - PORTETE</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>2×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×20lbPQS@$8 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$76.00 vs DB=$86.00 (neto $-10.00) | COT tiene +1×5lbCO2 que no está en DB (precio $2/ext) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | DB tiene +2×20lbPQS que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×5lbCO2 a BD? ($2/ext) | ¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿RETIRAR 2×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1464 R010 ORELLANA.xlsx</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>R010 - FRANCISCO DE ORELLANA</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>(sin líneas ext)</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×2.5GLSTIPO K@$99 + 1×2.5GLSTIPO K@$99  [+MOVIL:$18.80 — GYE-ORELLANA]</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Viáticos COT=$0.00 vs DB=$18.80 | (viáticos no detectados en líneas COT, posible formato) | Extintores COT=$0.00 vs DB=$399.90 (neto $-399.90) | Cantidad: 0 ext en COT vs 18 en DB | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | DB tiene +2×2.5GLSTIPO K que no aparece en COT ($99/ext) | DB tiene +1×20lbPQS que no aparece en COT ($20/ext) | DB tiene +4×5lbCO2 que no aparece en COT ($4/ext) | DB tiene +9×10lbPQS que no aparece en COT ($10/ext) | DB tiene +1×75lbCO2 que no aparece en COT ($68/ext)</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 4×5lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 9×10lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1501 ILCI04 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>ILCI4</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr"/>
+      <c r="E83" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F83" s="6" t="n"/>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="n"/>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1511 F003 DOLCE INCONTRO  AEROPUERTO.xlsx</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>F003 - DOLCE INCONTRO AERGYE</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 3×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$42.00 vs DB=$38.00 (neto +$4.00) | Cantidad: 6 ext en COT vs 5 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1507 CJNC08 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>J008 - TERMINAL</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$28.00 vs DB=$38.00 (neto $-10.00) | COT tiene +1×50lbCO2 que no está en DB (precio $20/ext) | DB tiene +1×75lbCO2 que no aparece en COT ($30/ext)</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×50lbCO2 a BD? ($20/ext) | ¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1510 CN35 RIOCENTRO NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>BS35</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>CN35 - RIO CENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1502 KFCK115 ENTRADA DE LA 8.xlsx</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>K115</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>K115 - ENTRADA DE LA 8</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1512 KFCK83 MUCHO LOTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>K83</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>K083 - MUCHO LOTE</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 2×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×20lbPQS@$8 + 1×75lbCO2@$30</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$54.00 vs DB=$46.00 (neto +$8.00) | Cantidad: 6 ext en COT vs 5 en DB | COT tiene +1×20lbPQS que no está en DB (precio $8/ext)</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×20lbPQS a BD? ($8/ext)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1508 T043 MALL EL FORTIN.xlsx</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>T43</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>T043 - MALL EL FORTIN</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1509 CN34 RIOCENTRO SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>BS34</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>CN34 - RIO CENTRO SUR CINNABON TO GO</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1504 GUSG52 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>GUSG52</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr"/>
+      <c r="E91" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F91" s="6" t="n"/>
+      <c r="G91" s="6" t="inlineStr"/>
+      <c r="H91" s="6" t="n"/>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1503 GUSG48 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>GUSG48</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr"/>
+      <c r="E92" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F92" s="6" t="n"/>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="n"/>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1505 M14 RIOCENTRO SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>M014 - RIOCENTRO SUR</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr"/>
+      <c r="M93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1500 KFCK79 MALECON BABAHOYO.xlsx</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>K79</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>K079 - BABAHOYO</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 2×10lbPQS@$4  [+MOVIL:$40.00 — MOVILZIACION GYE - BABAHOYO(75KM)]</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4  [+MOVIL:$40.00 — GYE-BABAHOYO 75KM]</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$36.00 vs DB=$32.00 (neto +$4.00) | Cantidad: 5 ext en COT vs 4 en DB | COT tiene +1×10lbCO2 que no está en DB (precio $4/ext)</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbCO2 a BD? ($4/ext)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1506 M28 VILLAGE PLAZA.xlsx</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>M28</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>M028 - VILLAGE</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
+      <c r="M95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1567 CJNC29 MALL DEL NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>J29</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>J029 - CAJUN MALL DEL NORTE</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr"/>
+      <c r="K96" s="3" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr"/>
+      <c r="M96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1562 DOLCEI02 RIOC CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>DOLCEI2</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr"/>
+      <c r="E97" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F97" s="6" t="n"/>
+      <c r="G97" s="6" t="inlineStr"/>
+      <c r="H97" s="6" t="n"/>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr"/>
+      <c r="L97" s="7" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1554 CJNC21 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>J21</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>J021 - MALL DEL SUR</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr"/>
+      <c r="M98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1569 KFCK93 QUEVEDO CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>K93</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>K093 - QUEVEDO</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
+      <c r="M99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1561 DI01 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>DI1</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>DI01 - DOLCE INCONTRO MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr"/>
+      <c r="M100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1563 DOLCEI03 RIOC ENTRE RIOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>DOLCEI3</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr"/>
+      <c r="E101" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F101" s="6" t="n"/>
+      <c r="G101" s="6" t="inlineStr"/>
+      <c r="H101" s="6" t="n"/>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1564 CJNC20 LIBERTAD.xlsx</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>J20</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>J020 - CAJUN PENINSULA</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr"/>
+      <c r="M102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1552 GUSG47 ALBORADA.xlsx</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>GUSG47</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr"/>
+      <c r="E103" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="F103" s="6" t="n"/>
+      <c r="G103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="n"/>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$30 + 1×10lbCO2@$4 + 1×20lbPQS@$8 + 4×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr"/>
+      <c r="L103" s="7" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1566 KFCK172 MALL DEL NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>K172</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>K172 - MALL DEL NORTE</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr"/>
+      <c r="M104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1565 KFCK78 DAULE.xlsx</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>K78</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>K078 - SHOPPING DAULE</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr"/>
+      <c r="M105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1555 CJNC06 RIOCENTRO ENTRE RIOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>J006 - CAJUN PUNTILLA</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr"/>
+      <c r="M106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1568 M62 MALL DEL NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>M62</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>M062 - MN MALL DEL NORTE GY</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr"/>
+      <c r="K107" s="3" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1550 KFCK92 FORTIN.xlsx</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>K92</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>K092 - EL FORTIN</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="3" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr"/>
+      <c r="M108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1559 JV03 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>V003 - SAN MARINO</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="3" t="inlineStr"/>
+      <c r="L109" s="3" t="inlineStr"/>
+      <c r="M109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1560 JV16 POLICENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>V16</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>V016 - POLICENTRO</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr"/>
+      <c r="M110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1551 KFCK165 PLAZA TIA DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>K165</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>K165 - PLAZA TIA DURAN</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="3" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1553 KFCK58 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>K58</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>K058 - MALL DEL SUR PLANTA ALTA</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr"/>
+      <c r="M112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1558 JV05 URDESA.xlsx</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>V005 - URDESA</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr"/>
+      <c r="K113" s="3" t="inlineStr"/>
+      <c r="L113" s="3" t="inlineStr"/>
+      <c r="M113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1556 AMCA07 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>AMCA7</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr"/>
+      <c r="E114" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F114" s="6" t="n"/>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="6" t="n"/>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×20lbPQS@$8 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K114" s="7" t="inlineStr"/>
+      <c r="L114" s="7" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1557 AMCA20 VILLAGE PLAZA.xlsx</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>AMCA20</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr"/>
+      <c r="E115" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F115" s="6" t="n"/>
+      <c r="G115" s="6" t="inlineStr"/>
+      <c r="H115" s="6" t="n"/>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K115" s="7" t="inlineStr"/>
+      <c r="L115" s="7" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1573 KFCK149 VENTANAS.xlsx</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>K149</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>K149 - PETROCOMERIAL VENTANAS</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="3" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr"/>
+      <c r="M116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1574 KFCK162 SHELL PASCUALES.xlsx</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>K162</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>K162 - DAULE ESTACION</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 1×10lbPQS@$4 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$50.00 (neto $-4.00) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×20lbPQS que no aparece en COT ($8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1575 KFCK171 SHELL ABUDHABI.xlsx</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>K171</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>K171 - SHELL ABU DABI</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×20lbPQS@$8 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$44.00 vs DB=$40.00 (neto +$4.00) | COT tiene +1×10lbCO2 que no está en DB (precio $4/ext) | COT tiene +1×20lbPQS que no está en DB (precio $8/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +2×10lbPQS que no aparece en COT ($4/ext)</t>
+        </is>
+      </c>
+      <c r="M118" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbCO2 a BD? ($4/ext) | ¿AGREGAR 1×20lbPQS a BD? ($8/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1570 KFCK106 SHOPPING QUEVEDO.xlsx</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>K106</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>K106 - SHOPPING QUEVEDO</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr"/>
+      <c r="M119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1571 GUSG51 SHOPPING QUEVEDO.xlsx</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>GUSG51</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr"/>
+      <c r="E120" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="F120" s="6" t="n"/>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="n"/>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×10lbPQS@$4  [+MOVIL:$35.00 — MOVILIZACION (GUAYAQUIL-QUEVEDO)]</t>
+        </is>
+      </c>
+      <c r="K120" s="7" t="inlineStr"/>
+      <c r="L120" s="7" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1572 M32 SHOPPING QUEVEDO.xlsx</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>M32</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>M032 - SHOPPING QUEVEDO</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr"/>
+      <c r="M121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1606 M39 BABAHOYO.xlsx</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>M39</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>M039 - PASEO SHOPPING BABAHOYO</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr"/>
+      <c r="M122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1614 ESPE22 AEROPUERTO ARRIBO NAC.xlsx</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>ESPE22</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr"/>
+      <c r="E123" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F123" s="6" t="n"/>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="6" t="n"/>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 2×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K123" s="7" t="inlineStr"/>
+      <c r="L123" s="7" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1603 KFCK53 SHOPPING BABAHOYO.xlsx</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>K53</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>K053 - PASEO SHOPPING BABAHOYO</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr"/>
+      <c r="M124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1616 CN26 AEROPUERTO PREEMB.xlsx</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>BS26</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>CN26 - PREEMB INTER GYE</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr"/>
+      <c r="K125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr"/>
+      <c r="M125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1604 M10 MALECON Y SUCRE.xlsx</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>M010 - MALECON</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr"/>
+      <c r="M126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1601 KFCK12 RIOCENTRO PUNTILLA.xlsx</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>K012 - RIO CENTRO</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="3" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr"/>
+      <c r="M127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1605 M21 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>M021 - TERMINAL TER GYQ.</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="3" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr"/>
+      <c r="M128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1607 M43 FORTIN.xlsx</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>M43</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>M043 - EL FORTIN</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr"/>
+      <c r="K129" s="3" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr"/>
+      <c r="M129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1615 CA03 DUPORT AEROPUERTO ARRIBO NAC.xlsx</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>CA3</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>CA03 - CAFE DUPORT HALL PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr"/>
+      <c r="M130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1609 AMCA19 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>AMCA19</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr"/>
+      <c r="E131" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F131" s="6" t="n"/>
+      <c r="G131" s="6" t="inlineStr"/>
+      <c r="H131" s="6" t="n"/>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr"/>
+      <c r="L131" s="7" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1611 DI04 URDESA.xlsx</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>DI4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>DI04 - DOLCE INCONTRO URDESA</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="3" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr"/>
+      <c r="M132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1612 CA01 ASTORIA.xlsx</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>CA1</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>CA01 - CAFE ASTORIA SALIDA INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr"/>
+      <c r="M133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1613 CA02 ASTORIA.xlsx</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>CA2</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>CA02 - CAFE ASTORIA PREEMBARQUE INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr"/>
+      <c r="M134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1602 KFCK52 PEÑAS.xlsx</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>K52</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>K052 - LAS PEÃ????AS</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr"/>
+      <c r="M135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1608 CJNC05 RIOCENTRO CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>J005 - CAJUN CEIBOS</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="3" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr"/>
+      <c r="M136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1600 KFCK21 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>K21</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>K021 - MALL EL SOL</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="3" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr"/>
+      <c r="M137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1610 ESPE07 URDESA.xlsx</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>ESPE7</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr"/>
+      <c r="E138" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F138" s="6" t="n"/>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="6" t="n"/>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>2×5lbCO2@$2 + 4×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K138" s="7" t="inlineStr"/>
+      <c r="L138" s="7" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1650 KFCK129 EXCLUSAS.xlsx</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>K129</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>K129 - LLEVAR 5 ESQUINAS</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="3" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr"/>
+      <c r="M139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1651 AMCA33 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>AMCA33</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr"/>
+      <c r="E140" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F140" s="6" t="n"/>
+      <c r="G140" s="6" t="inlineStr"/>
+      <c r="H140" s="6" t="n"/>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K140" s="7" t="inlineStr"/>
+      <c r="L140" s="7" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1652 BS22 POLICENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>BS22</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>BS22 - POLICENTRO</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr"/>
+      <c r="K141" s="3" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr"/>
+      <c r="M141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1653 ESPE31 POLICENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>ESPE31</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr"/>
+      <c r="E142" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F142" s="6" t="n"/>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="6" t="n"/>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K142" s="7" t="inlineStr"/>
+      <c r="L142" s="7" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1654 V080 AGORA.xlsx</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>V80</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>V080 - AGORA GYE</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr"/>
+      <c r="K143" s="3" t="inlineStr"/>
+      <c r="L143" s="3" t="inlineStr"/>
+      <c r="M143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1213 KFC OFICINAS CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>KFC</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr"/>
+      <c r="E144" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="F144" s="6" t="n"/>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="6" t="n"/>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 4×5lbCO2@$2 + 12×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr"/>
+      <c r="L144" s="7" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>COTIZACION1217 M33 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>M33</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>M033 - CITY MALL</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
+        </is>
+      </c>
+      <c r="M145" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $63.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>COTIZACION1218 CJNC11 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>J011 - CITY MALL</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K146" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L146" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
+        </is>
+      </c>
+      <c r="M146" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $63.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1219 ESPE09 RIOCENTRO CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>ESPE9</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr"/>
+      <c r="E147" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F147" s="6" t="n"/>
+      <c r="G147" s="6" t="inlineStr"/>
+      <c r="H147" s="6" t="n"/>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K147" s="7" t="inlineStr"/>
+      <c r="L147" s="7" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1220 ESPE30 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>ESPE30</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr"/>
+      <c r="E148" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F148" s="6" t="n"/>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="6" t="n"/>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J148" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K148" s="7" t="inlineStr"/>
+      <c r="L148" s="7" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>COTIZACION1221 M61 PORTETE.xlsx</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>M61</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="inlineStr">
+        <is>
+          <t>M061 - PORTETE</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="F149" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="I149" s="8" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 6×10lbPQS@$4 + 2×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K149" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20</t>
+        </is>
+      </c>
+      <c r="L149" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($64.00). Debería ser RECARGA ($152.00). | Extintores COT=$64.00 vs DB=$152.00 (neto $-88.00) | 1×10lbCO2: precio COT=$4 vs DB=$9/ext | 2×20lbPQS: precio COT=$8 vs DB=$20/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 6×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
+        </is>
+      </c>
+      <c r="M149" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $152.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>COTIZACION1222 KFCK109 CITY MALL PA.xlsx</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>K109</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>K109 - CITY MALL PA</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="F150" s="8" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>1×50lb?@$20 + 1×10lbCO2@$4 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K150" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L150" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($32.00). Debería ser RECARGA ($72.80). | Extintores COT=$32.00 vs DB=$72.80 (neto $-40.80) | COT tiene +1×50lb? que no está en DB (precio $20/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($45/ext) | 1×10lbCO2: precio COT=$4 vs DB=$9/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
+        </is>
+      </c>
+      <c r="M150" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $72.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1214 KFCK88 HIPER VIA A DAULE.xlsx</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>K88</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>K088 - HIPERMARKET VIA DAULE</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 3×10lbPQS@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$97.70 (neto $-51.70) | Cantidad: 8 ext en COT vs 7 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | 1×20lbPQS: precio COT=$8 vs DB=$20/ext | 3×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext? | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext?</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1215 KFCK110 CITY MALL PB.xlsx</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>K110</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>K110 - CITY MALL PB</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×20lbPQS@$8 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbCO2@$9 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$50.00 vs DB=$124.70 (neto $-74.70) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | 1×75lbCO2: precio COT=$30 vs DB=$68/ext | 1×20lbPQS: precio COT=$8 vs DB=$20/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 2×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
+        </is>
+      </c>
+      <c r="M152" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿Actualizar precio 75lbCO2 en BD: $68→$30/ext? | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext? | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 10lbPQS en BD: $10→$4/ext?</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>COTIZACION1216 KFCK117 SEDALANA.xlsx</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>K117</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>K117 - 29 Y SEDALANA</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="F153" s="8" t="n">
+        <v>241.2</v>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="I153" s="8" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>3×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 5×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L153" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($104.00). Debería ser RECARGA ($241.20). | Extintores COT=$104.00 vs DB=$241.20 (neto $-137.20) | 2×20lbPQS: precio COT=$8 vs DB=$20/ext | 4×5lbCO2: precio COT=$2 vs DB=$4/ext | 3×50lbCO2: precio COT=$20 vs DB=$45/ext | 5×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
+        </is>
+      </c>
+      <c r="M153" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $241.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1212 B001 ARRECIFE AEROPUERTO.xlsx</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>B001 - STATION SPORTS BAR</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>1×20lbCO2@$20 + 3×10lbPQS@$10 + 2×5lbPQS@$5 + 1×50lbCO2@$20</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×20lbCO2@$18 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$78.80 vs DB=$92.40 (neto $-13.60) | Cantidad: 7 ext en COT vs 5 en DB | COT tiene +2×5lbPQS que no está en DB (precio $5/ext) | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 1×20lbCO2: precio COT=$20 vs DB=$18/ext</t>
+        </is>
+      </c>
+      <c r="M154" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 2×5lbPQS a BD? ($5/ext) | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext? | ¿Actualizar precio 20lbCO2 en BD: $18→$20/ext?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -541,7 +7718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -549,7 +7726,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>RESUMEN REVISION COTIZACIONES 2026</t>
         </is>
@@ -567,7 +7744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +7754,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
@@ -587,7 +7764,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +7774,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -607,7 +7784,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -658,6 +7835,256 @@
         <is>
           <t>OTROS</t>
         </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/REVISION_COTIZACIONES_2026.xlsx
+++ b/REVISION_COTIZACIONES_2026.xlsx
@@ -35,7 +35,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,6 +126,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -733,20 +744,16 @@
       <c r="E5" s="4" t="n">
         <v>126.7</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>72</v>
-      </c>
+      <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>75.97</v>
-      </c>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>INCONSISTENCIA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -754,19 +761,15 @@
           <t>1×??@$48 + 1×10lbPQS@$34  [+MOVIL:$40.00 — MOVILIZACION (GYE - BABAHOYO)]</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4  [+MOVIL:$40.00 — GYE-BABAHOYO 75KM]</t>
-        </is>
-      </c>
+      <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Extintores COT=$81.80 vs DB=$32.00 (neto +$49.80) | Cantidad: 2 ext en COT vs 4 en DB | COT tiene +1×?? que no está en DB (precio $48/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($20/ext) | DB tiene +1×10lbCO2 que no aparece en COT ($4/ext) | DB tiene +1×10lbPQS que no aparece en COT ($4/ext)</t>
+          <t>Cotización por venta de extintores / servicio, no mantenimiento</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>¿AGREGAR 1×?? a BD? ($48/ext) | ¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+          <t>Informativo — no afecta la base de datos</t>
         </is>
       </c>
     </row>
@@ -906,126 +909,94 @@
       <c r="M8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1262 KFCK25 MOBIL DURAN.xlsx</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>K25</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>K025 - MOBIL DURAN</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×10lbCO2@$4 + 3×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>1×10lbCO2@$4 + 1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$46.00 vs DB=$42.00 (neto +$4.00) | Cantidad: 5 ext en COT vs 4 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext)</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext)</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1273 KFCK154 PASCUALES.xlsx</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>K154</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>K154 - PASCUALES</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 1×20lbPQS@$8 + 3×10lbPQS@$4 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$54.00 vs DB=$52.00 (neto +$2.00) | Cantidad: 9 ext en COT vs 8 en DB | COT tiene +1×5lbCO2 que no está en DB (precio $2/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×5lbCO2 a BD? ($2/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+      <c r="F10" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1253,61 +1224,61 @@
       <c r="M15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1267 KFCK76 PARQUE CENTENARIO.xlsx</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>K76</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>K076 - PARQUE CENTENARIO</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 3×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Extintores COT=$36.00 vs DB=$40.00 (neto $-4.00) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbPQS que no aparece en COT ($4/ext)</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>¿RETIRAR 1×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
         </is>
@@ -1584,61 +1555,61 @@
       <c r="M22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1271 KFCK105 RIOCENTRO NORTE.xlsx</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>K105</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>K105 - HIPER MARKET</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n">
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>4.55</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>1×75lbCO2@$30 + 1×5lbCO2@$4 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Extintores COT=$46.00 vs DB=$44.00 (neto +$2.00) | 1×5lbCO2: precio COT=$4 vs DB=$2/ext</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>¿Actualizar precio 5lbCO2 en BD: $2→$4/ext?</t>
         </is>
@@ -1780,65 +1751,49 @@
       <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1291 KFCK45 BOYACA.xlsx</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>K45</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>K045 - BOYACA</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F27" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 3×20lbPQS@$8 + 6×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$70.00 vs DB=$66.00 (neto +$4.00) | Cantidad: 11 ext en COT vs 10 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext)</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext)</t>
-        </is>
-      </c>
+      <c r="F27" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1976,115 +1931,115 @@
       <c r="M30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1301 ESPE06 MALL DEL SOL.xlsx</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>ESPE6</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>1×10lbPQS@$4 + 1×5lbCO2@$2</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
-      <c r="M31" s="7" t="inlineStr"/>
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1302 ESPE10 SAN MARINO.xlsx</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>ESPE10</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>2×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
-      <c r="M32" s="7" t="inlineStr"/>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1303 ESPE26 RIOC PUNTILLA.xlsx</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>ESPE26</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×5lbCO2@$2</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
-      <c r="M33" s="7" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2222,41 +2177,41 @@
       <c r="M36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1307 ILCI02 RIOC. CEIBOS.xlsx</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>ILCI2</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr"/>
-      <c r="M37" s="7" t="inlineStr"/>
+      <c r="K37" s="9" t="inlineStr"/>
+      <c r="L37" s="9" t="inlineStr"/>
+      <c r="M37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2529,41 +2484,41 @@
       <c r="M43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1296 AMCA37 EL DORADO.xlsx</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>AMCA37</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="inlineStr"/>
-      <c r="H44" s="6" t="n"/>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-      <c r="M44" s="7" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2611,41 +2566,41 @@
       <c r="M45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1352 GUSG49 DURAN.xlsx</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>GUSG49</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="6" t="n">
+      <c r="D46" s="8" t="inlineStr"/>
+      <c r="E46" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="6" t="n"/>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr"/>
-      <c r="L46" s="7" t="inlineStr"/>
-      <c r="M46" s="7" t="inlineStr"/>
+      <c r="K46" s="9" t="inlineStr"/>
+      <c r="L46" s="9" t="inlineStr"/>
+      <c r="M46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2738,102 +2693,86 @@
       <c r="M48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1357 ILCI05 SAN MARINO.xlsx</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>ILCI5</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="6" t="n">
+      <c r="D49" s="8" t="inlineStr"/>
+      <c r="E49" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="inlineStr"/>
-      <c r="H49" s="6" t="n"/>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×2.5glnK@$8</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr"/>
-      <c r="M49" s="7" t="inlineStr"/>
+      <c r="K49" s="9" t="inlineStr"/>
+      <c r="L49" s="9" t="inlineStr"/>
+      <c r="M49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1358 KFCK75 MOBIL KENNEDY.xlsx</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>K75</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>K075 - MOBIL KENNEDY</t>
         </is>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 2×10lbPQS@$4 + 1×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$40.00 vs DB=$32.00 (neto +$8.00) | Cantidad: 5 ext en COT vs 4 en DB | COT tiene +1×20lbPQS que no está en DB (precio $8/ext)</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×20lbPQS a BD? ($8/ext)</t>
-        </is>
-      </c>
+      <c r="F50" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3016,246 +2955,214 @@
       <c r="M54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1350 KFCK94 PASEO SHOPPING DURAN.xlsx</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>K94</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>K094 - OUTLET DURAN</t>
         </is>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="n">
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="n">
         <v>6.25</v>
       </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>Extintores COT=$30.00 vs DB=$32.00 (neto $-2.00) | Cantidad: 4 ext en COT vs 5 en DB | DB tiene +1×5lbCO2 que no aparece en COT ($2/ext)</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr">
         <is>
           <t>¿RETIRAR 1×5lbCO2 de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1353 M11 MALL DEL SUR.xlsx</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>M011 - MALL SUR</t>
         </is>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="F56" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="F56" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="3" t="inlineStr"/>
+      <c r="L56" s="3" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1351 KFCK145 AKI SAN EDUARDO.xlsx</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>K145</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>K145 - SUPER AKI SAN EDUARDO</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1354 M37 CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>M37</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>M037 - 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 2×10lbPQS@$4 + 1×5lbCO2@$2 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$48.00 vs DB=$38.00 (neto +$10.00) | Cantidad: 5 ext en COT vs 3 en DB | COT tiene +1×5lbCO2 que no está en DB (precio $2/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext)</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×5lbCO2 a BD? ($2/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>COTIZACION1351 KFCK145 AKI SAN EDUARDO.xlsx</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>K145</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>K145 - SUPER AKI SAN EDUARDO</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 2×10lbPQS@$4 + 1×2.5glnK@$8 + 1×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×50lbCO2@$20</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$50.00 vs DB=$42.00 (neto +$8.00) | Cantidad: 8 ext en COT vs 7 en DB | COT tiene +1×20lbPQS que no está en DB (precio $8/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×20lbPQS a BD? ($8/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>COTIZACION1354 M37 CENTRO.xlsx</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>M37</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>M037 - 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 6×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$58.00 vs DB=$48.00 (neto +$10.00) | COT tiene +1×75lbCO2 que no está en DB (precio $30/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($20/ext)</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×75lbCO2 a BD? ($30/ext) | ¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT)</t>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>Extintores COT=$58.00 vs DB=$48.00 (neto +$10.00) | Cantidad: 9 ext en COT vs 8 en DB | COT tiene +1×75lbCO2 que no está en DB (precio $30/ext) | COT tiene +2×10lbPQS que no está en DB (precio $4/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($20/ext)</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×75lbCO2 a BD? ($30/ext) | ¿AGREGAR 2×10lbPQS a BD? ($4/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
@@ -3305,41 +3212,41 @@
       <c r="M59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1404 ILCI12 TERMINAL.xlsx</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>ILCI12</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr"/>
-      <c r="E60" s="6" t="n">
+      <c r="D60" s="8" t="inlineStr"/>
+      <c r="E60" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="6" t="n"/>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="inlineStr"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J60" s="7" t="inlineStr">
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×2.5glnK@$8</t>
         </is>
       </c>
-      <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr"/>
-      <c r="M60" s="7" t="inlineStr"/>
+      <c r="K60" s="9" t="inlineStr"/>
+      <c r="L60" s="9" t="inlineStr"/>
+      <c r="M60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3387,41 +3294,41 @@
       <c r="M61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1403 GUSG45 TUNGURAHUA.xlsx</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>GUSG45</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr"/>
-      <c r="E62" s="6" t="n">
+      <c r="D62" s="8" t="inlineStr"/>
+      <c r="E62" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="6" t="n"/>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="inlineStr"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J62" s="7" t="inlineStr">
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
-      <c r="M62" s="7" t="inlineStr"/>
+      <c r="K62" s="9" t="inlineStr"/>
+      <c r="L62" s="9" t="inlineStr"/>
+      <c r="M62" s="9" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3559,65 +3466,41 @@
       <c r="M65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1400 KFCK124 GRAN AKI LOJA.xlsx</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>K124</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>K124 - GRAN AKI</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="n">
+      <c r="D66" s="8" t="inlineStr"/>
+      <c r="E66" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F66" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>3×10lbCO2@$4 + 1×20lbPQS@$8</t>
         </is>
       </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>1×10lbCO2@$4 + 1×10lbCO2@$4 + 1×10lbCO2@$4 + 1×20lbPQS@$8 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$20.00 vs DB=$28.00 (neto $-8.00) | Cantidad: 4 ext en COT vs 5 en DB | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+      <c r="K66" s="9" t="inlineStr"/>
+      <c r="L66" s="9" t="inlineStr"/>
+      <c r="M66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -3643,20 +3526,16 @@
       <c r="E67" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="F67" s="4" t="n">
-        <v>97.7</v>
-      </c>
+      <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>65.40000000000001</v>
-      </c>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>INCONSISTENCIA</t>
+          <t>VENTA</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -3664,19 +3543,15 @@
           <t>1×10lbPQS@$34</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20</t>
-        </is>
-      </c>
+      <c r="K67" s="5" t="inlineStr"/>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Extintores COT=$33.80 vs DB=$97.70 (neto $-63.90) | Cantidad: 1 ext en COT vs 7 en DB | DB tiene +1×50lbCO2 que no aparece en COT ($45/ext) | DB tiene +1×20lbPQS que no aparece en COT ($20/ext) | DB tiene +3×5lbCO2 que no aparece en COT ($4/ext) | DB tiene +1×10lbPQS que no aparece en COT ($10/ext)</t>
+          <t>Cotización por venta de extintores / servicio, no mantenimiento</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 3×5lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+          <t>Informativo — no afecta la base de datos</t>
         </is>
       </c>
     </row>
@@ -3726,41 +3601,41 @@
       <c r="M68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1455 AMCA24 MALL DEL SUR.xlsx</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>AMCA24</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr"/>
-      <c r="E69" s="6" t="n">
+      <c r="D69" s="8" t="inlineStr"/>
+      <c r="E69" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="inlineStr"/>
-      <c r="H69" s="6" t="n"/>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J69" s="7" t="inlineStr">
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr"/>
-      <c r="L69" s="7" t="inlineStr"/>
-      <c r="M69" s="7" t="inlineStr"/>
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3988,184 +3863,184 @@
       <c r="M74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1453 GUSG50 MALL DEL SUR.xlsx</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>GUSG50</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr"/>
-      <c r="E75" s="6" t="n">
+      <c r="D75" s="8" t="inlineStr"/>
+      <c r="E75" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F75" s="6" t="n"/>
-      <c r="G75" s="6" t="inlineStr"/>
-      <c r="H75" s="6" t="n"/>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="J75" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 2×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K75" s="7" t="inlineStr"/>
-      <c r="L75" s="7" t="inlineStr"/>
-      <c r="M75" s="7" t="inlineStr"/>
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1454 AMCA06 TERMINAL.xlsx</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>AMCA6</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr"/>
-      <c r="E76" s="6" t="n">
+      <c r="D76" s="8" t="inlineStr"/>
+      <c r="E76" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="n"/>
-      <c r="I76" s="6" t="inlineStr">
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="J76" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
         </is>
       </c>
-      <c r="K76" s="7" t="inlineStr"/>
-      <c r="L76" s="7" t="inlineStr"/>
-      <c r="M76" s="7" t="inlineStr"/>
+      <c r="K76" s="9" t="inlineStr"/>
+      <c r="L76" s="9" t="inlineStr"/>
+      <c r="M76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1460 R004 SAN MARINO.xlsx</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>R004 - SAN MARINO</t>
         </is>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="F77" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="F77" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1463 R010 ORELLANA.xlsx</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>R010 - FRANCISCO DE ORELLANA</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>448.1</v>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>2×50lbCO2@$20 + 3×5lbCO2@$2 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×2.5GLSTIPO K@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$62.00 vs DB=$72.00 (neto $-10.00) | COT tiene +1×50lbCO2 que no está en DB (precio $20/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×75lbCO2 que no aparece en COT ($30/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M77" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×50lbCO2 a BD? ($20/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1463 R010 ORELLANA.xlsx</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>R010 - FRANCISCO DE ORELLANA</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>418.7</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>418.7</v>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="inlineStr"/>
-      <c r="K78" s="3" t="inlineStr"/>
-      <c r="L78" s="3" t="inlineStr"/>
-      <c r="M78" s="3" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 2×10lbCO2@$9 + 4×5lbCO2@$4 + 1×20lbPQS@$20 + 10×10lbPQS@$10 + 2×2.5glnK@$99</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbCO2@$9 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×2.5GLSTIPO K@$99 + 1×2.5GLSTIPO K@$99  [+MOVIL:$18.80 — GYE-ORELLANA]</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>Viáticos COT=$0.00 vs DB=$18.80 | (viáticos no detectados en líneas COT, posible formato) | Extintores COT=$418.70 vs DB=$429.30 (neto $-10.60) | COT tiene +1×10lbCO2 que no está en DB (precio $9/ext) | COT tiene +2×2.5glnK que no está en DB (precio $99/ext) | DB tiene +2×2.5GLSTIPO K que no aparece en COT ($99/ext) | DB tiene +1×20lbPQS que no aparece en COT ($20/ext)</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbCO2 a BD? ($9/ext) | ¿AGREGAR 2×2.5glnK a BD? ($99/ext) | ¿RETIRAR 2×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4258,281 +4133,281 @@
       <c r="M80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1452 KFCK96 PORTETE.xlsx</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>K96</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>K096 - PORTETE</t>
         </is>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="F81" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
+      <c r="F81" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>2×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 3×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K81" s="5" t="inlineStr">
-        <is>
-          <t>1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×5lbCO2@$2 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×20lbPQS@$8 + 1×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="L81" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$76.00 vs DB=$86.00 (neto $-10.00) | COT tiene +1×5lbCO2 que no está en DB (precio $2/ext) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | DB tiene +2×20lbPQS que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M81" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×5lbCO2 a BD? ($2/ext) | ¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿RETIRAR 2×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>Extintores COT=$76.00 vs DB=$84.00 (neto $-8.00) | Cantidad: 11 ext en COT vs 12 en DB | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1464 R010 ORELLANA.xlsx</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>R010 - FRANCISCO DE ORELLANA</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="F82" s="4" t="n">
-        <v>418.7</v>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="F82" s="6" t="n">
+        <v>448.1</v>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H82" s="4" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="H82" s="6" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="J82" s="7" t="inlineStr">
         <is>
           <t>(sin líneas ext)</t>
         </is>
       </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$68 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×2.5GLSTIPO K@$99 + 1×2.5GLSTIPO K@$99  [+MOVIL:$18.80 — GYE-ORELLANA]</t>
-        </is>
-      </c>
-      <c r="L82" s="5" t="inlineStr">
-        <is>
-          <t>Viáticos COT=$0.00 vs DB=$18.80 | (viáticos no detectados en líneas COT, posible formato) | Extintores COT=$0.00 vs DB=$399.90 (neto $-399.90) | Cantidad: 0 ext en COT vs 18 en DB | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | DB tiene +2×2.5GLSTIPO K que no aparece en COT ($99/ext) | DB tiene +1×20lbPQS que no aparece en COT ($20/ext) | DB tiene +4×5lbCO2 que no aparece en COT ($4/ext) | DB tiene +9×10lbPQS que no aparece en COT ($10/ext) | DB tiene +1×75lbCO2 que no aparece en COT ($68/ext)</t>
-        </is>
-      </c>
-      <c r="M82" s="5" t="inlineStr">
-        <is>
-          <t>¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 4×5lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 9×10lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT)</t>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbCO2@$9 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×2.5GLSTIPO K@$99 + 1×2.5GLSTIPO K@$99  [+MOVIL:$18.80 — GYE-ORELLANA]</t>
+        </is>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>Viáticos COT=$0.00 vs DB=$18.80 | (viáticos no detectados en líneas COT, posible formato) | Extintores COT=$0.00 vs DB=$429.30 (neto $-429.30) | Cantidad: 0 ext en COT vs 20 en DB | DB tiene +1×75lbCO2 que no aparece en COT ($68/ext) | DB tiene +2×2.5GLSTIPO K que no aparece en COT ($99/ext) | DB tiene +10×10lbPQS que no aparece en COT ($10/ext) | DB tiene +4×5lbCO2 que no aparece en COT ($4/ext) | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | DB tiene +2×20lbPQS que no aparece en COT ($20/ext)</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 10×10lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 4×5lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1501 ILCI04 MALL DEL SUR.xlsx</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>ILCI4</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr"/>
-      <c r="E83" s="6" t="n">
+      <c r="D83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="F83" s="6" t="n"/>
-      <c r="G83" s="6" t="inlineStr"/>
-      <c r="H83" s="6" t="n"/>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J83" s="7" t="inlineStr">
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K83" s="7" t="inlineStr"/>
-      <c r="L83" s="7" t="inlineStr"/>
-      <c r="M83" s="7" t="inlineStr"/>
+      <c r="K83" s="9" t="inlineStr"/>
+      <c r="L83" s="9" t="inlineStr"/>
+      <c r="M83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1511 F003 DOLCE INCONTRO  AEROPUERTO.xlsx</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>F003 - DOLCE INCONTRO AERGYE</t>
         </is>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="n">
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="n">
         <v>10.53</v>
       </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="J84" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 3×10lbPQS@$4 + 1×2.5glnK@$8</t>
         </is>
       </c>
-      <c r="K84" s="5" t="inlineStr">
+      <c r="K84" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$42.00 vs DB=$38.00 (neto +$4.00) | Cantidad: 6 ext en COT vs 5 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M84" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>Extintores COT=$42.00 vs DB=$38.00 (neto +$4.00) | Cantidad: 6 ext en COT vs 5 en DB | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1507 CJNC08 TERMINAL.xlsx</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>J8</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>J008 - TERMINAL</t>
         </is>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="n">
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="n">
         <v>26.32</v>
       </c>
-      <c r="I85" s="4" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="J85" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr">
+      <c r="K85" s="7" t="inlineStr">
         <is>
           <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="L85" s="7" t="inlineStr">
         <is>
           <t>Extintores COT=$28.00 vs DB=$38.00 (neto $-10.00) | COT tiene +1×50lbCO2 que no está en DB (precio $20/ext) | DB tiene +1×75lbCO2 que no aparece en COT ($30/ext)</t>
         </is>
       </c>
-      <c r="M85" s="5" t="inlineStr">
+      <c r="M85" s="7" t="inlineStr">
         <is>
           <t>¿AGREGAR 1×50lbCO2 a BD? ($20/ext) | ¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT)</t>
         </is>
@@ -4629,65 +4504,49 @@
       <c r="M87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1512 KFCK83 MUCHO LOTE.xlsx</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>K83</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>K083 - MUCHO LOTE</t>
         </is>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="F88" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 2×20lbPQS@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="inlineStr">
-        <is>
-          <t>1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×20lbPQS@$8 + 1×75lbCO2@$30</t>
-        </is>
-      </c>
-      <c r="L88" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$54.00 vs DB=$46.00 (neto +$8.00) | Cantidad: 6 ext en COT vs 5 en DB | COT tiene +1×20lbPQS que no está en DB (precio $8/ext)</t>
-        </is>
-      </c>
-      <c r="M88" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×20lbPQS a BD? ($8/ext)</t>
-        </is>
-      </c>
+      <c r="F88" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4780,78 +4639,78 @@
       <c r="M90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1504 GUSG52 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>GUSG52</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr"/>
-      <c r="E91" s="6" t="n">
+      <c r="D91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F91" s="6" t="n"/>
-      <c r="G91" s="6" t="inlineStr"/>
-      <c r="H91" s="6" t="n"/>
-      <c r="I91" s="6" t="inlineStr">
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J91" s="7" t="inlineStr">
+      <c r="J91" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K91" s="7" t="inlineStr"/>
-      <c r="L91" s="7" t="inlineStr"/>
-      <c r="M91" s="7" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1503 GUSG48 TERMINAL.xlsx</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>GUSG48</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr"/>
-      <c r="E92" s="6" t="n">
+      <c r="D92" s="8" t="inlineStr"/>
+      <c r="E92" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="n"/>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J92" s="7" t="inlineStr">
+      <c r="J92" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K92" s="7" t="inlineStr"/>
-      <c r="L92" s="7" t="inlineStr"/>
-      <c r="M92" s="7" t="inlineStr"/>
+      <c r="K92" s="9" t="inlineStr"/>
+      <c r="L92" s="9" t="inlineStr"/>
+      <c r="M92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4899,65 +4758,49 @@
       <c r="M93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>COTIZACION1500 KFCK79 MALECON BABAHOYO.xlsx</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>K79</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>K079 - BABAHOYO</t>
         </is>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="F94" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 2×10lbPQS@$4  [+MOVIL:$40.00 — MOVILZIACION GYE - BABAHOYO(75KM)]</t>
-        </is>
-      </c>
-      <c r="K94" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4  [+MOVIL:$40.00 — GYE-BABAHOYO 75KM]</t>
-        </is>
-      </c>
-      <c r="L94" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$36.00 vs DB=$32.00 (neto +$4.00) | Cantidad: 5 ext en COT vs 4 en DB | COT tiene +1×10lbCO2 que no está en DB (precio $4/ext)</t>
-        </is>
-      </c>
-      <c r="M94" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbCO2 a BD? ($4/ext)</t>
-        </is>
-      </c>
+      <c r="F94" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr"/>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr"/>
+      <c r="M94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5050,41 +4893,41 @@
       <c r="M96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1562 DOLCEI02 RIOC CEIBOS.xlsx</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>DOLCEI2</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr"/>
-      <c r="E97" s="6" t="n">
+      <c r="D97" s="8" t="inlineStr"/>
+      <c r="E97" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F97" s="6" t="n"/>
-      <c r="G97" s="6" t="inlineStr"/>
-      <c r="H97" s="6" t="n"/>
-      <c r="I97" s="6" t="inlineStr">
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr">
+      <c r="J97" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K97" s="7" t="inlineStr"/>
-      <c r="L97" s="7" t="inlineStr"/>
-      <c r="M97" s="7" t="inlineStr"/>
+      <c r="K97" s="9" t="inlineStr"/>
+      <c r="L97" s="9" t="inlineStr"/>
+      <c r="M97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5222,41 +5065,41 @@
       <c r="M100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1563 DOLCEI03 RIOC ENTRE RIOS.xlsx</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>DOLCEI3</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr"/>
-      <c r="E101" s="6" t="n">
+      <c r="D101" s="8" t="inlineStr"/>
+      <c r="E101" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F101" s="6" t="n"/>
-      <c r="G101" s="6" t="inlineStr"/>
-      <c r="H101" s="6" t="n"/>
-      <c r="I101" s="6" t="inlineStr">
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J101" s="7" t="inlineStr">
+      <c r="J101" s="9" t="inlineStr">
         <is>
           <t>1×10lbCO2@$4 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K101" s="7" t="inlineStr"/>
-      <c r="L101" s="7" t="inlineStr"/>
-      <c r="M101" s="7" t="inlineStr"/>
+      <c r="K101" s="9" t="inlineStr"/>
+      <c r="L101" s="9" t="inlineStr"/>
+      <c r="M101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5304,41 +5147,41 @@
       <c r="M102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1552 GUSG47 ALBORADA.xlsx</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>GUSG47</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr"/>
-      <c r="E103" s="6" t="n">
+      <c r="D103" s="8" t="inlineStr"/>
+      <c r="E103" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="F103" s="6" t="n"/>
-      <c r="G103" s="6" t="inlineStr"/>
-      <c r="H103" s="6" t="n"/>
-      <c r="I103" s="6" t="inlineStr">
+      <c r="F103" s="8" t="n"/>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="n"/>
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J103" s="7" t="inlineStr">
+      <c r="J103" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$30 + 1×10lbCO2@$4 + 1×20lbPQS@$8 + 4×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K103" s="7" t="inlineStr"/>
-      <c r="L103" s="7" t="inlineStr"/>
-      <c r="M103" s="7" t="inlineStr"/>
+      <c r="K103" s="9" t="inlineStr"/>
+      <c r="L103" s="9" t="inlineStr"/>
+      <c r="M103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5791,78 +5634,78 @@
       <c r="M113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1556 AMCA07 SAN MARINO.xlsx</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>AMCA7</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr"/>
-      <c r="E114" s="6" t="n">
+      <c r="D114" s="8" t="inlineStr"/>
+      <c r="E114" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="F114" s="6" t="n"/>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="6" t="n"/>
-      <c r="I114" s="6" t="inlineStr">
+      <c r="F114" s="8" t="n"/>
+      <c r="G114" s="8" t="inlineStr"/>
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J114" s="7" t="inlineStr">
+      <c r="J114" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×20lbPQS@$8 + 1×2.5glnK@$8</t>
         </is>
       </c>
-      <c r="K114" s="7" t="inlineStr"/>
-      <c r="L114" s="7" t="inlineStr"/>
-      <c r="M114" s="7" t="inlineStr"/>
+      <c r="K114" s="9" t="inlineStr"/>
+      <c r="L114" s="9" t="inlineStr"/>
+      <c r="M114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="inlineStr">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1557 AMCA20 VILLAGE PLAZA.xlsx</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>AMCA20</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr"/>
-      <c r="E115" s="6" t="n">
+      <c r="D115" s="8" t="inlineStr"/>
+      <c r="E115" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F115" s="6" t="n"/>
-      <c r="G115" s="6" t="inlineStr"/>
-      <c r="H115" s="6" t="n"/>
-      <c r="I115" s="6" t="inlineStr">
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J115" s="7" t="inlineStr">
+      <c r="J115" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K115" s="7" t="inlineStr"/>
-      <c r="L115" s="7" t="inlineStr"/>
-      <c r="M115" s="7" t="inlineStr"/>
+      <c r="K115" s="9" t="inlineStr"/>
+      <c r="L115" s="9" t="inlineStr"/>
+      <c r="M115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5910,124 +5753,124 @@
       <c r="M116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1574 KFCK162 SHELL PASCUALES.xlsx</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>K162</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>K162 - DAULE ESTACION</t>
         </is>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F117" s="4" t="n">
+      <c r="F117" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="n">
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I117" s="4" t="inlineStr">
+      <c r="I117" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J117" s="5" t="inlineStr">
+      <c r="J117" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 1×10lbPQS@$4 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
         </is>
       </c>
-      <c r="K117" s="5" t="inlineStr">
+      <c r="K117" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
         </is>
       </c>
-      <c r="L117" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$46.00 vs DB=$50.00 (neto $-4.00) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×20lbPQS que no aparece en COT ($8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M117" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$50.00 (neto $-4.00) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +1×20lbPQS que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M117" s="7" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1575 KFCK171 SHELL ABUDHABI.xlsx</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>K171</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>K171 - SHELL ABU DABI</t>
         </is>
       </c>
-      <c r="E118" s="4" t="n">
+      <c r="E118" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="n">
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="I118" s="4" t="inlineStr">
+      <c r="I118" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J118" s="5" t="inlineStr">
+      <c r="J118" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×20lbPQS@$8 + 1×2.5glnK@$8</t>
         </is>
       </c>
-      <c r="K118" s="5" t="inlineStr">
+      <c r="K118" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
         </is>
       </c>
-      <c r="L118" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$44.00 vs DB=$40.00 (neto +$4.00) | COT tiene +1×10lbCO2 que no está en DB (precio $4/ext) | COT tiene +1×20lbPQS que no está en DB (precio $8/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +2×10lbPQS que no aparece en COT ($4/ext)</t>
-        </is>
-      </c>
-      <c r="M118" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbCO2 a BD? ($4/ext) | ¿AGREGAR 1×20lbPQS a BD? ($8/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>Extintores COT=$44.00 vs DB=$40.00 (neto +$4.00) | COT tiene +1×10lbCO2 que no está en DB (precio $4/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×20lbPQS que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +2×10lbPQS que no aparece en COT ($4/ext)</t>
+        </is>
+      </c>
+      <c r="M118" s="7" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbCO2 a BD? ($4/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×20lbPQS a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
@@ -6077,41 +5920,41 @@
       <c r="M119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1571 GUSG51 SHOPPING QUEVEDO.xlsx</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C120" s="8" t="inlineStr">
         <is>
           <t>GUSG51</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr"/>
-      <c r="E120" s="6" t="n">
+      <c r="D120" s="8" t="inlineStr"/>
+      <c r="E120" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="F120" s="6" t="n"/>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="n"/>
-      <c r="I120" s="6" t="inlineStr">
+      <c r="F120" s="8" t="n"/>
+      <c r="G120" s="8" t="inlineStr"/>
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J120" s="7" t="inlineStr">
+      <c r="J120" s="9" t="inlineStr">
         <is>
           <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×10lbPQS@$4  [+MOVIL:$35.00 — MOVILIZACION (GUAYAQUIL-QUEVEDO)]</t>
         </is>
       </c>
-      <c r="K120" s="7" t="inlineStr"/>
-      <c r="L120" s="7" t="inlineStr"/>
-      <c r="M120" s="7" t="inlineStr"/>
+      <c r="K120" s="9" t="inlineStr"/>
+      <c r="L120" s="9" t="inlineStr"/>
+      <c r="M120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6204,41 +6047,41 @@
       <c r="M122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1614 ESPE22 AEROPUERTO ARRIBO NAC.xlsx</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C123" s="8" t="inlineStr">
         <is>
           <t>ESPE22</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr"/>
-      <c r="E123" s="6" t="n">
+      <c r="D123" s="8" t="inlineStr"/>
+      <c r="E123" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F123" s="6" t="n"/>
-      <c r="G123" s="6" t="inlineStr"/>
-      <c r="H123" s="6" t="n"/>
-      <c r="I123" s="6" t="inlineStr">
+      <c r="F123" s="8" t="n"/>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="8" t="n"/>
+      <c r="I123" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J123" s="7" t="inlineStr">
+      <c r="J123" s="9" t="inlineStr">
         <is>
           <t>1×5lbCO2@$2 + 2×5lbPQS@$2</t>
         </is>
       </c>
-      <c r="K123" s="7" t="inlineStr"/>
-      <c r="L123" s="7" t="inlineStr"/>
-      <c r="M123" s="7" t="inlineStr"/>
+      <c r="K123" s="9" t="inlineStr"/>
+      <c r="L123" s="9" t="inlineStr"/>
+      <c r="M123" s="9" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6556,41 +6399,41 @@
       <c r="M130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="inlineStr">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1609 AMCA19 MALL DEL SOL.xlsx</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
+      <c r="C131" s="8" t="inlineStr">
         <is>
           <t>AMCA19</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr"/>
-      <c r="E131" s="6" t="n">
+      <c r="D131" s="8" t="inlineStr"/>
+      <c r="E131" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F131" s="6" t="n"/>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="6" t="n"/>
-      <c r="I131" s="6" t="inlineStr">
+      <c r="F131" s="8" t="n"/>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="8" t="n"/>
+      <c r="I131" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J131" s="7" t="inlineStr">
+      <c r="J131" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×10lbCO2@$4</t>
         </is>
       </c>
-      <c r="K131" s="7" t="inlineStr"/>
-      <c r="L131" s="7" t="inlineStr"/>
-      <c r="M131" s="7" t="inlineStr"/>
+      <c r="K131" s="9" t="inlineStr"/>
+      <c r="L131" s="9" t="inlineStr"/>
+      <c r="M131" s="9" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6863,41 +6706,41 @@
       <c r="M137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="inlineStr">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1610 ESPE07 URDESA.xlsx</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C138" s="8" t="inlineStr">
         <is>
           <t>ESPE7</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr"/>
-      <c r="E138" s="6" t="n">
+      <c r="D138" s="8" t="inlineStr"/>
+      <c r="E138" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="F138" s="6" t="n"/>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="6" t="n"/>
-      <c r="I138" s="6" t="inlineStr">
+      <c r="F138" s="8" t="n"/>
+      <c r="G138" s="8" t="inlineStr"/>
+      <c r="H138" s="8" t="n"/>
+      <c r="I138" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J138" s="7" t="inlineStr">
+      <c r="J138" s="9" t="inlineStr">
         <is>
           <t>2×5lbCO2@$2 + 4×10lbPQS@$4 + 1×5lbPQS@$2</t>
         </is>
       </c>
-      <c r="K138" s="7" t="inlineStr"/>
-      <c r="L138" s="7" t="inlineStr"/>
-      <c r="M138" s="7" t="inlineStr"/>
+      <c r="K138" s="9" t="inlineStr"/>
+      <c r="L138" s="9" t="inlineStr"/>
+      <c r="M138" s="9" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -6945,41 +6788,41 @@
       <c r="M139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="inlineStr">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1651 AMCA33 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
+      <c r="C140" s="8" t="inlineStr">
         <is>
           <t>AMCA33</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr"/>
-      <c r="E140" s="6" t="n">
+      <c r="D140" s="8" t="inlineStr"/>
+      <c r="E140" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F140" s="6" t="n"/>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="n"/>
-      <c r="I140" s="6" t="inlineStr">
+      <c r="F140" s="8" t="n"/>
+      <c r="G140" s="8" t="inlineStr"/>
+      <c r="H140" s="8" t="n"/>
+      <c r="I140" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J140" s="7" t="inlineStr">
+      <c r="J140" s="9" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K140" s="7" t="inlineStr"/>
-      <c r="L140" s="7" t="inlineStr"/>
-      <c r="M140" s="7" t="inlineStr"/>
+      <c r="K140" s="9" t="inlineStr"/>
+      <c r="L140" s="9" t="inlineStr"/>
+      <c r="M140" s="9" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -7027,41 +6870,41 @@
       <c r="M141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="6" t="inlineStr">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1653 ESPE31 POLICENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C142" s="8" t="inlineStr">
         <is>
           <t>ESPE31</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr"/>
-      <c r="E142" s="6" t="n">
+      <c r="D142" s="8" t="inlineStr"/>
+      <c r="E142" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F142" s="6" t="n"/>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="n"/>
-      <c r="I142" s="6" t="inlineStr">
+      <c r="F142" s="8" t="n"/>
+      <c r="G142" s="8" t="inlineStr"/>
+      <c r="H142" s="8" t="n"/>
+      <c r="I142" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J142" s="7" t="inlineStr">
+      <c r="J142" s="9" t="inlineStr">
         <is>
           <t>1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K142" s="7" t="inlineStr"/>
-      <c r="L142" s="7" t="inlineStr"/>
-      <c r="M142" s="7" t="inlineStr"/>
+      <c r="K142" s="9" t="inlineStr"/>
+      <c r="L142" s="9" t="inlineStr"/>
+      <c r="M142" s="9" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -7109,601 +6952,601 @@
       <c r="M143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="6" t="inlineStr">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1213 KFC OFICINAS CENTRO.xlsx</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C144" s="8" t="inlineStr">
         <is>
           <t>KFC</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr"/>
-      <c r="E144" s="6" t="n">
+      <c r="D144" s="8" t="inlineStr"/>
+      <c r="E144" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="F144" s="6" t="n"/>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="6" t="n"/>
-      <c r="I144" s="6" t="inlineStr">
+      <c r="F144" s="8" t="n"/>
+      <c r="G144" s="8" t="inlineStr"/>
+      <c r="H144" s="8" t="n"/>
+      <c r="I144" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J144" s="7" t="inlineStr">
+      <c r="J144" s="9" t="inlineStr">
         <is>
           <t>1×10lbCO2@$4 + 4×5lbCO2@$2 + 12×10lbPQS@$4 + 1×5lbPQS@$2</t>
         </is>
       </c>
-      <c r="K144" s="7" t="inlineStr"/>
-      <c r="L144" s="7" t="inlineStr"/>
-      <c r="M144" s="7" t="inlineStr"/>
+      <c r="K144" s="9" t="inlineStr"/>
+      <c r="L144" s="9" t="inlineStr"/>
+      <c r="M144" s="9" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>COTIZACION1217 M33 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C145" s="8" t="inlineStr">
+      <c r="C145" s="10" t="inlineStr">
         <is>
           <t>M33</t>
         </is>
       </c>
-      <c r="D145" s="8" t="inlineStr">
+      <c r="D145" s="10" t="inlineStr">
         <is>
           <t>M033 - CITY MALL</t>
         </is>
       </c>
-      <c r="E145" s="8" t="n">
+      <c r="E145" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="F145" s="8" t="n">
+      <c r="F145" s="10" t="n">
         <v>63.8</v>
       </c>
-      <c r="G145" s="8" t="inlineStr">
+      <c r="G145" s="10" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H145" s="8" t="n">
+      <c r="H145" s="10" t="n">
         <v>56.11</v>
       </c>
-      <c r="I145" s="8" t="inlineStr">
+      <c r="I145" s="10" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J145" s="9" t="inlineStr">
+      <c r="J145" s="11" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K145" s="9" t="inlineStr">
+      <c r="K145" s="11" t="inlineStr">
         <is>
           <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
         </is>
       </c>
-      <c r="L145" s="9" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
-        </is>
-      </c>
-      <c r="M145" s="9" t="inlineStr">
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
         <is>
           <t>Reemitir cotización como RECARGA por $63.80</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>COTIZACION1218 CJNC11 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C146" s="8" t="inlineStr">
+      <c r="C146" s="10" t="inlineStr">
         <is>
           <t>J11</t>
         </is>
       </c>
-      <c r="D146" s="8" t="inlineStr">
+      <c r="D146" s="10" t="inlineStr">
         <is>
           <t>J011 - CITY MALL</t>
         </is>
       </c>
-      <c r="E146" s="8" t="n">
+      <c r="E146" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="F146" s="8" t="n">
+      <c r="F146" s="10" t="n">
         <v>63.8</v>
       </c>
-      <c r="G146" s="8" t="inlineStr">
+      <c r="G146" s="10" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H146" s="8" t="n">
+      <c r="H146" s="10" t="n">
         <v>56.11</v>
       </c>
-      <c r="I146" s="8" t="inlineStr">
+      <c r="I146" s="10" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J146" s="9" t="inlineStr">
+      <c r="J146" s="11" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K146" s="9" t="inlineStr">
+      <c r="K146" s="11" t="inlineStr">
         <is>
           <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
         </is>
       </c>
-      <c r="L146" s="9" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
-        </is>
-      </c>
-      <c r="M146" s="9" t="inlineStr">
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="inlineStr">
         <is>
           <t>Reemitir cotización como RECARGA por $63.80</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="6" t="inlineStr">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1219 ESPE09 RIOCENTRO CEIBOS.xlsx</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
+      <c r="C147" s="8" t="inlineStr">
         <is>
           <t>ESPE9</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr"/>
-      <c r="E147" s="6" t="n">
+      <c r="D147" s="8" t="inlineStr"/>
+      <c r="E147" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F147" s="6" t="n"/>
-      <c r="G147" s="6" t="inlineStr"/>
-      <c r="H147" s="6" t="n"/>
-      <c r="I147" s="6" t="inlineStr">
+      <c r="F147" s="8" t="n"/>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="8" t="n"/>
+      <c r="I147" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J147" s="7" t="inlineStr">
+      <c r="J147" s="9" t="inlineStr">
         <is>
           <t>1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
         </is>
       </c>
-      <c r="K147" s="7" t="inlineStr"/>
-      <c r="L147" s="7" t="inlineStr"/>
-      <c r="M147" s="7" t="inlineStr"/>
+      <c r="K147" s="9" t="inlineStr"/>
+      <c r="L147" s="9" t="inlineStr"/>
+      <c r="M147" s="9" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="6" t="inlineStr">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>COTIZACION1220 ESPE30 CITY MALL.xlsx</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
+      <c r="C148" s="8" t="inlineStr">
         <is>
           <t>ESPE30</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr"/>
-      <c r="E148" s="6" t="n">
+      <c r="D148" s="8" t="inlineStr"/>
+      <c r="E148" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F148" s="6" t="n"/>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="6" t="n"/>
-      <c r="I148" s="6" t="inlineStr">
+      <c r="F148" s="8" t="n"/>
+      <c r="G148" s="8" t="inlineStr"/>
+      <c r="H148" s="8" t="n"/>
+      <c r="I148" s="8" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J148" s="7" t="inlineStr">
+      <c r="J148" s="9" t="inlineStr">
         <is>
           <t>1×5lbCO2@$2 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K148" s="7" t="inlineStr"/>
-      <c r="L148" s="7" t="inlineStr"/>
-      <c r="M148" s="7" t="inlineStr"/>
+      <c r="K148" s="9" t="inlineStr"/>
+      <c r="L148" s="9" t="inlineStr"/>
+      <c r="M148" s="9" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="inlineStr">
+      <c r="A149" s="10" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B149" s="10" t="inlineStr">
         <is>
           <t>COTIZACION1221 M61 PORTETE.xlsx</t>
         </is>
       </c>
-      <c r="C149" s="8" t="inlineStr">
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>M61</t>
         </is>
       </c>
-      <c r="D149" s="8" t="inlineStr">
+      <c r="D149" s="10" t="inlineStr">
         <is>
           <t>M061 - PORTETE</t>
         </is>
       </c>
-      <c r="E149" s="8" t="n">
+      <c r="E149" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="F149" s="8" t="n">
+      <c r="F149" s="10" t="n">
         <v>152</v>
       </c>
-      <c r="G149" s="8" t="inlineStr">
+      <c r="G149" s="10" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H149" s="8" t="n">
+      <c r="H149" s="10" t="n">
         <v>57.89</v>
       </c>
-      <c r="I149" s="8" t="inlineStr">
+      <c r="I149" s="10" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J149" s="9" t="inlineStr">
+      <c r="J149" s="11" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 6×10lbPQS@$4 + 2×20lbPQS@$8</t>
         </is>
       </c>
-      <c r="K149" s="9" t="inlineStr">
+      <c r="K149" s="11" t="inlineStr">
         <is>
           <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20</t>
         </is>
       </c>
-      <c r="L149" s="9" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($64.00). Debería ser RECARGA ($152.00). | Extintores COT=$64.00 vs DB=$152.00 (neto $-88.00) | 1×10lbCO2: precio COT=$4 vs DB=$9/ext | 2×20lbPQS: precio COT=$8 vs DB=$20/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 6×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
-        </is>
-      </c>
-      <c r="M149" s="9" t="inlineStr">
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($64.00). Debería ser RECARGA ($152.00). | Extintores COT=$64.00 vs DB=$152.00 (neto $-88.00) | 1×10lbCO2: precio COT=$4 vs DB=$9/ext | 6×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
+        </is>
+      </c>
+      <c r="M149" s="11" t="inlineStr">
         <is>
           <t>Reemitir cotización como RECARGA por $152.00</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="inlineStr">
+      <c r="A150" s="10" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B150" s="10" t="inlineStr">
         <is>
           <t>COTIZACION1222 KFCK109 CITY MALL PA.xlsx</t>
         </is>
       </c>
-      <c r="C150" s="8" t="inlineStr">
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>K109</t>
         </is>
       </c>
-      <c r="D150" s="8" t="inlineStr">
+      <c r="D150" s="10" t="inlineStr">
         <is>
           <t>K109 - CITY MALL PA</t>
         </is>
       </c>
-      <c r="E150" s="8" t="n">
+      <c r="E150" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="F150" s="8" t="n">
+      <c r="F150" s="10" t="n">
         <v>72.8</v>
       </c>
-      <c r="G150" s="8" t="inlineStr">
+      <c r="G150" s="10" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H150" s="8" t="n">
+      <c r="H150" s="10" t="n">
         <v>56.04</v>
       </c>
-      <c r="I150" s="8" t="inlineStr">
+      <c r="I150" s="10" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J150" s="9" t="inlineStr">
+      <c r="J150" s="11" t="inlineStr">
         <is>
           <t>1×50lb?@$20 + 1×10lbCO2@$4 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K150" s="9" t="inlineStr">
+      <c r="K150" s="11" t="inlineStr">
         <is>
           <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
         </is>
       </c>
-      <c r="L150" s="9" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($32.00). Debería ser RECARGA ($72.80). | Extintores COT=$32.00 vs DB=$72.80 (neto $-40.80) | COT tiene +1×50lb? que no está en DB (precio $20/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($45/ext) | 1×10lbCO2: precio COT=$4 vs DB=$9/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
-        </is>
-      </c>
-      <c r="M150" s="9" t="inlineStr">
+      <c r="L150" s="11" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($32.00). Debería ser RECARGA ($72.80). | Extintores COT=$32.00 vs DB=$72.80 (neto $-40.80) | COT tiene +1×50lb? que no está en DB (precio $20/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($45/ext) | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbCO2: precio COT=$4 vs DB=$9/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
+        </is>
+      </c>
+      <c r="M150" s="11" t="inlineStr">
         <is>
           <t>Reemitir cotización como RECARGA por $72.80</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1214 KFCK88 HIPER VIA A DAULE.xlsx</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
         <is>
           <t>K88</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr">
+      <c r="D151" s="6" t="inlineStr">
         <is>
           <t>K088 - HIPERMARKET VIA DAULE</t>
         </is>
       </c>
-      <c r="E151" s="4" t="n">
+      <c r="E151" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="F151" s="6" t="n">
         <v>97.7</v>
       </c>
-      <c r="G151" s="4" t="inlineStr">
+      <c r="G151" s="6" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H151" s="4" t="n">
+      <c r="H151" s="6" t="n">
         <v>52.92</v>
       </c>
-      <c r="I151" s="4" t="inlineStr">
+      <c r="I151" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J151" s="5" t="inlineStr">
+      <c r="J151" s="7" t="inlineStr">
         <is>
           <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 3×10lbPQS@$4 + 1×20lbPQS@$8</t>
         </is>
       </c>
-      <c r="K151" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20</t>
-        </is>
-      </c>
-      <c r="L151" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$46.00 vs DB=$97.70 (neto $-51.70) | Cantidad: 8 ext en COT vs 7 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | 1×20lbPQS: precio COT=$8 vs DB=$20/ext | 3×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext</t>
-        </is>
-      </c>
-      <c r="M151" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext? | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext?</t>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$97.70 (neto $-51.70) | Cantidad: 8 ext en COT vs 7 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | 3×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 1×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
+        </is>
+      </c>
+      <c r="M151" s="7" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext? | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext?</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="B152" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1215 KFCK110 CITY MALL PB.xlsx</t>
         </is>
       </c>
-      <c r="C152" s="4" t="inlineStr">
+      <c r="C152" s="6" t="inlineStr">
         <is>
           <t>K110</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr">
+      <c r="D152" s="6" t="inlineStr">
         <is>
           <t>K110 - CITY MALL PB</t>
         </is>
       </c>
-      <c r="E152" s="4" t="n">
+      <c r="E152" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="F152" s="4" t="n">
+      <c r="F152" s="6" t="n">
         <v>124.7</v>
       </c>
-      <c r="G152" s="4" t="inlineStr">
+      <c r="G152" s="6" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H152" s="4" t="n">
+      <c r="H152" s="6" t="n">
         <v>59.9</v>
       </c>
-      <c r="I152" s="4" t="inlineStr">
+      <c r="I152" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J152" s="5" t="inlineStr">
+      <c r="J152" s="7" t="inlineStr">
         <is>
           <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×20lbPQS@$8 + 2×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K152" s="5" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$68 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbCO2@$9 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
-        </is>
-      </c>
-      <c r="L152" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$50.00 vs DB=$124.70 (neto $-74.70) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | 1×75lbCO2: precio COT=$30 vs DB=$68/ext | 1×20lbPQS: precio COT=$8 vs DB=$20/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 2×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
-        </is>
-      </c>
-      <c r="M152" s="5" t="inlineStr">
-        <is>
-          <t>¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿Actualizar precio 75lbCO2 en BD: $68→$30/ext? | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext? | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 10lbPQS en BD: $10→$4/ext?</t>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>Extintores COT=$50.00 vs DB=$124.70 (neto $-74.70) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×75lbCO2: precio COT=$30 vs DB=$68/ext | 2×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
+        </is>
+      </c>
+      <c r="M152" s="7" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 75lbCO2 en BD: $68→$30/ext? | ¿Actualizar precio 10lbPQS en BD: $10→$4/ext? | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext?</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="inlineStr">
+      <c r="A153" s="10" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B153" s="10" t="inlineStr">
         <is>
           <t>COTIZACION1216 KFCK117 SEDALANA.xlsx</t>
         </is>
       </c>
-      <c r="C153" s="8" t="inlineStr">
+      <c r="C153" s="10" t="inlineStr">
         <is>
           <t>K117</t>
         </is>
       </c>
-      <c r="D153" s="8" t="inlineStr">
+      <c r="D153" s="10" t="inlineStr">
         <is>
           <t>K117 - 29 Y SEDALANA</t>
         </is>
       </c>
-      <c r="E153" s="8" t="n">
+      <c r="E153" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="F153" s="8" t="n">
+      <c r="F153" s="10" t="n">
         <v>241.2</v>
       </c>
-      <c r="G153" s="8" t="inlineStr">
+      <c r="G153" s="10" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H153" s="8" t="n">
+      <c r="H153" s="10" t="n">
         <v>56.88</v>
       </c>
-      <c r="I153" s="8" t="inlineStr">
+      <c r="I153" s="10" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J153" s="9" t="inlineStr">
+      <c r="J153" s="11" t="inlineStr">
         <is>
           <t>3×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 5×10lbPQS@$4</t>
         </is>
       </c>
-      <c r="K153" s="9" t="inlineStr">
+      <c r="K153" s="11" t="inlineStr">
         <is>
           <t>1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10</t>
         </is>
       </c>
-      <c r="L153" s="9" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($104.00). Debería ser RECARGA ($241.20). | Extintores COT=$104.00 vs DB=$241.20 (neto $-137.20) | 2×20lbPQS: precio COT=$8 vs DB=$20/ext | 4×5lbCO2: precio COT=$2 vs DB=$4/ext | 3×50lbCO2: precio COT=$20 vs DB=$45/ext | 5×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
-        </is>
-      </c>
-      <c r="M153" s="9" t="inlineStr">
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($104.00). Debería ser RECARGA ($241.20). | Extintores COT=$104.00 vs DB=$241.20 (neto $-137.20) | 4×5lbCO2: precio COT=$2 vs DB=$4/ext | 5×10lbPQS: precio COT=$4 vs DB=$10/ext | 3×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="inlineStr">
         <is>
           <t>Reemitir cotización como RECARGA por $241.20</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="inlineStr">
+      <c r="A154" s="6" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B154" s="6" t="inlineStr">
         <is>
           <t>COTIZACION1212 B001 ARRECIFE AEROPUERTO.xlsx</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
+      <c r="C154" s="6" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="D154" s="4" t="inlineStr">
+      <c r="D154" s="6" t="inlineStr">
         <is>
           <t>B001 - STATION SPORTS BAR</t>
         </is>
       </c>
-      <c r="E154" s="4" t="n">
+      <c r="E154" s="6" t="n">
         <v>78.8</v>
       </c>
-      <c r="F154" s="4" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="G154" s="4" t="inlineStr">
+      <c r="F154" s="6" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H154" s="4" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="I154" s="4" t="inlineStr">
+      <c r="H154" s="6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J154" s="5" t="inlineStr">
+      <c r="J154" s="7" t="inlineStr">
         <is>
           <t>1×20lbCO2@$20 + 3×10lbPQS@$10 + 2×5lbPQS@$5 + 1×50lbCO2@$20</t>
         </is>
       </c>
-      <c r="K154" s="5" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×20lbCO2@$18 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
-        </is>
-      </c>
-      <c r="L154" s="5" t="inlineStr">
-        <is>
-          <t>Extintores COT=$78.80 vs DB=$92.40 (neto $-13.60) | Cantidad: 7 ext en COT vs 5 en DB | COT tiene +2×5lbPQS que no está en DB (precio $5/ext) | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 1×20lbCO2: precio COT=$20 vs DB=$18/ext</t>
-        </is>
-      </c>
-      <c r="M154" s="5" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 2×5lbPQS a BD? ($5/ext) | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext? | ¿Actualizar precio 20lbCO2 en BD: $18→$20/ext?</t>
+      <c r="K154" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×20lbCO2@$18 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×5lbPQS@$5 + 1×5lbPQS@$5</t>
+        </is>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>Extintores COT=$78.80 vs DB=$102.20 (neto $-23.40) | 1×20lbCO2: precio COT=$20 vs DB=$18/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext</t>
+        </is>
+      </c>
+      <c r="M154" s="7" t="inlineStr">
+        <is>
+          <t>¿Actualizar precio 20lbCO2 en BD: $18→$20/ext? | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext?</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7569,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>RESUMEN REVISION COTIZACIONES 2026</t>
         </is>
@@ -7754,7 +7597,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
@@ -7764,7 +7607,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -7784,7 +7627,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -7847,10 +7690,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -7859,7 +7702,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -7872,10 +7715,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -7897,10 +7740,10 @@
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -7925,16 +7768,16 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -7972,10 +7815,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/REVISION_COTIZACIONES_2026.xlsx
+++ b/REVISION_COTIZACIONES_2026.xlsx
@@ -35,7 +35,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -50,11 +50,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -99,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -126,12 +121,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -500,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -721,57 +710,49 @@
       <c r="M4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>COTIZACION1282 KFCK79 BABAHOYO.xlsx</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>K79</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>K079 - BABAHOYO</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>1×??@$48 + 1×10lbPQS@$34  [+MOVIL:$40.00 — MOVILIZACION (GYE - BABAHOYO)]</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Cotización por venta de extintores / servicio, no mantenimiento</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Informativo — no afecta la base de datos</t>
-        </is>
-      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1262 KFCK02 9 DE OCT Y CHIMBORAZO.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>K002 - 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -781,24 +762,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1262 KFCK02 9 DE OCT Y CHIMBORAZO.xlsx</t>
+          <t>COTIZACION1275 M35 GARZOTA.xlsx</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>M35</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>K002 - 9 DE OCTUBRE</t>
+          <t>M035 - GARZOTA</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -826,24 +807,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1275 M35 GARZOTA.xlsx</t>
+          <t>COTIZACION1270 KFCK95 PASEO SHOPPING VIA A DAULE.xlsx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>M35</t>
+          <t>K95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>M035 - GARZOTA</t>
+          <t>K095 - PASEO SHOP KM 9 VIA DAULE</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -871,24 +852,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1270 KFCK95 PASEO SHOPPING VIA A DAULE.xlsx</t>
+          <t>COTIZACION1262 KFCK25 MOBIL DURAN.xlsx</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>K95</t>
+          <t>K25</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>K095 - PASEO SHOP KM 9 VIA DAULE</t>
+          <t>K025 - MOBIL DURAN</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -916,24 +897,24 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1262 KFCK25 MOBIL DURAN.xlsx</t>
+          <t>COTIZACION1273 KFCK154 PASCUALES.xlsx</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>K25</t>
+          <t>K154</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>K025 - MOBIL DURAN</t>
+          <t>K154 - PASCUALES</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -961,24 +942,24 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1273 KFCK154 PASCUALES.xlsx</t>
+          <t>COTIZACION1266 KFCK74 PARQUE CALIFORNIA.xlsx</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>K154</t>
+          <t>K74</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>K154 - PASCUALES</t>
+          <t>K074 - CALIFORNIA</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1006,24 +987,24 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1266 KFCK74 PARQUE CALIFORNIA.xlsx</t>
+          <t>COTIZACION1268 KFCK77 RIOCENTRO CEIBOS.xlsx</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>K74</t>
+          <t>K77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>K074 - CALIFORNIA</t>
+          <t>K077 - RIO CENTRO LOS CEIBOS</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1051,24 +1032,24 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1268 KFCK77 RIOCENTRO CEIBOS.xlsx</t>
+          <t>COTIZACION1272 KFCK153 LIGA CANTONAL DURAN.xlsx</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>K77</t>
+          <t>K153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>K077 - RIO CENTRO LOS CEIBOS</t>
+          <t>K153 - LIGA CANTONAL DURAN</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1096,24 +1077,24 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1272 KFCK153 LIGA CANTONAL DURAN.xlsx</t>
+          <t>COTIZACION1277 T032 TERMINAL GYE.xlsx</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>K153</t>
+          <t>T32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>K153 - LIGA CANTONAL DURAN</t>
+          <t>T032 - TERMINAL</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1141,24 +1122,24 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1277 T032 TERMINAL GYE.xlsx</t>
+          <t>COTIZACION1263 KFCK34 KM4,5 VIA A DAULE.xlsx</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>T32</t>
+          <t>K34</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>T032 - TERMINAL</t>
+          <t>K034 - VIA DAULE</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1179,110 +1160,110 @@
       <c r="M14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1263 KFCK34 KM4,5 VIA A DAULE.xlsx</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>K34</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>K034 - VIA DAULE</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1267 KFCK76 PARQUE CENTENARIO.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>K76</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>K076 - PARQUE CENTENARIO</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$36.00 vs DB=$40.00 (neto $-4.00) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbPQS que no aparece en COT ($4/ext)</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1267 KFCK76 PARQUE CENTENARIO.xlsx</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>K76</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>K076 - PARQUE CENTENARIO</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 3×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$36.00 vs DB=$40.00 (neto $-4.00) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbPQS que no aparece en COT ($4/ext)</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>¿RETIRAR 1×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1279 KFCK63 RIOCENTRO SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>K063 - RIO CENTRO SUR</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1292,24 +1273,24 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1279 KFCK63 RIOCENTRO SUR.xlsx</t>
+          <t>COTIZACION1274 M31 RIOCENTRO NORTE.xlsx</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>K63</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>K063 - RIO CENTRO SUR</t>
+          <t>M031 - RIO CENTRO NORTE</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1337,24 +1318,24 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1274 M31 RIOCENTRO NORTE.xlsx</t>
+          <t>COTIZACION1276 CJNC01 MALL DEL SOL.xlsx</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>M031 - RIO CENTRO NORTE</t>
+          <t>J001 - MALL DEL SOL</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1382,24 +1363,24 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1276 CJNC01 MALL DEL SOL.xlsx</t>
+          <t>COTIZACION1263 KFCK29 MALECON Y OLMEDO.xlsx</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>K29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>J001 - MALL DEL SOL</t>
+          <t>K029 - MALECON 2000</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1427,17 +1408,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1263 KFCK29 MALECON Y OLMEDO.xlsx</t>
+          <t>COTIZACION1278 I003 MALL DEL SOL.xlsx</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>K29</t>
+          <t>I3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>K029 - MALECON 2000</t>
+          <t>I003 - MALL DEL SOL</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1472,24 +1453,24 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1278 I003 MALL DEL SOL.xlsx</t>
+          <t>COTIZACION1260 JV55 MALL DEL SOL.xlsx</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>I3</t>
+          <t>V55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>I003 - MALL DEL SOL</t>
+          <t>V055 - MALL DEL SOL ZONA GASTRO</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1510,110 +1491,110 @@
       <c r="M21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1260 JV55 MALL DEL SOL.xlsx</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>V55</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>V055 - MALL DEL SOL ZONA GASTRO</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1271 KFCK105 RIOCENTRO NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>K105</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>K105 - HIPER MARKET</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$4 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$44.00 (neto +$2.00) | 1×5lbCO2: precio COT=$4 vs DB=$2/ext</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>¿Actualizar precio 5lbCO2 en BD: $2→$4/ext?</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1271 KFCK105 RIOCENTRO NORTE.xlsx</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>K105</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>K105 - HIPER MARKET</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×5lbCO2@$4 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$46.00 vs DB=$44.00 (neto +$2.00) | 1×5lbCO2: precio COT=$4 vs DB=$2/ext</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>¿Actualizar precio 5lbCO2 en BD: $2→$4/ext?</t>
-        </is>
-      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1264 KFCK37 AKI DOMINGO COMIN.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>K37</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>K037 - DOMINGO COMIN</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1623,24 +1604,24 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1264 KFCK37 AKI DOMINGO COMIN.xlsx</t>
+          <t>COTIZACION1265 KFCK55 MOBIL CORDOVA.xlsx</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>K37</t>
+          <t>K55</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>K037 - DOMINGO COMIN</t>
+          <t>K055 - MOBIL CORDOVA</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1663,29 +1644,29 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ENERO</t>
+          <t>FEBRERO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1265 KFCK55 MOBIL CORDOVA.xlsx</t>
+          <t>COTIZACION1290 KFCK07 ALBORADA.xlsx</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>K55</t>
+          <t>K7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>K055 - MOBIL CORDOVA</t>
+          <t>K007 - ALBORADA</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -1713,24 +1694,24 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1290 KFCK07 ALBORADA.xlsx</t>
+          <t>COTIZACION1291 KFCK45 BOYACA.xlsx</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K45</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>K007 - ALBORADA</t>
+          <t>K045 - BOYACA</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1758,24 +1739,24 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1291 KFCK45 BOYACA.xlsx</t>
+          <t>COTIZACION1295 KFCK148 TERMINAL MACHALA.xlsx</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>K45</t>
+          <t>K148</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>K045 - BOYACA</t>
+          <t>K148 - TERMINAL TERRESTRE MACHALA</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>70</v>
+        <v>93.5</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>70</v>
+        <v>93.5</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -1803,24 +1784,24 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1295 KFCK148 TERMINAL MACHALA.xlsx</t>
+          <t>COTIZACION1299 BS31 RIOC CEIBOS.xlsx</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>K148</t>
+          <t>BS31</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>K148 - TERMINAL TERRESTRE MACHALA</t>
+          <t>CN31 - RIOCENTRO CEIBOS</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>93.5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>93.5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1848,24 +1829,24 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1299 BS31 RIOC CEIBOS.xlsx</t>
+          <t>COTIZACION1300 BS38 RIOC CEIBOS2.xlsx</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>BS31</t>
+          <t>BS38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CN31 - RIOCENTRO CEIBOS</t>
+          <t>BS38 - CEIBOS BASKIN</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -1886,160 +1867,160 @@
       <c r="M29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1300 BS38 RIOC CEIBOS2.xlsx</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>BS38</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>BS38 - CEIBOS BASKIN</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1301 ESPE06 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ESPE6</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1302 ESPE10 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ESPE10</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1303 ESPE26 RIOC PUNTILLA.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>ESPE26</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×5lbCO2@$2</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1301 ESPE06 MALL DEL SOL.xlsx</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>ESPE6</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>1×10lbPQS@$4 + 1×5lbCO2@$2</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="9" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>FEBRERO</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1302 ESPE10 SAN MARINO.xlsx</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>ESPE10</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>FEBRERO</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1303 ESPE26 RIOC PUNTILLA.xlsx</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>ESPE26</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr"/>
-      <c r="E33" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>1×10lbPQS@$4 + 1×5lbPQS@$2 + 1×5lbCO2@$2</t>
-        </is>
-      </c>
-      <c r="K33" s="9" t="inlineStr"/>
-      <c r="L33" s="9" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1304 V015 RIOC CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>V15</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>V015 - CEIBOS</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2049,17 +2030,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1304 V015 RIOC CEIBOS.xlsx</t>
+          <t>COTIZACION1305 V021 MALL DEL SOL.xlsx</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>V15</t>
+          <t>V21</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>V015 - CEIBOS</t>
+          <t>V021 - MALL DEL SOL</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
@@ -2094,24 +2075,24 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1305 V021 MALL DEL SOL.xlsx</t>
+          <t>COTIZACION1306 CJNC02 SAN MARINO.xlsx</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>V21</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>V021 - MALL DEL SOL</t>
+          <t>J002 - SAN MARINO</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -2132,86 +2113,86 @@
       <c r="M35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1306 CJNC02 SAN MARINO.xlsx</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>J002 - SAN MARINO</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1307 ILCI02 RIOC. CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>ILCI2</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1307 ILCI02 RIOC. CEIBOS.xlsx</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>ILCI2</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K37" s="9" t="inlineStr"/>
-      <c r="L37" s="9" t="inlineStr"/>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1308 JV75 PASEO SHOPPING MACHALA.xlsx</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>V75</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>V075 - PASEO SHOPPING MACHALA</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2221,24 +2202,24 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1308 JV75 PASEO SHOPPING MACHALA.xlsx</t>
+          <t>COTIZACION1293 KFCK90 MACHALA CENTRO.xlsx</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>V75</t>
+          <t>K90</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>V075 - PASEO SHOPPING MACHALA</t>
+          <t>K090 - MACHALA CENTRO</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>16</v>
+        <v>111.5</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>16</v>
+        <v>111.5</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2266,24 +2247,24 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1293 KFCK90 MACHALA CENTRO.xlsx</t>
+          <t>COTIZACION1294 KFCK91PASEO SHOPP MACHALA.xlsx</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>K90</t>
+          <t>K91</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>K090 - MACHALA CENTRO</t>
+          <t>K091 - MACHALA RIO CENTRO</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>111.5</v>
+        <v>87.5</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>111.5</v>
+        <v>87.5</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2311,24 +2292,24 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1294 KFCK91PASEO SHOPP MACHALA.xlsx</t>
+          <t>COTIZACION1292 KFCK65 MILAGRO.xlsx</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>K91</t>
+          <t>K65</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>K091 - MACHALA RIO CENTRO</t>
+          <t>K065 - MILAGRO</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>87.5</v>
+        <v>61</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>87.5</v>
+        <v>61</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2356,24 +2337,24 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1292 KFCK65 MILAGRO.xlsx</t>
+          <t>COTIZACION1298 BS09 RIOC SUR.xlsx</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>K65</t>
+          <t>BS9</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>K065 - MILAGRO</t>
+          <t>BS09 - RIO CENTRO SUR</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2401,24 +2382,24 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1298 BS09 RIOC SUR.xlsx</t>
+          <t>COTIZACION1309 JV79 MILAGRO.xlsx</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>BS9</t>
+          <t>V79</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>BS09 - RIO CENTRO SUR</t>
+          <t>V079 - MILAGRO</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2439,168 +2420,168 @@
       <c r="M42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1309 JV79 MILAGRO.xlsx</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>V79</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>V079 - MILAGRO</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1296 AMCA37 EL DORADO.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>AMCA37</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1296 AMCA37 EL DORADO.xlsx</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>AMCA37</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr"/>
-      <c r="E44" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1297 BS04 CN04 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>BS04 - MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1352 GUSG49 DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>GUSG49</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>FEBRERO</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1297 BS04 CN04 MALL DEL SOL.xlsx</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>BS04 - MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr"/>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1352 GUSG49 DURAN.xlsx</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>GUSG49</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr"/>
-      <c r="E46" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="inlineStr"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K46" s="9" t="inlineStr"/>
-      <c r="L46" s="9" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1355 M47 DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>M47</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>M047 - PASEO SHOPPING DURAN</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2610,24 +2591,24 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1355 M47 DURAN.xlsx</t>
+          <t>COTIZACION1356 M57 ALBORADA.xlsx</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>M47</t>
+          <t>M57</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>M047 - PASEO SHOPPING DURAN</t>
+          <t>M057 - ALBORADA</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -2648,86 +2629,86 @@
       <c r="M47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1356 M57 ALBORADA.xlsx</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>M57</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>M057 - ALBORADA</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr"/>
-      <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="3" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1357 ILCI05 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>ILCI5</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="n"/>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1357 ILCI05 SAN MARINO.xlsx</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>ILCI5</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr"/>
-      <c r="E49" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="inlineStr"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbPQS@$4 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K49" s="9" t="inlineStr"/>
-      <c r="L49" s="9" t="inlineStr"/>
-      <c r="M49" s="9" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1358 KFCK75 MOBIL KENNEDY.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>K75</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>K075 - MOBIL KENNEDY</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2737,24 +2718,24 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1358 KFCK75 MOBIL KENNEDY.xlsx</t>
+          <t>COTIZACION1359 CN37 EL DORADO.xlsx</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>K75</t>
+          <t>BS37</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>K075 - MOBIL KENNEDY</t>
+          <t>BS37 - DORADO</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -2782,24 +2763,24 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1359 CN37 EL DORADO.xlsx</t>
+          <t>COTIZACION1361 KFCK176 SUPERCINES ORELLANA.xlsx</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>BS37</t>
+          <t>K176</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>BS37 - DORADO</t>
+          <t>K176 - SUPERCINES</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -2827,17 +2808,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1361 KFCK176 SUPERCINES ORELLANA.xlsx</t>
+          <t>COTIZACION1362 KFCK169 PLAZA PACIFICO.xlsx</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>K176</t>
+          <t>K169</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>K176 - SUPERCINES</t>
+          <t>K169 - PLAZA PACIFICO DAULE</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
@@ -2872,24 +2853,24 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1362 KFCK169 PLAZA PACIFICO.xlsx</t>
+          <t>COTIZACION1363 JV66 PLAZA PACIFICO.xlsx</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>K169</t>
+          <t>V66</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>K169 - PLAZA PACIFICO DAULE</t>
+          <t>V066 PLAZA PACIFICO DAULE</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -2910,110 +2891,110 @@
       <c r="M53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1363 JV66 PLAZA PACIFICO.xlsx</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>V66</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>V066 PLAZA PACIFICO DAULE</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr"/>
-      <c r="K54" s="3" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr"/>
-      <c r="M54" s="3" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1350 KFCK94 PASEO SHOPPING DURAN.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>K94</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>K094 - OUTLET DURAN</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$30.00 vs DB=$32.00 (neto $-2.00) | Cantidad: 4 ext en COT vs 5 en DB | DB tiene +1×5lbCO2 que no aparece en COT ($2/ext)</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×5lbCO2 de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1350 KFCK94 PASEO SHOPPING DURAN.xlsx</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>K94</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>K094 - OUTLET DURAN</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$30.00 vs DB=$32.00 (neto $-2.00) | Cantidad: 4 ext en COT vs 5 en DB | DB tiene +1×5lbCO2 que no aparece en COT ($2/ext)</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>¿RETIRAR 1×5lbCO2 de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1353 M11 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>M011 - MALL SUR</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3023,24 +3004,24 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1353 M11 MALL DEL SUR.xlsx</t>
+          <t>COTIZACION1351 KFCK145 AKI SAN EDUARDO.xlsx</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>K145</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>M011 - MALL SUR</t>
+          <t>K145 - SUPER AKI SAN EDUARDO</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3061,274 +3042,274 @@
       <c r="M56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1351 KFCK145 AKI SAN EDUARDO.xlsx</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>K145</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>K145 - SUPER AKI SAN EDUARDO</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr"/>
-      <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="3" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1354 M37 CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>M37</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>M037 - 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 6×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$58.00 vs DB=$48.00 (neto +$10.00) | Cantidad: 9 ext en COT vs 8 en DB | COT tiene +2×10lbPQS que no está en DB (precio $4/ext) | COT tiene +1×75lbCO2 que no está en DB (precio $30/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($20/ext)</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 2×10lbPQS a BD? ($4/ext) | ¿AGREGAR 1×75lbCO2 a BD? ($30/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1354 M37 CENTRO.xlsx</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>M37</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>M037 - 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 6×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$58.00 vs DB=$48.00 (neto +$10.00) | Cantidad: 9 ext en COT vs 8 en DB | COT tiene +1×75lbCO2 que no está en DB (precio $30/ext) | COT tiene +2×10lbPQS que no está en DB (precio $4/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($20/ext)</t>
-        </is>
-      </c>
-      <c r="M58" s="7" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×75lbCO2 a BD? ($30/ext) | ¿AGREGAR 2×10lbPQS a BD? ($4/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×50lbCO2 de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1360 M46 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>M46</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>M046 - SAN MARINO</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr"/>
+      <c r="M58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1360 M46 SAN MARINO.xlsx</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>M46</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>M046 - SAN MARINO</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr"/>
-      <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="3" t="inlineStr"/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1404 ILCI12 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>ILCI12</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1404 ILCI12 TERMINAL.xlsx</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>ILCI12</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr"/>
-      <c r="E60" s="8" t="n">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1405 JV57 CORAL SAMBORONDON.xlsx</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>V57</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>V057 - CORAL SAMBORONDON</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1403 GUSG45 TUNGURAHUA.xlsx</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>GUSG45</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="inlineStr"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="F61" s="6" t="n"/>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="n"/>
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr"/>
-      <c r="L60" s="9" t="inlineStr"/>
-      <c r="M60" s="9" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1405 JV57 CORAL SAMBORONDON.xlsx</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>V57</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>V057 - CORAL SAMBORONDON</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr"/>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>ABRIL</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1403 GUSG45 TUNGURAHUA.xlsx</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>GUSG45</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr"/>
-      <c r="E62" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="inlineStr"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K62" s="9" t="inlineStr"/>
-      <c r="L62" s="9" t="inlineStr"/>
-      <c r="M62" s="9" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1402 KFCK161 MALL DEL RIO GYE.xlsx</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>K161</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>K161 - MALL DEL RIO GYE</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3338,24 +3319,24 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1402 KFCK161 MALL DEL RIO GYE.xlsx</t>
+          <t>COTIZACION1401 KFCK82 PLAYAS.xlsx</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>K161</t>
+          <t>K82</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>K161 - MALL DEL RIO GYE</t>
+          <t>K082 - SHOPPING PLAYAS</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -3383,24 +3364,24 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1401 KFCK82 PLAYAS.xlsx</t>
+          <t>COTIZACION1406 JV87 DAULE.xlsx</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>K82</t>
+          <t>V87</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>K082 - SHOPPING PLAYAS</t>
+          <t>V087 - PASEO SHOPPING DAULE</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -3421,139 +3402,123 @@
       <c r="M64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1406 JV87 DAULE.xlsx</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>V87</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>V087 - PASEO SHOPPING DAULE</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr"/>
-      <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
-      <c r="M65" s="3" t="inlineStr"/>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1400 KFCK124 GRAN AKI LOJA.xlsx</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>K124</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>3×10lbCO2@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>ABRIL</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1400 KFCK124 GRAN AKI LOJA.xlsx</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>K124</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr"/>
-      <c r="E66" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F66" s="8" t="n"/>
-      <c r="G66" s="8" t="inlineStr"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1456 BS16 RIOC PUNTILLA.xlsx</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>BS16</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>BS16 - PUNTILLA</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1455 AMCA24 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>AMCA24</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F67" s="6" t="n"/>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="n"/>
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t>3×10lbCO2@$4 + 1×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="K66" s="9" t="inlineStr"/>
-      <c r="L66" s="9" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>ABRIL</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>COTIZACION1407 KFCK88 HIPER VIA A DAULE.xlsx</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>K88</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>K088 - HIPERMARKET VIA DAULE</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="F67" s="4" t="n"/>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>VENTA</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>1×10lbPQS@$34</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr"/>
-      <c r="L67" s="5" t="inlineStr">
-        <is>
-          <t>Cotización por venta de extintores / servicio, no mantenimiento</t>
-        </is>
-      </c>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>Informativo — no afecta la base de datos</t>
-        </is>
-      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3563,24 +3528,24 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1456 BS16 RIOC PUNTILLA.xlsx</t>
+          <t>COTIZACION1450 KFCK03 PLAZA QUIL.xlsx</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>BS16</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>BS16 - PUNTILLA</t>
+          <t>K003 - PLAZA QUIL</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -3601,41 +3566,49 @@
       <c r="M68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1455 AMCA24 MALL DEL SUR.xlsx</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>AMCA24</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr"/>
-      <c r="E69" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="F69" s="8" t="n"/>
-      <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K69" s="9" t="inlineStr"/>
-      <c r="L69" s="9" t="inlineStr"/>
-      <c r="M69" s="9" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1459 M56 AEROPUERTO.xlsx</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>M56</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>M056 - AEROPUERTO GYE</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3645,24 +3618,24 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1450 KFCK03 PLAZA QUIL.xlsx</t>
+          <t>COTIZACION1458 JV48 MALL DEL RIO GYE.xlsx</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>V48</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>K003 - PLAZA QUIL</t>
+          <t>V048 - MALL DEL RIO GYE</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -3690,24 +3663,24 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1459 M56 AEROPUERTO.xlsx</t>
+          <t>COTIZACION1457 BS20 RIOCENTRO NORTE.xlsx</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>M56</t>
+          <t>BS20</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>M056 - AEROPUERTO GYE</t>
+          <t>BS20 - RIO CENTRO NORTE</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -3735,24 +3708,24 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1458 JV48 MALL DEL RIO GYE.xlsx</t>
+          <t>COTIZACION1451 KFCK59 MALL DEL SUR PB.xlsx</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>V48</t>
+          <t>K59</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>V048 - MALL DEL RIO GYE</t>
+          <t>K059 - MALL DEL SUR P/B</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -3773,168 +3746,184 @@
       <c r="M72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1457 BS20 RIOCENTRO NORTE.xlsx</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>BS20</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>BS20 - RIO CENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr"/>
-      <c r="K73" s="3" t="inlineStr"/>
-      <c r="L73" s="3" t="inlineStr"/>
-      <c r="M73" s="3" t="inlineStr"/>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1453 GUSG50 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>GUSG50</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr"/>
+      <c r="E73" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr"/>
+      <c r="L73" s="7" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1451 KFCK59 MALL DEL SUR PB.xlsx</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>K59</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>K059 - MALL DEL SUR P/B</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr"/>
-      <c r="K74" s="3" t="inlineStr"/>
-      <c r="L74" s="3" t="inlineStr"/>
-      <c r="M74" s="3" t="inlineStr"/>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1454 AMCA06 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>AMCA6</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr"/>
+      <c r="E74" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="n"/>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1453 GUSG50 MALL DEL SUR.xlsx</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>GUSG50</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="F75" s="8" t="n"/>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="n"/>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K75" s="9" t="inlineStr"/>
-      <c r="L75" s="9" t="inlineStr"/>
-      <c r="M75" s="9" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1460 R004 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>R004 - SAN MARINO</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1454 AMCA06 TERMINAL.xlsx</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>AMCA6</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr"/>
-      <c r="E76" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="F76" s="8" t="n"/>
-      <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8" t="n"/>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
-        </is>
-      </c>
-      <c r="K76" s="9" t="inlineStr"/>
-      <c r="L76" s="9" t="inlineStr"/>
-      <c r="M76" s="9" t="inlineStr"/>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1463 R010 ORELLANA.xlsx</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>R010 - FRANCISCO DE ORELLANA</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>448.1</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 2×10lbCO2@$9 + 4×5lbCO2@$4 + 1×20lbPQS@$20 + 10×10lbPQS@$10 + 2×2.5glnK@$99</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbCO2@$9 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×2.5GLSTIPO K@$99 + 1×2.5GLSTIPO K@$99  [+MOVIL:$18.80 — GYE-ORELLANA]</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Viáticos COT=$0.00 vs DB=$18.80 | (viáticos no detectados en líneas COT, posible formato) | Extintores COT=$418.70 vs DB=$429.30 (neto $-10.60) | COT tiene +2×2.5glnK que no está en DB (precio $99/ext) | COT tiene +1×10lbCO2 que no está en DB (precio $9/ext) | DB tiene +2×2.5GLSTIPO K que no aparece en COT ($99/ext) | DB tiene +1×20lbPQS que no aparece en COT ($20/ext)</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 2×2.5glnK a BD? ($99/ext) | ¿AGREGAR 1×10lbCO2 a BD? ($9/ext) | ¿RETIRAR 2×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3944,28 +3933,28 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1460 R004 SAN MARINO.xlsx</t>
+          <t>COTIZACION1462 R008 MALL DEL SOL.xlsx</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>R004 - SAN MARINO</t>
+          <t>R008 - MALL DEL SOL</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>62</v>
+        <v>232.5</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>62</v>
+        <v>232.5</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO</t>
+          <t>RECARGA</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
@@ -3982,436 +3971,404 @@
       <c r="M77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1463 R010 ORELLANA.xlsx</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>R010 - FRANCISCO DE ORELLANA</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="n">
-        <v>418.7</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>448.1</v>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1461 R003 CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>R003 - 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H78" s="6" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1452 KFCK96 PORTETE.xlsx</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>K96</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>K096 - PORTETE</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J78" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$68 + 2×10lbCO2@$9 + 4×5lbCO2@$4 + 1×20lbPQS@$20 + 10×10lbPQS@$10 + 2×2.5glnK@$99</t>
-        </is>
-      </c>
-      <c r="K78" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$68 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbCO2@$9 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×2.5GLSTIPO K@$99 + 1×2.5GLSTIPO K@$99  [+MOVIL:$18.80 — GYE-ORELLANA]</t>
-        </is>
-      </c>
-      <c r="L78" s="7" t="inlineStr">
-        <is>
-          <t>Viáticos COT=$0.00 vs DB=$18.80 | (viáticos no detectados en líneas COT, posible formato) | Extintores COT=$418.70 vs DB=$429.30 (neto $-10.60) | COT tiene +1×10lbCO2 que no está en DB (precio $9/ext) | COT tiene +2×2.5glnK que no está en DB (precio $99/ext) | DB tiene +2×2.5GLSTIPO K que no aparece en COT ($99/ext) | DB tiene +1×20lbPQS que no aparece en COT ($20/ext)</t>
-        </is>
-      </c>
-      <c r="M78" s="7" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbCO2 a BD? ($9/ext) | ¿AGREGAR 2×2.5glnK a BD? ($99/ext) | ¿RETIRAR 2×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1462 R008 MALL DEL SOL.xlsx</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>R008 - MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>232.5</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>232.5</v>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr"/>
-      <c r="K79" s="3" t="inlineStr"/>
-      <c r="L79" s="3" t="inlineStr"/>
-      <c r="M79" s="3" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>2×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$76.00 vs DB=$84.00 (neto $-8.00) | Cantidad: 11 ext en COT vs 12 en DB | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1461 R003 CENTRO.xlsx</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>R003 - 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr"/>
-      <c r="K80" s="3" t="inlineStr"/>
-      <c r="L80" s="3" t="inlineStr"/>
-      <c r="M80" s="3" t="inlineStr"/>
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1501 ILCI04 MALL DEL SUR.xlsx</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>ILCI4</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr"/>
+      <c r="E80" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F80" s="6" t="n"/>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="n"/>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr"/>
+      <c r="L80" s="7" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1452 KFCK96 PORTETE.xlsx</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>K96</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>K096 - PORTETE</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="n">
-        <v>76</v>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1511 F003 DOLCE INCONTRO  AEROPUERTO.xlsx</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>F003 - DOLCE INCONTRO AERGYE</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t>2×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 3×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L81" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$76.00 vs DB=$84.00 (neto $-8.00) | Cantidad: 11 ext en COT vs 12 en DB | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M81" s="7" t="inlineStr">
-        <is>
-          <t>¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 3×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$42.00 vs DB=$38.00 (neto +$4.00) | Cantidad: 6 ext en COT vs 5 en DB | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1464 R010 ORELLANA.xlsx</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>R010 - FRANCISCO DE ORELLANA</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>448.1</v>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="n">
-        <v>79.92</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1507 CJNC08 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>J008 - TERMINAL</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J82" s="7" t="inlineStr">
-        <is>
-          <t>(sin líneas ext)</t>
-        </is>
-      </c>
-      <c r="K82" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$68 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbCO2@$9 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×2.5GLSTIPO K@$99 + 1×2.5GLSTIPO K@$99  [+MOVIL:$18.80 — GYE-ORELLANA]</t>
-        </is>
-      </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>Viáticos COT=$0.00 vs DB=$18.80 | (viáticos no detectados en líneas COT, posible formato) | Extintores COT=$0.00 vs DB=$429.30 (neto $-429.30) | Cantidad: 0 ext en COT vs 20 en DB | DB tiene +1×75lbCO2 que no aparece en COT ($68/ext) | DB tiene +2×2.5GLSTIPO K que no aparece en COT ($99/ext) | DB tiene +10×10lbPQS que no aparece en COT ($10/ext) | DB tiene +4×5lbCO2 que no aparece en COT ($4/ext) | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | DB tiene +2×20lbPQS que no aparece en COT ($20/ext)</t>
-        </is>
-      </c>
-      <c r="M82" s="7" t="inlineStr">
-        <is>
-          <t>¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 10×10lbPQS de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 4×5lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$28.00 vs DB=$38.00 (neto $-10.00) | COT tiene +1×50lbCO2 que no está en DB (precio $20/ext) | DB tiene +1×75lbCO2 que no aparece en COT ($30/ext)</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×50lbCO2 a BD? ($20/ext) | ¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1501 ILCI04 MALL DEL SUR.xlsx</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>ILCI4</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr"/>
-      <c r="E83" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K83" s="9" t="inlineStr"/>
-      <c r="L83" s="9" t="inlineStr"/>
-      <c r="M83" s="9" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1510 CN35 RIOCENTRO NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>BS35</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>CN35 - RIO CENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1511 F003 DOLCE INCONTRO  AEROPUERTO.xlsx</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>F003 - DOLCE INCONTRO AERGYE</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 3×10lbPQS@$4 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K84" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L84" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$42.00 vs DB=$38.00 (neto +$4.00) | Cantidad: 6 ext en COT vs 5 en DB | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M84" s="7" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1502 KFCK115 ENTRADA DE LA 8.xlsx</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>K115</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>K115 - ENTRADA DE LA 8</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr"/>
+      <c r="M84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1507 CJNC08 TERMINAL.xlsx</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>J8</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>J008 - TERMINAL</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K85" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×10lbPQS@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="L85" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$28.00 vs DB=$38.00 (neto $-10.00) | COT tiene +1×50lbCO2 que no está en DB (precio $20/ext) | DB tiene +1×75lbCO2 que no aparece en COT ($30/ext)</t>
-        </is>
-      </c>
-      <c r="M85" s="7" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×50lbCO2 a BD? ($20/ext) | ¿RETIRAR 1×75lbCO2 de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1512 KFCK83 MUCHO LOTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>K83</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>K083 - MUCHO LOTE</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4421,24 +4378,24 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1510 CN35 RIOCENTRO NORTE.xlsx</t>
+          <t>COTIZACION1508 T043 MALL EL FORTIN.xlsx</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>BS35</t>
+          <t>T43</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CN35 - RIO CENTRO NORTE</t>
+          <t>T043 - MALL EL FORTIN</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -4466,24 +4423,24 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1502 KFCK115 ENTRADA DE LA 8.xlsx</t>
+          <t>COTIZACION1509 CN34 RIOCENTRO SUR.xlsx</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>K115</t>
+          <t>BS34</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>K115 - ENTRADA DE LA 8</t>
+          <t>CN34 - RIO CENTRO SUR CINNABON TO GO</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -4504,94 +4461,78 @@
       <c r="M87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1512 KFCK83 MUCHO LOTE.xlsx</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>K83</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>K083 - MUCHO LOTE</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr"/>
-      <c r="K88" s="3" t="inlineStr"/>
-      <c r="L88" s="3" t="inlineStr"/>
-      <c r="M88" s="3" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1504 GUSG52 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>GUSG52</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr"/>
+      <c r="E88" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F88" s="6" t="n"/>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="n"/>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K88" s="7" t="inlineStr"/>
+      <c r="L88" s="7" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1508 T043 MALL EL FORTIN.xlsx</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>T43</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>T043 - MALL EL FORTIN</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr"/>
-      <c r="K89" s="3" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="3" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1503 GUSG48 TERMINAL.xlsx</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>GUSG48</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr"/>
+      <c r="E89" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F89" s="6" t="n"/>
+      <c r="G89" s="6" t="inlineStr"/>
+      <c r="H89" s="6" t="n"/>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr"/>
+      <c r="L89" s="7" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4601,24 +4542,24 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1509 CN34 RIOCENTRO SUR.xlsx</t>
+          <t>COTIZACION1505 M14 RIOCENTRO SUR.xlsx</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>BS34</t>
+          <t>M14</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>CN34 - RIO CENTRO SUR CINNABON TO GO</t>
+          <t>M014 - RIOCENTRO SUR</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -4639,105 +4580,137 @@
       <c r="M90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1504 GUSG52 CITY MALL.xlsx</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>GUSG52</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr"/>
-      <c r="E91" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="F91" s="8" t="n"/>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="n"/>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K91" s="9" t="inlineStr"/>
-      <c r="L91" s="9" t="inlineStr"/>
-      <c r="M91" s="9" t="inlineStr"/>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1500 KFCK79 MALECON BABAHOYO.xlsx</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>K79</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>K079 - BABAHOYO</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 2×10lbPQS@$4  [+MOVIL:$40.00 — MOVILZIACION GYE - BABAHOYO(75KM)]</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4  [+MOVIL:$39.00 — GYE-BABAHOYO 75KM]</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Viáticos COT=$40.00 vs DB=$39.00</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>Actualizar viáticos en DB: $39.00→$40.00</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1503 GUSG48 TERMINAL.xlsx</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>GUSG48</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr"/>
-      <c r="E92" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="F92" s="8" t="n"/>
-      <c r="G92" s="8" t="inlineStr"/>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J92" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K92" s="9" t="inlineStr"/>
-      <c r="L92" s="9" t="inlineStr"/>
-      <c r="M92" s="9" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1506 M28 VILLAGE PLAZA.xlsx</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>M28</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>M028 - VILLAGE</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr"/>
+      <c r="M92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>JUNIO</t>
+          <t>JULIO</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1505 M14 RIOCENTRO SUR.xlsx</t>
+          <t>COTIZACION1567 CJNC29 MALL DEL NORTE.xlsx</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>M14</t>
+          <t>J29</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>M014 - RIOCENTRO SUR</t>
+          <t>J029 - CAJUN MALL DEL NORTE</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -4758,76 +4731,68 @@
       <c r="M93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>JUNIO</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1500 KFCK79 MALECON BABAHOYO.xlsx</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>K79</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>K079 - BABAHOYO</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J94" s="3" t="inlineStr"/>
-      <c r="K94" s="3" t="inlineStr"/>
-      <c r="L94" s="3" t="inlineStr"/>
-      <c r="M94" s="3" t="inlineStr"/>
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1562 DOLCEI02 RIOC CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>DOLCEI2</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F94" s="6" t="n"/>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="n"/>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K94" s="7" t="inlineStr"/>
+      <c r="L94" s="7" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>JUNIO</t>
+          <t>JULIO</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1506 M28 VILLAGE PLAZA.xlsx</t>
+          <t>COTIZACION1554 CJNC21 MALL DEL SUR.xlsx</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>M28</t>
+          <t>J21</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>M028 - VILLAGE</t>
+          <t>J021 - MALL DEL SUR</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -4855,24 +4820,24 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1567 CJNC29 MALL DEL NORTE.xlsx</t>
+          <t>COTIZACION1569 KFCK93 QUEVEDO CENTRO.xlsx</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>J29</t>
+          <t>K93</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>J029 - CAJUN MALL DEL NORTE</t>
+          <t>K093 - QUEVEDO</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -4893,86 +4858,86 @@
       <c r="M96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1562 DOLCEI02 RIOC CEIBOS.xlsx</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
-        <is>
-          <t>DOLCEI2</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr"/>
-      <c r="E97" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1561 DI01 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>DI1</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>DI01 - DOLCE INCONTRO MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr"/>
+      <c r="K97" s="3" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr"/>
+      <c r="M97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1563 DOLCEI03 RIOC ENTRE RIOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>DOLCEI3</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr"/>
+      <c r="E98" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="6" t="n"/>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="6" t="n"/>
+      <c r="I98" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr"/>
-      <c r="L97" s="9" t="inlineStr"/>
-      <c r="M97" s="9" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>JULIO</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1554 CJNC21 MALL DEL SUR.xlsx</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>J21</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>J021 - MALL DEL SUR</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr"/>
-      <c r="K98" s="3" t="inlineStr"/>
-      <c r="L98" s="3" t="inlineStr"/>
-      <c r="M98" s="3" t="inlineStr"/>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="inlineStr"/>
+      <c r="L98" s="7" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4982,24 +4947,24 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1569 KFCK93 QUEVEDO CENTRO.xlsx</t>
+          <t>COTIZACION1564 CJNC20 LIBERTAD.xlsx</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>K93</t>
+          <t>J20</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>K093 - QUEVEDO</t>
+          <t>J020 - CAJUN PENINSULA</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -5020,86 +4985,86 @@
       <c r="M99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1561 DI01 MALL DEL SOL.xlsx</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>DI1</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>DI01 - DOLCE INCONTRO MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr"/>
-      <c r="K100" s="3" t="inlineStr"/>
-      <c r="L100" s="3" t="inlineStr"/>
-      <c r="M100" s="3" t="inlineStr"/>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1552 GUSG47 ALBORADA.xlsx</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>GUSG47</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr"/>
+      <c r="E100" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="F100" s="6" t="n"/>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="n"/>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$30 + 1×10lbCO2@$4 + 1×20lbPQS@$8 + 4×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="inlineStr"/>
+      <c r="L100" s="7" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1563 DOLCEI03 RIOC ENTRE RIOS.xlsx</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t>DOLCEI3</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr"/>
-      <c r="E101" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F101" s="8" t="n"/>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>1×10lbCO2@$4 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr"/>
-      <c r="M101" s="9" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1566 KFCK172 MALL DEL NORTE.xlsx</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>K172</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>K172 - MALL DEL NORTE</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="3" t="inlineStr"/>
+      <c r="L101" s="3" t="inlineStr"/>
+      <c r="M101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5109,24 +5074,24 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1564 CJNC20 LIBERTAD.xlsx</t>
+          <t>COTIZACION1565 KFCK78 DAULE.xlsx</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>J20</t>
+          <t>K78</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>J020 - CAJUN PENINSULA</t>
+          <t>K078 - SHOPPING DAULE</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -5147,41 +5112,49 @@
       <c r="M102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1552 GUSG47 ALBORADA.xlsx</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t>GUSG47</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr"/>
-      <c r="E103" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$30 + 1×10lbCO2@$4 + 1×20lbPQS@$8 + 4×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K103" s="9" t="inlineStr"/>
-      <c r="L103" s="9" t="inlineStr"/>
-      <c r="M103" s="9" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1555 CJNC06 RIOCENTRO ENTRE RIOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>J006 - CAJUN PUNTILLA</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr"/>
+      <c r="M103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5191,24 +5164,24 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1566 KFCK172 MALL DEL NORTE.xlsx</t>
+          <t>COTIZACION1568 M62 MALL DEL NORTE.xlsx</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>K172</t>
+          <t>M62</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>K172 - MALL DEL NORTE</t>
+          <t>M062 - MN MALL DEL NORTE GY</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -5236,24 +5209,24 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1565 KFCK78 DAULE.xlsx</t>
+          <t>COTIZACION1550 KFCK92 FORTIN.xlsx</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>K78</t>
+          <t>K92</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>K078 - SHOPPING DAULE</t>
+          <t>K092 - EL FORTIN</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -5281,24 +5254,24 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1555 CJNC06 RIOCENTRO ENTRE RIOS.xlsx</t>
+          <t>COTIZACION1559 JV03 SAN MARINO.xlsx</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>J006 - CAJUN PUNTILLA</t>
+          <t>V003 - SAN MARINO</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -5326,24 +5299,24 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1568 M62 MALL DEL NORTE.xlsx</t>
+          <t>COTIZACION1560 JV16 POLICENTRO.xlsx</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>M62</t>
+          <t>V16</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>M062 - MN MALL DEL NORTE GY</t>
+          <t>V016 - POLICENTRO</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -5371,24 +5344,24 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1550 KFCK92 FORTIN.xlsx</t>
+          <t>COTIZACION1551 KFCK165 PLAZA TIA DURAN.xlsx</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>K92</t>
+          <t>K165</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>K092 - EL FORTIN</t>
+          <t>K165 - PLAZA TIA DURAN</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -5416,24 +5389,24 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1559 JV03 SAN MARINO.xlsx</t>
+          <t>COTIZACION1553 KFCK58 MALL DEL SUR.xlsx</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>K58</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>V003 - SAN MARINO</t>
+          <t>K058 - MALL DEL SUR PLANTA ALTA</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -5461,24 +5434,24 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1560 JV16 POLICENTRO.xlsx</t>
+          <t>COTIZACION1558 JV05 URDESA.xlsx</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>V16</t>
+          <t>V5</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>V016 - POLICENTRO</t>
+          <t>V005 - URDESA</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -5499,94 +5472,78 @@
       <c r="M110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1551 KFCK165 PLAZA TIA DURAN.xlsx</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>K165</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>K165 - PLAZA TIA DURAN</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J111" s="3" t="inlineStr"/>
-      <c r="K111" s="3" t="inlineStr"/>
-      <c r="L111" s="3" t="inlineStr"/>
-      <c r="M111" s="3" t="inlineStr"/>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1556 AMCA07 SAN MARINO.xlsx</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>AMCA7</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr"/>
+      <c r="E111" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F111" s="6" t="n"/>
+      <c r="G111" s="6" t="inlineStr"/>
+      <c r="H111" s="6" t="n"/>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×20lbPQS@$8 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr"/>
+      <c r="L111" s="7" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1553 KFCK58 MALL DEL SUR.xlsx</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>K58</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>K058 - MALL DEL SUR PLANTA ALTA</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J112" s="3" t="inlineStr"/>
-      <c r="K112" s="3" t="inlineStr"/>
-      <c r="L112" s="3" t="inlineStr"/>
-      <c r="M112" s="3" t="inlineStr"/>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1557 AMCA20 VILLAGE PLAZA.xlsx</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>AMCA20</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr"/>
+      <c r="E112" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F112" s="6" t="n"/>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="6" t="n"/>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J112" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K112" s="7" t="inlineStr"/>
+      <c r="L112" s="7" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5596,24 +5553,24 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1558 JV05 URDESA.xlsx</t>
+          <t>COTIZACION1573 KFCK149 VENTANAS.xlsx</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>K149</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>V005 - URDESA</t>
+          <t>K149 - PETROCOMERIAL VENTANAS</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -5634,78 +5591,126 @@
       <c r="M113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1556 AMCA07 SAN MARINO.xlsx</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>AMCA7</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr"/>
-      <c r="E114" s="8" t="n">
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1574 KFCK162 SHELL PASCUALES.xlsx</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>K162</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>K162 - DAULE ESTACION</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 1×10lbPQS@$4 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$50.00 (neto $-4.00) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +1×20lbPQS que no aparece en COT ($8/ext)</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1575 KFCK171 SHELL ABUDHABI.xlsx</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>K171</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>K171 - SHELL ABU DABI</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="F114" s="8" t="n"/>
-      <c r="G114" s="8" t="inlineStr"/>
-      <c r="H114" s="8" t="n"/>
-      <c r="I114" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×20lbPQS@$8 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K114" s="9" t="inlineStr"/>
-      <c r="L114" s="9" t="inlineStr"/>
-      <c r="M114" s="9" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>JULIO</t>
-        </is>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1557 AMCA20 VILLAGE PLAZA.xlsx</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>AMCA20</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr"/>
-      <c r="E115" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="F115" s="8" t="n"/>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="8" t="n"/>
-      <c r="I115" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 3×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K115" s="9" t="inlineStr"/>
-      <c r="L115" s="9" t="inlineStr"/>
-      <c r="M115" s="9" t="inlineStr"/>
+      <c r="F115" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×20lbPQS@$8 + 1×2.5glnK@$8</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$44.00 vs DB=$40.00 (neto +$4.00) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×10lbCO2 que no está en DB (precio $4/ext) | COT tiene +1×20lbPQS que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +2×10lbPQS que no aparece en COT ($4/ext)</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×10lbCO2 a BD? ($4/ext) | ¿AGREGAR 1×20lbPQS a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5715,24 +5720,24 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1573 KFCK149 VENTANAS.xlsx</t>
+          <t>COTIZACION1570 KFCK106 SHOPPING QUEVEDO.xlsx</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>K149</t>
+          <t>K106</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>K149 - PETROCOMERIAL VENTANAS</t>
+          <t>K106 - SHOPPING QUEVEDO</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -5760,146 +5765,106 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>COTIZACION1574 KFCK162 SHELL PASCUALES.xlsx</t>
+          <t>COTIZACION1571 GUSG51 SHOPPING QUEVEDO.xlsx</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>K162</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>K162 - DAULE ESTACION</t>
-        </is>
-      </c>
+          <t>GUSG51</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr"/>
       <c r="E117" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="n">
-        <v>8</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F117" s="6" t="n"/>
+      <c r="G117" s="6" t="inlineStr"/>
+      <c r="H117" s="6" t="n"/>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>INCONSISTENCIA</t>
+          <t>SIN_MATCH_DB</t>
         </is>
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 1×10lbPQS@$4 + 2×10lbPQS@$4 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K117" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×5lbCO2@$2 + 1×20lbPQS@$8 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$46.00 vs DB=$50.00 (neto $-4.00) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +1×20lbPQS que no aparece en COT ($8/ext)</t>
-        </is>
-      </c>
-      <c r="M117" s="7" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 1×20lbPQS de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×10lbPQS@$4  [+MOVIL:$35.00 — MOVILIZACION (GUAYAQUIL-QUEVEDO)]</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="inlineStr"/>
+      <c r="L117" s="7" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1575 KFCK171 SHELL ABUDHABI.xlsx</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>K171</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>K171 - SHELL ABU DABI</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="F118" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J118" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×10lbCO2@$4 + 1×20lbPQS@$8 + 1×2.5glnK@$8</t>
-        </is>
-      </c>
-      <c r="K118" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 1×10lbPQS@$4 + 1×10lbPQS@$4 + 1×2.5GLSTIPO K@$8</t>
-        </is>
-      </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$44.00 vs DB=$40.00 (neto +$4.00) | COT tiene +1×10lbCO2 que no está en DB (precio $4/ext) | COT tiene +1×2.5glnK que no está en DB (precio $8/ext) | COT tiene +1×20lbPQS que no está en DB (precio $8/ext) | DB tiene +1×2.5GLSTIPO K que no aparece en COT ($8/ext) | DB tiene +2×10lbPQS que no aparece en COT ($4/ext)</t>
-        </is>
-      </c>
-      <c r="M118" s="7" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbCO2 a BD? ($4/ext) | ¿AGREGAR 1×2.5glnK a BD? ($8/ext) | ¿AGREGAR 1×20lbPQS a BD? ($8/ext) | ¿RETIRAR 1×2.5GLSTIPO K de BD? (o verificar si fue omitido en COT) | ¿RETIRAR 2×10lbPQS de BD? (o verificar si fue omitido en COT)</t>
-        </is>
-      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1572 M32 SHOPPING QUEVEDO.xlsx</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>M32</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>M032 - SHOPPING QUEVEDO</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr"/>
+      <c r="M118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>JULIO</t>
+          <t>AGOSTO</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1570 KFCK106 SHOPPING QUEVEDO.xlsx</t>
+          <t>COTIZACION1606 M39 BABAHOYO.xlsx</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>K106</t>
+          <t>M39</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>K106 - SHOPPING QUEVEDO</t>
+          <t>M039 - PASEO SHOPPING BABAHOYO</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -5920,68 +5885,68 @@
       <c r="M119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>JULIO</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1571 GUSG51 SHOPPING QUEVEDO.xlsx</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>GUSG51</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr"/>
-      <c r="E120" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="F120" s="8" t="n"/>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="8" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1614 ESPE22 AEROPUERTO ARRIBO NAC.xlsx</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>ESPE22</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr"/>
+      <c r="E120" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" s="6" t="n"/>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="n"/>
+      <c r="I120" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 1×5lbCO2@$2 + 1×10lbPQS@$4  [+MOVIL:$35.00 — MOVILIZACION (GUAYAQUIL-QUEVEDO)]</t>
-        </is>
-      </c>
-      <c r="K120" s="9" t="inlineStr"/>
-      <c r="L120" s="9" t="inlineStr"/>
-      <c r="M120" s="9" t="inlineStr"/>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 2×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K120" s="7" t="inlineStr"/>
+      <c r="L120" s="7" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>JULIO</t>
+          <t>AGOSTO</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1572 M32 SHOPPING QUEVEDO.xlsx</t>
+          <t>COTIZACION1603 KFCK53 SHOPPING BABAHOYO.xlsx</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>M32</t>
+          <t>K53</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>M032 - SHOPPING QUEVEDO</t>
+          <t>K053 - PASEO SHOPPING BABAHOYO</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
@@ -6009,24 +5974,24 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1606 M39 BABAHOYO.xlsx</t>
+          <t>COTIZACION1616 CN26 AEROPUERTO PREEMB.xlsx</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>M39</t>
+          <t>BS26</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>M039 - PASEO SHOPPING BABAHOYO</t>
+          <t>CN26 - PREEMB INTER GYE</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -6047,41 +6012,49 @@
       <c r="M122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1614 ESPE22 AEROPUERTO ARRIBO NAC.xlsx</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>ESPE22</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr"/>
-      <c r="E123" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F123" s="8" t="n"/>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="8" t="n"/>
-      <c r="I123" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>1×5lbCO2@$2 + 2×5lbPQS@$2</t>
-        </is>
-      </c>
-      <c r="K123" s="9" t="inlineStr"/>
-      <c r="L123" s="9" t="inlineStr"/>
-      <c r="M123" s="9" t="inlineStr"/>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1604 M10 MALECON Y SUCRE.xlsx</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>M010 - MALECON</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr"/>
+      <c r="K123" s="3" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr"/>
+      <c r="M123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6091,24 +6064,24 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1603 KFCK53 SHOPPING BABAHOYO.xlsx</t>
+          <t>COTIZACION1601 KFCK12 RIOCENTRO PUNTILLA.xlsx</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>K53</t>
+          <t>K12</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>K053 - PASEO SHOPPING BABAHOYO</t>
+          <t>K012 - RIO CENTRO</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -6136,24 +6109,24 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1616 CN26 AEROPUERTO PREEMB.xlsx</t>
+          <t>COTIZACION1605 M21 TERMINAL.xlsx</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>BS26</t>
+          <t>M21</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>CN26 - PREEMB INTER GYE</t>
+          <t>M021 - TERMINAL TER GYQ.</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -6181,24 +6154,24 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1604 M10 MALECON Y SUCRE.xlsx</t>
+          <t>COTIZACION1607 M43 FORTIN.xlsx</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M43</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>M010 - MALECON</t>
+          <t>M043 - EL FORTIN</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -6226,24 +6199,24 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1601 KFCK12 RIOCENTRO PUNTILLA.xlsx</t>
+          <t>COTIZACION1615 CA03 DUPORT AEROPUERTO ARRIBO NAC.xlsx</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>K12</t>
+          <t>CA3</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>K012 - RIO CENTRO</t>
+          <t>CA03 - CAFE DUPORT HALL PRINCIPAL</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -6264,49 +6237,41 @@
       <c r="M127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1605 M21 TERMINAL.xlsx</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>M21</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>M021 - TERMINAL TER GYQ.</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J128" s="3" t="inlineStr"/>
-      <c r="K128" s="3" t="inlineStr"/>
-      <c r="L128" s="3" t="inlineStr"/>
-      <c r="M128" s="3" t="inlineStr"/>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1609 AMCA19 MALL DEL SOL.xlsx</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>AMCA19</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr"/>
+      <c r="E128" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F128" s="6" t="n"/>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="n"/>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×10lbCO2@$4</t>
+        </is>
+      </c>
+      <c r="K128" s="7" t="inlineStr"/>
+      <c r="L128" s="7" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6316,24 +6281,24 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1607 M43 FORTIN.xlsx</t>
+          <t>COTIZACION1611 DI04 URDESA.xlsx</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>M43</t>
+          <t>DI4</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>M043 - EL FORTIN</t>
+          <t>DI04 - DOLCE INCONTRO URDESA</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
@@ -6361,24 +6326,24 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1615 CA03 DUPORT AEROPUERTO ARRIBO NAC.xlsx</t>
+          <t>COTIZACION1612 CA01 ASTORIA.xlsx</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>CA3</t>
+          <t>CA1</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>CA03 - CAFE DUPORT HALL PRINCIPAL</t>
+          <t>CA01 - CAFE ASTORIA SALIDA INTERNACIONAL</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
@@ -6399,41 +6364,49 @@
       <c r="M130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1609 AMCA19 MALL DEL SOL.xlsx</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr">
-        <is>
-          <t>AMCA19</t>
-        </is>
-      </c>
-      <c r="D131" s="8" t="inlineStr"/>
-      <c r="E131" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="F131" s="8" t="n"/>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="8" t="n"/>
-      <c r="I131" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J131" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×10lbCO2@$4</t>
-        </is>
-      </c>
-      <c r="K131" s="9" t="inlineStr"/>
-      <c r="L131" s="9" t="inlineStr"/>
-      <c r="M131" s="9" t="inlineStr"/>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1613 CA02 ASTORIA.xlsx</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>CA2</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>CA02 - CAFE ASTORIA PREEMBARQUE INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr"/>
+      <c r="M131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6443,24 +6416,24 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1611 DI04 URDESA.xlsx</t>
+          <t>COTIZACION1602 KFCK52 PEÑAS.xlsx</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>DI4</t>
+          <t>K52</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>DI04 - DOLCE INCONTRO URDESA</t>
+          <t>K052 - LAS PEÃ????AS</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -6488,24 +6461,24 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1612 CA01 ASTORIA.xlsx</t>
+          <t>COTIZACION1608 CJNC05 RIOCENTRO CEIBOS.xlsx</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>CA1</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>CA01 - CAFE ASTORIA SALIDA INTERNACIONAL</t>
+          <t>J005 - CAJUN CEIBOS</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
@@ -6533,24 +6506,24 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1613 CA02 ASTORIA.xlsx</t>
+          <t>COTIZACION1600 KFCK21 MALL DEL SOL.xlsx</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>CA2</t>
+          <t>K21</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>CA02 - CAFE ASTORIA PREEMBARQUE INTERNACIONAL</t>
+          <t>K021 - MALL EL SOL</t>
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -6571,76 +6544,68 @@
       <c r="M134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1602 KFCK52 PEÑAS.xlsx</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>K52</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>K052 - LAS PEÃ????AS</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J135" s="3" t="inlineStr"/>
-      <c r="K135" s="3" t="inlineStr"/>
-      <c r="L135" s="3" t="inlineStr"/>
-      <c r="M135" s="3" t="inlineStr"/>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1610 ESPE07 URDESA.xlsx</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>ESPE7</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr"/>
+      <c r="E135" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F135" s="6" t="n"/>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="n"/>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>2×5lbCO2@$2 + 4×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K135" s="7" t="inlineStr"/>
+      <c r="L135" s="7" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>AGOSTO</t>
+          <t>SEPTIEMBRE</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>COTIZACION1608 CJNC05 RIOCENTRO CEIBOS.xlsx</t>
+          <t>COTIZACION1650 KFCK129 EXCLUSAS.xlsx</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>K129</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>J005 - CAJUN CEIBOS</t>
+          <t>K129 - LLEVAR 5 ESQUINAS</t>
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -6661,452 +6626,460 @@
       <c r="M136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1600 KFCK21 MALL DEL SOL.xlsx</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>K21</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>K021 - MALL EL SOL</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J137" s="3" t="inlineStr"/>
-      <c r="K137" s="3" t="inlineStr"/>
-      <c r="L137" s="3" t="inlineStr"/>
-      <c r="M137" s="3" t="inlineStr"/>
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1651 AMCA33 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>AMCA33</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr"/>
+      <c r="E137" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F137" s="6" t="n"/>
+      <c r="G137" s="6" t="inlineStr"/>
+      <c r="H137" s="6" t="n"/>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K137" s="7" t="inlineStr"/>
+      <c r="L137" s="7" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1610 ESPE07 URDESA.xlsx</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="inlineStr">
-        <is>
-          <t>ESPE7</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr"/>
-      <c r="E138" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="F138" s="8" t="n"/>
-      <c r="G138" s="8" t="inlineStr"/>
-      <c r="H138" s="8" t="n"/>
-      <c r="I138" s="8" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1652 BS22 POLICENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>BS22</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>BS22 - POLICENTRO</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr"/>
+      <c r="K138" s="3" t="inlineStr"/>
+      <c r="L138" s="3" t="inlineStr"/>
+      <c r="M138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1653 ESPE31 POLICENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>ESPE31</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr"/>
+      <c r="E139" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F139" s="6" t="n"/>
+      <c r="G139" s="6" t="inlineStr"/>
+      <c r="H139" s="6" t="n"/>
+      <c r="I139" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J138" s="9" t="inlineStr">
-        <is>
-          <t>2×5lbCO2@$2 + 4×10lbPQS@$4 + 1×5lbPQS@$2</t>
-        </is>
-      </c>
-      <c r="K138" s="9" t="inlineStr"/>
-      <c r="L138" s="9" t="inlineStr"/>
-      <c r="M138" s="9" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="inlineStr"/>
+      <c r="L139" s="7" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1650 KFCK129 EXCLUSAS.xlsx</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>K129</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>K129 - LLEVAR 5 ESQUINAS</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J139" s="3" t="inlineStr"/>
-      <c r="K139" s="3" t="inlineStr"/>
-      <c r="L139" s="3" t="inlineStr"/>
-      <c r="M139" s="3" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t>SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1651 AMCA33 CITY MALL.xlsx</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="inlineStr">
-        <is>
-          <t>AMCA33</t>
-        </is>
-      </c>
-      <c r="D140" s="8" t="inlineStr"/>
-      <c r="E140" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="F140" s="8" t="n"/>
-      <c r="G140" s="8" t="inlineStr"/>
-      <c r="H140" s="8" t="n"/>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>COTIZACION1654 V080 AGORA.xlsx</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>V80</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>V080 - AGORA GYE</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr"/>
+      <c r="K140" s="3" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr"/>
+      <c r="M140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1213 KFC OFICINAS CENTRO.xlsx</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>KFC</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr"/>
+      <c r="E141" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="F141" s="6" t="n"/>
+      <c r="G141" s="6" t="inlineStr"/>
+      <c r="H141" s="6" t="n"/>
+      <c r="I141" s="6" t="inlineStr">
         <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J140" s="9" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K140" s="9" t="inlineStr"/>
-      <c r="L140" s="9" t="inlineStr"/>
-      <c r="M140" s="9" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1652 BS22 POLICENTRO.xlsx</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>BS22</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>BS22 - POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J141" s="3" t="inlineStr"/>
-      <c r="K141" s="3" t="inlineStr"/>
-      <c r="L141" s="3" t="inlineStr"/>
-      <c r="M141" s="3" t="inlineStr"/>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>1×10lbCO2@$4 + 4×5lbCO2@$2 + 12×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr"/>
+      <c r="L141" s="7" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>SEPTIEMBRE</t>
+          <t>OCTUBRE</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>COTIZACION1653 ESPE31 POLICENTRO.xlsx</t>
+          <t>COTIZACION1217 M33 CITY MALL.xlsx</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>ESPE31</t>
-        </is>
-      </c>
-      <c r="D142" s="8" t="inlineStr"/>
+          <t>M33</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>M033 - CITY MALL</t>
+        </is>
+      </c>
       <c r="E142" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F142" s="8" t="n"/>
-      <c r="G142" s="8" t="inlineStr"/>
-      <c r="H142" s="8" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="n">
+        <v>56.11</v>
+      </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K142" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L142" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×10lbPQS: precio COT=$4 vs DB=$10/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext</t>
+        </is>
+      </c>
+      <c r="M142" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $63.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>COTIZACION1218 CJNC11 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>J011 - CITY MALL</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F143" s="8" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t>COT_DEBE_RECARGA</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K143" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L143" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×10lbPQS: precio COT=$4 vs DB=$10/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext</t>
+        </is>
+      </c>
+      <c r="M143" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $63.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1219 ESPE09 RIOCENTRO CEIBOS.xlsx</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>ESPE9</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr"/>
+      <c r="E144" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F144" s="6" t="n"/>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="6" t="n"/>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
           <t>SIN_MATCH_DB</t>
         </is>
       </c>
-      <c r="J142" s="9" t="inlineStr">
-        <is>
-          <t>1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K142" s="9" t="inlineStr"/>
-      <c r="L142" s="9" t="inlineStr"/>
-      <c r="M142" s="9" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>COTIZACION1654 V080 AGORA.xlsx</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>V80</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>V080 - AGORA GYE</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="n">
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr"/>
+      <c r="L144" s="7" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>COTIZACION1220 ESPE30 CITY MALL.xlsx</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>ESPE30</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr"/>
+      <c r="E145" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F143" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J143" s="3" t="inlineStr"/>
-      <c r="K143" s="3" t="inlineStr"/>
-      <c r="L143" s="3" t="inlineStr"/>
-      <c r="M143" s="3" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="8" t="inlineStr">
+      <c r="F145" s="6" t="n"/>
+      <c r="G145" s="6" t="inlineStr"/>
+      <c r="H145" s="6" t="n"/>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>SIN_MATCH_DB</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>1×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K145" s="7" t="inlineStr"/>
+      <c r="L145" s="7" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1213 KFC OFICINAS CENTRO.xlsx</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr">
-        <is>
-          <t>KFC</t>
-        </is>
-      </c>
-      <c r="D144" s="8" t="inlineStr"/>
-      <c r="E144" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="F144" s="8" t="n"/>
-      <c r="G144" s="8" t="inlineStr"/>
-      <c r="H144" s="8" t="n"/>
-      <c r="I144" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J144" s="9" t="inlineStr">
-        <is>
-          <t>1×10lbCO2@$4 + 4×5lbCO2@$2 + 12×10lbPQS@$4 + 1×5lbPQS@$2</t>
-        </is>
-      </c>
-      <c r="K144" s="9" t="inlineStr"/>
-      <c r="L144" s="9" t="inlineStr"/>
-      <c r="M144" s="9" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t>COTIZACION1217 M33 CITY MALL.xlsx</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>M33</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>M033 - CITY MALL</t>
-        </is>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="F145" s="10" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="G145" s="10" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>COTIZACION1221 M61 PORTETE.xlsx</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>M61</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>M061 - PORTETE</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H145" s="10" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="I145" s="10" t="inlineStr">
+      <c r="H146" s="8" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="I146" s="8" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J145" s="11" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K145" s="11" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
-        </is>
-      </c>
-      <c r="L145" s="11" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext</t>
-        </is>
-      </c>
-      <c r="M145" s="11" t="inlineStr">
-        <is>
-          <t>Reemitir cotización como RECARGA por $63.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B146" s="10" t="inlineStr">
-        <is>
-          <t>COTIZACION1218 CJNC11 CITY MALL.xlsx</t>
-        </is>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
-        <is>
-          <t>J11</t>
-        </is>
-      </c>
-      <c r="D146" s="10" t="inlineStr">
-        <is>
-          <t>J011 - CITY MALL</t>
-        </is>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="F146" s="10" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="G146" s="10" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H146" s="10" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="I146" s="10" t="inlineStr">
-        <is>
-          <t>COT_DEBE_RECARGA</t>
-        </is>
-      </c>
-      <c r="J146" s="11" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K146" s="11" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
-        </is>
-      </c>
-      <c r="L146" s="11" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($28.00). Debería ser RECARGA ($63.80). | Extintores COT=$28.00 vs DB=$63.80 (neto $-35.80) | 1×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×5lbCO2: precio COT=$2 vs DB=$4/ext</t>
-        </is>
-      </c>
-      <c r="M146" s="11" t="inlineStr">
-        <is>
-          <t>Reemitir cotización como RECARGA por $63.80</t>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 6×10lbPQS@$4 + 2×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K146" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20</t>
+        </is>
+      </c>
+      <c r="L146" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($64.00). Debería ser RECARGA ($152.00). | Extintores COT=$64.00 vs DB=$152.00 (neto $-88.00) | 2×20lbPQS: precio COT=$8 vs DB=$20/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 6×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×10lbCO2: precio COT=$4 vs DB=$9/ext</t>
+        </is>
+      </c>
+      <c r="M146" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $152.00</t>
         </is>
       </c>
     </row>
@@ -7118,433 +7091,298 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>COTIZACION1219 ESPE09 RIOCENTRO CEIBOS.xlsx</t>
+          <t>COTIZACION1222 KFCK109 CITY MALL PA.xlsx</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>ESPE9</t>
-        </is>
-      </c>
-      <c r="D147" s="8" t="inlineStr"/>
+          <t>K109</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>K109 - CITY MALL PA</t>
+        </is>
+      </c>
       <c r="E147" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F147" s="8" t="n"/>
-      <c r="G147" s="8" t="inlineStr"/>
-      <c r="H147" s="8" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="F147" s="8" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="n">
+        <v>56.04</v>
+      </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>SIN_MATCH_DB</t>
+          <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
       <c r="J147" s="9" t="inlineStr">
         <is>
-          <t>1×5lbCO2@$2 + 1×10lbPQS@$4 + 1×5lbPQS@$2</t>
-        </is>
-      </c>
-      <c r="K147" s="9" t="inlineStr"/>
-      <c r="L147" s="9" t="inlineStr"/>
-      <c r="M147" s="9" t="inlineStr"/>
+          <t>1×50lb?@$20 + 1×10lbCO2@$4 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L147" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($32.00). Debería ser RECARGA ($72.80). | Extintores COT=$32.00 vs DB=$72.80 (neto $-40.80) | COT tiene +1×50lb? que no está en DB (precio $20/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($45/ext) | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×10lbCO2: precio COT=$4 vs DB=$9/ext</t>
+        </is>
+      </c>
+      <c r="M147" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $72.80</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="inlineStr">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
-        <is>
-          <t>COTIZACION1220 ESPE30 CITY MALL.xlsx</t>
-        </is>
-      </c>
-      <c r="C148" s="8" t="inlineStr">
-        <is>
-          <t>ESPE30</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="inlineStr"/>
-      <c r="E148" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F148" s="8" t="n"/>
-      <c r="G148" s="8" t="inlineStr"/>
-      <c r="H148" s="8" t="n"/>
-      <c r="I148" s="8" t="inlineStr">
-        <is>
-          <t>SIN_MATCH_DB</t>
-        </is>
-      </c>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>1×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K148" s="9" t="inlineStr"/>
-      <c r="L148" s="9" t="inlineStr"/>
-      <c r="M148" s="9" t="inlineStr"/>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1214 KFCK88 HIPER VIA A DAULE.xlsx</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>K88</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>K088 - HIPERMARKET VIA DAULE</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 3×10lbPQS@$4 + 1×20lbPQS@$8</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$46.00 vs DB=$97.70 (neto $-51.70) | Cantidad: 8 ext en COT vs 7 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | 3×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 1×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext? | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext?</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="10" t="inlineStr">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B149" s="10" t="inlineStr">
-        <is>
-          <t>COTIZACION1221 M61 PORTETE.xlsx</t>
-        </is>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>M61</t>
-        </is>
-      </c>
-      <c r="D149" s="10" t="inlineStr">
-        <is>
-          <t>M061 - PORTETE</t>
-        </is>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="F149" s="10" t="n">
-        <v>152</v>
-      </c>
-      <c r="G149" s="10" t="inlineStr">
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1215 KFCK110 CITY MALL PB.xlsx</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>K110</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>K110 - CITY MALL PB</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H149" s="10" t="n">
-        <v>57.89</v>
-      </c>
-      <c r="I149" s="10" t="inlineStr">
+      <c r="H149" s="4" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>INCONSISTENCIA</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×20lbPQS@$8 + 2×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>1×75lbCO2@$68 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>Extintores COT=$50.00 vs DB=$124.70 (neto $-74.70) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×75lbCO2: precio COT=$30 vs DB=$68/ext | 2×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr">
+        <is>
+          <t>¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 75lbCO2 en BD: $68→$30/ext? | ¿Actualizar precio 10lbPQS en BD: $10→$4/ext? | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext?</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>COTIZACION1216 KFCK117 SEDALANA.xlsx</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>K117</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>K117 - 29 Y SEDALANA</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="F150" s="8" t="n">
+        <v>241.2</v>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>RECARGA</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
         <is>
           <t>COT_DEBE_RECARGA</t>
         </is>
       </c>
-      <c r="J149" s="11" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 1×10lbCO2@$4 + 6×10lbPQS@$4 + 2×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="K149" s="11" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20</t>
-        </is>
-      </c>
-      <c r="L149" s="11" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($64.00). Debería ser RECARGA ($152.00). | Extintores COT=$64.00 vs DB=$152.00 (neto $-88.00) | 1×10lbCO2: precio COT=$4 vs DB=$9/ext | 6×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
-        </is>
-      </c>
-      <c r="M149" s="11" t="inlineStr">
-        <is>
-          <t>Reemitir cotización como RECARGA por $152.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="10" t="inlineStr">
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>3×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 5×10lbPQS@$4</t>
+        </is>
+      </c>
+      <c r="K150" s="9" t="inlineStr">
+        <is>
+          <t>1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10</t>
+        </is>
+      </c>
+      <c r="L150" s="9" t="inlineStr">
+        <is>
+          <t>⚠ COT usa precio MANTENIMIENTO ($104.00). Debería ser RECARGA ($241.20). | Extintores COT=$104.00 vs DB=$241.20 (neto $-137.20) | 4×5lbCO2: precio COT=$2 vs DB=$4/ext | 3×50lbCO2: precio COT=$20 vs DB=$45/ext | 5×10lbPQS: precio COT=$4 vs DB=$10/ext | 2×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
+        </is>
+      </c>
+      <c r="M150" s="9" t="inlineStr">
+        <is>
+          <t>Reemitir cotización como RECARGA por $241.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B150" s="10" t="inlineStr">
-        <is>
-          <t>COTIZACION1222 KFCK109 CITY MALL PA.xlsx</t>
-        </is>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>K109</t>
-        </is>
-      </c>
-      <c r="D150" s="10" t="inlineStr">
-        <is>
-          <t>K109 - CITY MALL PA</t>
-        </is>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="F150" s="10" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="G150" s="10" t="inlineStr">
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>COTIZACION1212 B001 ARRECIFE AEROPUERTO.xlsx</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>B001 - STATION SPORTS BAR</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
         <is>
           <t>RECARGA</t>
         </is>
       </c>
-      <c r="H150" s="10" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="I150" s="10" t="inlineStr">
-        <is>
-          <t>COT_DEBE_RECARGA</t>
-        </is>
-      </c>
-      <c r="J150" s="11" t="inlineStr">
-        <is>
-          <t>1×50lb?@$20 + 1×10lbCO2@$4 + 2×5lbCO2@$2 + 1×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K150" s="11" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10</t>
-        </is>
-      </c>
-      <c r="L150" s="11" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($32.00). Debería ser RECARGA ($72.80). | Extintores COT=$32.00 vs DB=$72.80 (neto $-40.80) | COT tiene +1×50lb? que no está en DB (precio $20/ext) | DB tiene +1×50lbCO2 que no aparece en COT ($45/ext) | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×10lbCO2: precio COT=$4 vs DB=$9/ext | 1×10lbPQS: precio COT=$4 vs DB=$10/ext</t>
-        </is>
-      </c>
-      <c r="M150" s="11" t="inlineStr">
-        <is>
-          <t>Reemitir cotización como RECARGA por $72.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1214 KFCK88 HIPER VIA A DAULE.xlsx</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>K88</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>K088 - HIPERMARKET VIA DAULE</t>
-        </is>
-      </c>
-      <c r="E151" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="F151" s="6" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="G151" s="6" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H151" s="6" t="n">
-        <v>52.92</v>
-      </c>
-      <c r="I151" s="6" t="inlineStr">
+      <c r="H151" s="4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
         <is>
           <t>INCONSISTENCIA</t>
         </is>
       </c>
-      <c r="J151" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$20 + 3×5lbCO2@$2 + 3×10lbPQS@$4 + 1×20lbPQS@$8</t>
-        </is>
-      </c>
-      <c r="K151" s="7" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
-        </is>
-      </c>
-      <c r="L151" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$46.00 vs DB=$97.70 (neto $-51.70) | Cantidad: 8 ext en COT vs 7 en DB | COT tiene +1×10lbPQS que no está en DB (precio $4/ext) | 3×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext | 1×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
-        </is>
-      </c>
-      <c r="M151" s="7" t="inlineStr">
-        <is>
-          <t>¿AGREGAR 1×10lbPQS a BD? ($4/ext) | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext? | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext?</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1215 KFCK110 CITY MALL PB.xlsx</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>K110</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>K110 - CITY MALL PB</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="F152" s="6" t="n">
-        <v>124.7</v>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H152" s="6" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="I152" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J152" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$30 + 2×5lbCO2@$2 + 1×20lbPQS@$8 + 2×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K152" s="7" t="inlineStr">
-        <is>
-          <t>1×75lbCO2@$68 + 1×10lbCO2@$9 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×20lbPQS@$20 + 1×10lbPQS@$10 + 1×10lbPQS@$10</t>
-        </is>
-      </c>
-      <c r="L152" s="7" t="inlineStr">
-        <is>
-          <t>Extintores COT=$50.00 vs DB=$124.70 (neto $-74.70) | Cantidad: 6 ext en COT vs 7 en DB | DB tiene +1×10lbCO2 que no aparece en COT ($9/ext) | 2×5lbCO2: precio COT=$2 vs DB=$4/ext | 1×75lbCO2: precio COT=$30 vs DB=$68/ext | 2×10lbPQS: precio COT=$4 vs DB=$10/ext | 1×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
-        </is>
-      </c>
-      <c r="M152" s="7" t="inlineStr">
-        <is>
-          <t>¿RETIRAR 1×10lbCO2 de BD? (o verificar si fue omitido en COT) | ¿Actualizar precio 5lbCO2 en BD: $4→$2/ext? | ¿Actualizar precio 75lbCO2 en BD: $68→$30/ext? | ¿Actualizar precio 10lbPQS en BD: $10→$4/ext? | ¿Actualizar precio 20lbPQS en BD: $20→$8/ext?</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="10" t="inlineStr">
-        <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t>COTIZACION1216 KFCK117 SEDALANA.xlsx</t>
-        </is>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
-        <is>
-          <t>K117</t>
-        </is>
-      </c>
-      <c r="D153" s="10" t="inlineStr">
-        <is>
-          <t>K117 - 29 Y SEDALANA</t>
-        </is>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>104</v>
-      </c>
-      <c r="F153" s="10" t="n">
-        <v>241.2</v>
-      </c>
-      <c r="G153" s="10" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H153" s="10" t="n">
-        <v>56.88</v>
-      </c>
-      <c r="I153" s="10" t="inlineStr">
-        <is>
-          <t>COT_DEBE_RECARGA</t>
-        </is>
-      </c>
-      <c r="J153" s="11" t="inlineStr">
-        <is>
-          <t>3×50lbCO2@$20 + 4×5lbCO2@$2 + 2×20lbPQS@$8 + 5×10lbPQS@$4</t>
-        </is>
-      </c>
-      <c r="K153" s="11" t="inlineStr">
-        <is>
-          <t>1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×50lbCO2@$45 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×5lbCO2@$4 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×20lbPQS@$20 + 1×20lbPQS@$20 + 1×10lbPQS@$10</t>
-        </is>
-      </c>
-      <c r="L153" s="11" t="inlineStr">
-        <is>
-          <t>⚠ COT usa precio MANTENIMIENTO ($104.00). Debería ser RECARGA ($241.20). | Extintores COT=$104.00 vs DB=$241.20 (neto $-137.20) | 4×5lbCO2: precio COT=$2 vs DB=$4/ext | 5×10lbPQS: precio COT=$4 vs DB=$10/ext | 3×50lbCO2: precio COT=$20 vs DB=$45/ext | 2×20lbPQS: precio COT=$8 vs DB=$20/ext</t>
-        </is>
-      </c>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>Reemitir cotización como RECARGA por $241.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>COTIZACION1212 B001 ARRECIFE AEROPUERTO.xlsx</t>
-        </is>
-      </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>B001 - STATION SPORTS BAR</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="F154" s="6" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>RECARGA</t>
-        </is>
-      </c>
-      <c r="H154" s="6" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>INCONSISTENCIA</t>
-        </is>
-      </c>
-      <c r="J154" s="7" t="inlineStr">
+      <c r="J151" s="5" t="inlineStr">
         <is>
           <t>1×20lbCO2@$20 + 3×10lbPQS@$10 + 2×5lbPQS@$5 + 1×50lbCO2@$20</t>
         </is>
       </c>
-      <c r="K154" s="7" t="inlineStr">
+      <c r="K151" s="5" t="inlineStr">
         <is>
           <t>1×50lbCO2@$45 + 1×20lbCO2@$18 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×10lbPQS@$10 + 1×5lbPQS@$5 + 1×5lbPQS@$5</t>
         </is>
       </c>
-      <c r="L154" s="7" t="inlineStr">
+      <c r="L151" s="5" t="inlineStr">
         <is>
           <t>Extintores COT=$78.80 vs DB=$102.20 (neto $-23.40) | 1×20lbCO2: precio COT=$20 vs DB=$18/ext | 1×50lbCO2: precio COT=$20 vs DB=$45/ext</t>
         </is>
       </c>
-      <c r="M154" s="7" t="inlineStr">
+      <c r="M151" s="5" t="inlineStr">
         <is>
           <t>¿Actualizar precio 20lbCO2 en BD: $18→$20/ext? | ¿Actualizar precio 50lbCO2 en BD: $45→$20/ext?</t>
         </is>
@@ -7569,7 +7407,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>RESUMEN REVISION COTIZACIONES 2026</t>
         </is>
@@ -7587,7 +7425,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
@@ -7597,7 +7435,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
@@ -7687,7 +7525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>21</v>
@@ -7702,7 +7540,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7762,7 +7600,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -7777,7 +7615,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -7787,13 +7625,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -7815,10 +7653,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
